--- a/воры/Amazing_Pics_SKU ALL_06.10.2026.xlsx
+++ b/воры/Amazing_Pics_SKU ALL_06.10.2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\воры\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933D827E-360D-41B8-BA75-363EF0B8782C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A4DB10-8233-4F3A-92AB-9A2B044EBE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8077,9 +8077,15 @@
       <c r="B243" s="13">
         <v>1912202150</v>
       </c>
-      <c r="C243" s="15"/>
-      <c r="D243" s="15"/>
-      <c r="E243" s="15"/>
+      <c r="C243" s="15">
+        <v>5550990571</v>
+      </c>
+      <c r="D243" s="15">
+        <v>5563643576</v>
+      </c>
+      <c r="E243" s="15">
+        <v>5739119917</v>
+      </c>
       <c r="F243" s="15"/>
       <c r="G243" s="15"/>
       <c r="H243" s="15"/>
@@ -8129,8 +8135,12 @@
       <c r="B245" s="13">
         <v>1912202516</v>
       </c>
-      <c r="C245" s="15"/>
-      <c r="D245" s="15"/>
+      <c r="C245" s="15">
+        <v>5260051785</v>
+      </c>
+      <c r="D245" s="15">
+        <v>5563644796</v>
+      </c>
       <c r="E245" s="15"/>
       <c r="F245" s="15"/>
       <c r="G245" s="15"/>
@@ -8155,8 +8165,12 @@
       <c r="B246" s="13">
         <v>1912202637</v>
       </c>
-      <c r="C246" s="15"/>
-      <c r="D246" s="15"/>
+      <c r="C246" s="15">
+        <v>5563647744</v>
+      </c>
+      <c r="D246" s="15">
+        <v>5739118888</v>
+      </c>
       <c r="E246" s="15"/>
       <c r="F246" s="15"/>
       <c r="G246" s="15"/>
@@ -8181,7 +8195,9 @@
       <c r="B247" s="13">
         <v>1912201812</v>
       </c>
-      <c r="C247" s="15"/>
+      <c r="C247" s="15">
+        <v>5739118581</v>
+      </c>
       <c r="D247" s="15"/>
       <c r="E247" s="15"/>
       <c r="F247" s="15"/>
@@ -8207,8 +8223,12 @@
       <c r="B248" s="13">
         <v>1912202756</v>
       </c>
-      <c r="C248" s="15"/>
-      <c r="D248" s="15"/>
+      <c r="C248" s="15">
+        <v>5260238915</v>
+      </c>
+      <c r="D248" s="15">
+        <v>5563642466</v>
+      </c>
       <c r="E248" s="15"/>
       <c r="F248" s="15"/>
       <c r="G248" s="15"/>
@@ -8259,7 +8279,9 @@
       <c r="B250" s="13">
         <v>1912202058</v>
       </c>
-      <c r="C250" s="15"/>
+      <c r="C250" s="15">
+        <v>5739118779</v>
+      </c>
       <c r="D250" s="15"/>
       <c r="E250" s="15"/>
       <c r="F250" s="15"/>
@@ -8285,9 +8307,15 @@
       <c r="B251" s="13">
         <v>2449977854</v>
       </c>
-      <c r="C251" s="15"/>
-      <c r="D251" s="15"/>
-      <c r="E251" s="15"/>
+      <c r="C251" s="15">
+        <v>4860283414</v>
+      </c>
+      <c r="D251" s="15">
+        <v>4850262687</v>
+      </c>
+      <c r="E251" s="15">
+        <v>4927493709</v>
+      </c>
       <c r="F251" s="15"/>
       <c r="G251" s="15"/>
       <c r="H251" s="15"/>
@@ -8312,10 +8340,18 @@
       <c r="B252" s="13">
         <v>2449977213</v>
       </c>
-      <c r="C252" s="15"/>
-      <c r="D252" s="15"/>
-      <c r="E252" s="15"/>
-      <c r="F252" s="15"/>
+      <c r="C252" s="15">
+        <v>5534248382</v>
+      </c>
+      <c r="D252" s="15">
+        <v>4860284001</v>
+      </c>
+      <c r="E252" s="15">
+        <v>5051064345</v>
+      </c>
+      <c r="F252" s="15">
+        <v>5051053774</v>
+      </c>
       <c r="G252" s="15"/>
       <c r="H252" s="15"/>
       <c r="I252" s="15"/>
@@ -8339,7 +8375,9 @@
       <c r="B253" s="13">
         <v>2449975997</v>
       </c>
-      <c r="C253" s="15"/>
+      <c r="C253" s="15">
+        <v>4927493679</v>
+      </c>
       <c r="D253" s="15"/>
       <c r="E253" s="15"/>
       <c r="F253" s="15"/>
@@ -8366,9 +8404,15 @@
       <c r="B254" s="13">
         <v>2449977489</v>
       </c>
-      <c r="C254" s="15"/>
-      <c r="D254" s="15"/>
-      <c r="E254" s="15"/>
+      <c r="C254" s="15">
+        <v>4850250121</v>
+      </c>
+      <c r="D254" s="15">
+        <v>4850285957</v>
+      </c>
+      <c r="E254" s="15">
+        <v>5876617261</v>
+      </c>
       <c r="F254" s="15"/>
       <c r="G254" s="15"/>
       <c r="H254" s="15"/>
@@ -8393,11 +8437,21 @@
       <c r="B255" s="13">
         <v>2449979646</v>
       </c>
-      <c r="C255" s="15"/>
-      <c r="D255" s="15"/>
-      <c r="E255" s="15"/>
-      <c r="F255" s="15"/>
-      <c r="G255" s="15"/>
+      <c r="C255" s="15">
+        <v>4850254194</v>
+      </c>
+      <c r="D255" s="15">
+        <v>4850265345</v>
+      </c>
+      <c r="E255" s="15">
+        <v>4860282968</v>
+      </c>
+      <c r="F255" s="15">
+        <v>4927492131</v>
+      </c>
+      <c r="G255" s="15">
+        <v>5643125807</v>
+      </c>
       <c r="H255" s="15"/>
       <c r="I255" s="15"/>
       <c r="J255" s="15"/>
@@ -8420,10 +8474,18 @@
       <c r="B256" s="13">
         <v>2449977972</v>
       </c>
-      <c r="C256" s="16"/>
-      <c r="D256" s="15"/>
-      <c r="E256" s="15"/>
-      <c r="F256" s="15"/>
+      <c r="C256" s="16">
+        <v>4927493514</v>
+      </c>
+      <c r="D256" s="15">
+        <v>5534875329</v>
+      </c>
+      <c r="E256" s="15">
+        <v>4850259702</v>
+      </c>
+      <c r="F256" s="15">
+        <v>4850263574</v>
+      </c>
       <c r="G256" s="15"/>
       <c r="H256" s="15"/>
       <c r="I256" s="15"/>
@@ -8447,8 +8509,12 @@
       <c r="B257" s="13">
         <v>2449976830</v>
       </c>
-      <c r="C257" s="15"/>
-      <c r="D257" s="15"/>
+      <c r="C257" s="15">
+        <v>4850254382</v>
+      </c>
+      <c r="D257" s="15">
+        <v>4927493905</v>
+      </c>
       <c r="E257" s="15"/>
       <c r="F257" s="15"/>
       <c r="G257" s="15"/>
@@ -8501,8 +8567,12 @@
       <c r="B259" s="13">
         <v>2449978096</v>
       </c>
-      <c r="C259" s="15"/>
-      <c r="D259" s="15"/>
+      <c r="C259" s="15">
+        <v>5868083016</v>
+      </c>
+      <c r="D259" s="15">
+        <v>5563955559</v>
+      </c>
       <c r="E259" s="15"/>
       <c r="F259" s="15"/>
       <c r="G259" s="15"/>
@@ -8528,10 +8598,18 @@
       <c r="B260" s="13">
         <v>2449977830</v>
       </c>
-      <c r="C260" s="15"/>
-      <c r="D260" s="15"/>
-      <c r="E260" s="15"/>
-      <c r="F260" s="15"/>
+      <c r="C260" s="15">
+        <v>4927494260</v>
+      </c>
+      <c r="D260" s="15">
+        <v>5868083357</v>
+      </c>
+      <c r="E260" s="15">
+        <v>5563954952</v>
+      </c>
+      <c r="F260" s="15">
+        <v>5682481768</v>
+      </c>
       <c r="G260" s="15"/>
       <c r="H260" s="15"/>
       <c r="I260" s="15"/>
@@ -8555,8 +8633,12 @@
       <c r="B261" s="13">
         <v>2449979383</v>
       </c>
-      <c r="C261" s="16"/>
-      <c r="D261" s="15"/>
+      <c r="C261" s="16">
+        <v>4927495342</v>
+      </c>
+      <c r="D261" s="15">
+        <v>5563958107</v>
+      </c>
       <c r="E261" s="15"/>
       <c r="F261" s="15"/>
       <c r="G261" s="15"/>
@@ -8582,9 +8664,15 @@
       <c r="B262" s="13">
         <v>2449977151</v>
       </c>
-      <c r="C262" s="15"/>
-      <c r="D262" s="15"/>
-      <c r="E262" s="15"/>
+      <c r="C262" s="15">
+        <v>5868025182</v>
+      </c>
+      <c r="D262" s="15">
+        <v>5868025782</v>
+      </c>
+      <c r="E262" s="15">
+        <v>5563961243</v>
+      </c>
       <c r="F262" s="15"/>
       <c r="G262" s="15"/>
       <c r="H262" s="15"/>
@@ -8609,8 +8697,12 @@
       <c r="B263" s="13">
         <v>2449977812</v>
       </c>
-      <c r="C263" s="16"/>
-      <c r="D263" s="15"/>
+      <c r="C263" s="16">
+        <v>4860284593</v>
+      </c>
+      <c r="D263" s="15">
+        <v>5563956295</v>
+      </c>
       <c r="E263" s="15"/>
       <c r="F263" s="15"/>
       <c r="G263" s="15"/>
@@ -8636,11 +8728,21 @@
       <c r="B264" s="13">
         <v>2449977848</v>
       </c>
-      <c r="C264" s="15"/>
-      <c r="D264" s="15"/>
-      <c r="E264" s="15"/>
-      <c r="F264" s="15"/>
-      <c r="G264" s="15"/>
+      <c r="C264" s="15">
+        <v>4860278760</v>
+      </c>
+      <c r="D264" s="15">
+        <v>5051048805</v>
+      </c>
+      <c r="E264" s="15">
+        <v>5167590180</v>
+      </c>
+      <c r="F264" s="15">
+        <v>5563961820</v>
+      </c>
+      <c r="G264" s="15">
+        <v>5591605465</v>
+      </c>
       <c r="H264" s="15"/>
       <c r="I264" s="15"/>
       <c r="J264" s="15"/>
@@ -8825,10 +8927,18 @@
       <c r="B271" s="13">
         <v>2449976986</v>
       </c>
-      <c r="C271" s="15"/>
-      <c r="D271" s="15"/>
-      <c r="E271" s="15"/>
-      <c r="F271" s="15"/>
+      <c r="C271" s="15">
+        <v>5051072453</v>
+      </c>
+      <c r="D271" s="15">
+        <v>5876578431</v>
+      </c>
+      <c r="E271" s="15">
+        <v>5876580808</v>
+      </c>
+      <c r="F271" s="15">
+        <v>5563954738</v>
+      </c>
       <c r="G271" s="15"/>
       <c r="H271" s="15"/>
       <c r="I271" s="15"/>
@@ -8852,8 +8962,12 @@
       <c r="B272" s="13">
         <v>2449979595</v>
       </c>
-      <c r="C272" s="15"/>
-      <c r="D272" s="15"/>
+      <c r="C272" s="15">
+        <v>4860284687</v>
+      </c>
+      <c r="D272" s="15">
+        <v>4927495338</v>
+      </c>
       <c r="E272" s="15"/>
       <c r="F272" s="15"/>
       <c r="G272" s="15"/>
@@ -8879,10 +8993,18 @@
       <c r="B273" s="13">
         <v>2449977394</v>
       </c>
-      <c r="C273" s="15"/>
-      <c r="D273" s="15"/>
-      <c r="E273" s="15"/>
-      <c r="F273" s="15"/>
+      <c r="C273" s="15">
+        <v>4860281785</v>
+      </c>
+      <c r="D273" s="15">
+        <v>4927493213</v>
+      </c>
+      <c r="E273" s="15">
+        <v>5876581017</v>
+      </c>
+      <c r="F273" s="15">
+        <v>5876581219</v>
+      </c>
       <c r="G273" s="15"/>
       <c r="H273" s="15"/>
       <c r="I273" s="15"/>
@@ -8933,11 +9055,21 @@
       <c r="B275" s="13">
         <v>2449977131</v>
       </c>
-      <c r="C275" s="15"/>
-      <c r="D275" s="15"/>
-      <c r="E275" s="15"/>
-      <c r="F275" s="15"/>
-      <c r="G275" s="15"/>
+      <c r="C275" s="15">
+        <v>5868030126</v>
+      </c>
+      <c r="D275" s="15">
+        <v>5868030966</v>
+      </c>
+      <c r="E275" s="15">
+        <v>5563955460</v>
+      </c>
+      <c r="F275" s="15">
+        <v>5682480813</v>
+      </c>
+      <c r="G275" s="15">
+        <v>5640688090</v>
+      </c>
       <c r="H275" s="15"/>
       <c r="I275" s="15"/>
       <c r="J275" s="15"/>
@@ -8960,9 +9092,15 @@
       <c r="B276" s="13">
         <v>2449977197</v>
       </c>
-      <c r="C276" s="15"/>
-      <c r="D276" s="15"/>
-      <c r="E276" s="15"/>
+      <c r="C276" s="15">
+        <v>5526236946</v>
+      </c>
+      <c r="D276" s="15">
+        <v>4850256119</v>
+      </c>
+      <c r="E276" s="15">
+        <v>4927492397</v>
+      </c>
       <c r="F276" s="15"/>
       <c r="G276" s="15"/>
       <c r="H276" s="15"/>
@@ -9014,8 +9152,12 @@
       <c r="B278" s="13">
         <v>2449977090</v>
       </c>
-      <c r="C278" s="15"/>
-      <c r="D278" s="15"/>
+      <c r="C278" s="15">
+        <v>4927491875</v>
+      </c>
+      <c r="D278" s="15">
+        <v>5876614967</v>
+      </c>
       <c r="E278" s="15"/>
       <c r="F278" s="15"/>
       <c r="G278" s="15"/>
@@ -9041,10 +9183,18 @@
       <c r="B279" s="13">
         <v>2449977863</v>
       </c>
-      <c r="C279" s="15"/>
-      <c r="D279" s="15"/>
-      <c r="E279" s="15"/>
-      <c r="F279" s="15"/>
+      <c r="C279" s="15">
+        <v>4927494198</v>
+      </c>
+      <c r="D279" s="15">
+        <v>4860283040</v>
+      </c>
+      <c r="E279" s="15">
+        <v>5051068883</v>
+      </c>
+      <c r="F279" s="15">
+        <v>5640688760</v>
+      </c>
       <c r="G279" s="15"/>
       <c r="H279" s="15"/>
       <c r="I279" s="15"/>
@@ -9068,8 +9218,12 @@
       <c r="B280" s="13">
         <v>2449977838</v>
       </c>
-      <c r="C280" s="15"/>
-      <c r="D280" s="15"/>
+      <c r="C280" s="15">
+        <v>5960098180</v>
+      </c>
+      <c r="D280" s="15">
+        <v>5563962605</v>
+      </c>
       <c r="E280" s="15"/>
       <c r="F280" s="15"/>
       <c r="G280" s="15"/>
@@ -9095,10 +9249,18 @@
       <c r="B281" s="13">
         <v>2449977504</v>
       </c>
-      <c r="C281" s="15"/>
-      <c r="D281" s="15"/>
-      <c r="E281" s="15"/>
-      <c r="F281" s="15"/>
+      <c r="C281" s="15">
+        <v>5051050320</v>
+      </c>
+      <c r="D281" s="15">
+        <v>5868040581</v>
+      </c>
+      <c r="E281" s="15">
+        <v>5868039742</v>
+      </c>
+      <c r="F281" s="15">
+        <v>5563957693</v>
+      </c>
       <c r="G281" s="15"/>
       <c r="H281" s="15"/>
       <c r="I281" s="15"/>
@@ -9176,9 +9338,15 @@
       <c r="B284" s="13">
         <v>2449978809</v>
       </c>
-      <c r="C284" s="15"/>
-      <c r="D284" s="15"/>
-      <c r="E284" s="15"/>
+      <c r="C284" s="15">
+        <v>5876580109</v>
+      </c>
+      <c r="D284" s="15">
+        <v>5876581359</v>
+      </c>
+      <c r="E284" s="15">
+        <v>5563958517</v>
+      </c>
       <c r="F284" s="15"/>
       <c r="G284" s="15"/>
       <c r="H284" s="15"/>
@@ -9260,12 +9428,8 @@
       <c r="C287" s="15"/>
       <c r="D287" s="15"/>
       <c r="E287" s="15"/>
-      <c r="F287" s="15">
-        <v>4927494502</v>
-      </c>
-      <c r="G287" s="15">
-        <v>4850287138</v>
-      </c>
+      <c r="F287" s="15"/>
+      <c r="G287" s="15"/>
       <c r="H287" s="15"/>
       <c r="I287" s="15"/>
       <c r="J287" s="15"/>
@@ -9288,12 +9452,8 @@
       <c r="B288" s="13">
         <v>2474254088</v>
       </c>
-      <c r="C288" s="15">
-        <v>4860781322</v>
-      </c>
-      <c r="D288" s="15">
-        <v>5639408257</v>
-      </c>
+      <c r="C288" s="15"/>
+      <c r="D288" s="15"/>
       <c r="E288" s="15"/>
       <c r="F288" s="15"/>
       <c r="G288" s="15"/>
@@ -9319,12 +9479,8 @@
       <c r="B289" s="13">
         <v>2474251681</v>
       </c>
-      <c r="C289" s="15">
-        <v>4860783324</v>
-      </c>
-      <c r="D289" s="15">
-        <v>5639409136</v>
-      </c>
+      <c r="C289" s="15"/>
+      <c r="D289" s="15"/>
       <c r="E289" s="15"/>
       <c r="F289" s="15"/>
       <c r="G289" s="15"/>
@@ -9350,15 +9506,9 @@
       <c r="B290" s="13">
         <v>2474254458</v>
       </c>
-      <c r="C290" s="15">
-        <v>5551347187</v>
-      </c>
-      <c r="D290" s="15">
-        <v>4860782451</v>
-      </c>
-      <c r="E290" s="15">
-        <v>5639403045</v>
-      </c>
+      <c r="C290" s="15"/>
+      <c r="D290" s="15"/>
+      <c r="E290" s="15"/>
       <c r="F290" s="15"/>
       <c r="G290" s="15"/>
       <c r="H290" s="15"/>
@@ -9383,9 +9533,7 @@
       <c r="B291" s="13">
         <v>2474254911</v>
       </c>
-      <c r="C291" s="15">
-        <v>4860778829</v>
-      </c>
+      <c r="C291" s="15"/>
       <c r="D291" s="15"/>
       <c r="E291" s="15"/>
       <c r="F291" s="15"/>
@@ -9412,9 +9560,7 @@
       <c r="B292" s="13">
         <v>2474252885</v>
       </c>
-      <c r="C292" s="15">
-        <v>4860786349</v>
-      </c>
+      <c r="C292" s="15"/>
       <c r="D292" s="15"/>
       <c r="E292" s="15"/>
       <c r="F292" s="15"/>
@@ -9441,9 +9587,7 @@
       <c r="B293" s="13">
         <v>2474252719</v>
       </c>
-      <c r="C293" s="15">
-        <v>4860781569</v>
-      </c>
+      <c r="C293" s="15"/>
       <c r="D293" s="15"/>
       <c r="E293" s="15"/>
       <c r="F293" s="15"/>
@@ -9470,9 +9614,7 @@
       <c r="B294" s="13">
         <v>2474252861</v>
       </c>
-      <c r="C294" s="16">
-        <v>4860778164</v>
-      </c>
+      <c r="C294" s="16"/>
       <c r="D294" s="15"/>
       <c r="E294" s="15"/>
       <c r="F294" s="15"/>
@@ -9499,12 +9641,8 @@
       <c r="B295" s="13">
         <v>2474254639</v>
       </c>
-      <c r="C295" s="15">
-        <v>4860778053</v>
-      </c>
-      <c r="D295" s="15">
-        <v>5639404086</v>
-      </c>
+      <c r="C295" s="15"/>
+      <c r="D295" s="15"/>
       <c r="E295" s="15"/>
       <c r="F295" s="15"/>
       <c r="G295" s="15"/>
@@ -9530,12 +9668,8 @@
       <c r="B296" s="13">
         <v>2474256003</v>
       </c>
-      <c r="C296" s="15">
-        <v>4860784591</v>
-      </c>
-      <c r="D296" s="15">
-        <v>5639404077</v>
-      </c>
+      <c r="C296" s="15"/>
+      <c r="D296" s="15"/>
       <c r="E296" s="15"/>
       <c r="F296" s="15"/>
       <c r="G296" s="15"/>
@@ -9561,9 +9695,7 @@
       <c r="B297" s="13">
         <v>2474254390</v>
       </c>
-      <c r="C297" s="15">
-        <v>4860786343</v>
-      </c>
+      <c r="C297" s="15"/>
       <c r="D297" s="15"/>
       <c r="E297" s="15"/>
       <c r="F297" s="15"/>
@@ -9590,9 +9722,7 @@
       <c r="B298" s="13">
         <v>2474254998</v>
       </c>
-      <c r="C298" s="15">
-        <v>4860784687</v>
-      </c>
+      <c r="C298" s="15"/>
       <c r="D298" s="15"/>
       <c r="E298" s="15"/>
       <c r="F298" s="15"/>
@@ -9890,7 +10020,7 @@
         <v>2474253289</v>
       </c>
       <c r="C309" s="15">
-        <v>4860788243</v>
+        <v>5639403097</v>
       </c>
       <c r="D309" s="15"/>
       <c r="E309" s="15"/>
@@ -9919,7 +10049,7 @@
         <v>2474252601</v>
       </c>
       <c r="C310" s="15">
-        <v>4860776782</v>
+        <v>5639404537</v>
       </c>
       <c r="D310" s="15"/>
       <c r="E310" s="15"/>
@@ -9948,7 +10078,7 @@
         <v>2474253325</v>
       </c>
       <c r="C311" s="15">
-        <v>4860784752</v>
+        <v>5639404856</v>
       </c>
       <c r="D311" s="15"/>
       <c r="E311" s="15"/>
@@ -9976,9 +10106,7 @@
       <c r="B312" s="13">
         <v>2474253882</v>
       </c>
-      <c r="C312" s="15">
-        <v>5639404280</v>
-      </c>
+      <c r="C312" s="15"/>
       <c r="D312" s="15"/>
       <c r="E312" s="15"/>
       <c r="F312" s="15"/>
@@ -10006,7 +10134,7 @@
         <v>2474253913</v>
       </c>
       <c r="C313" s="15">
-        <v>4860776447</v>
+        <v>5639404135</v>
       </c>
       <c r="D313" s="15"/>
       <c r="E313" s="15"/>
@@ -10034,8 +10162,12 @@
       <c r="B314" s="13">
         <v>2474255236</v>
       </c>
-      <c r="C314" s="15"/>
-      <c r="D314" s="15"/>
+      <c r="C314" s="15">
+        <v>4860785253</v>
+      </c>
+      <c r="D314" s="15">
+        <v>5639402463</v>
+      </c>
       <c r="E314" s="15"/>
       <c r="F314" s="15"/>
       <c r="G314" s="15"/>
@@ -10088,9 +10220,15 @@
       <c r="B316" s="13">
         <v>2474431127</v>
       </c>
-      <c r="C316" s="15"/>
-      <c r="D316" s="15"/>
-      <c r="E316" s="15"/>
+      <c r="C316" s="15">
+        <v>5152013894</v>
+      </c>
+      <c r="D316" s="15">
+        <v>4860783086</v>
+      </c>
+      <c r="E316" s="15">
+        <v>5639405153</v>
+      </c>
       <c r="F316" s="15"/>
       <c r="G316" s="15"/>
       <c r="H316" s="15"/>
@@ -10115,9 +10253,15 @@
       <c r="B317" s="13">
         <v>3691738336</v>
       </c>
-      <c r="C317" s="15"/>
-      <c r="D317" s="15"/>
-      <c r="E317" s="15"/>
+      <c r="C317" s="15">
+        <v>5152576892</v>
+      </c>
+      <c r="D317" s="15">
+        <v>4860343586</v>
+      </c>
+      <c r="E317" s="15">
+        <v>4860347463</v>
+      </c>
       <c r="F317" s="15"/>
       <c r="G317" s="15"/>
       <c r="H317" s="15"/>
@@ -10142,9 +10286,15 @@
       <c r="B318" s="13">
         <v>3691841964</v>
       </c>
-      <c r="C318" s="15"/>
-      <c r="D318" s="15"/>
-      <c r="E318" s="15"/>
+      <c r="C318" s="15">
+        <v>4860351060</v>
+      </c>
+      <c r="D318" s="15">
+        <v>4860355743</v>
+      </c>
+      <c r="E318" s="15">
+        <v>4964035357</v>
+      </c>
       <c r="F318" s="15"/>
       <c r="G318" s="15"/>
       <c r="H318" s="15"/>
@@ -10169,12 +10319,24 @@
       <c r="B319" s="13">
         <v>3691844921</v>
       </c>
-      <c r="C319" s="15"/>
-      <c r="D319" s="15"/>
-      <c r="E319" s="15"/>
-      <c r="F319" s="15"/>
-      <c r="G319" s="15"/>
-      <c r="H319" s="15"/>
+      <c r="C319" s="15">
+        <v>5152564836</v>
+      </c>
+      <c r="D319" s="15">
+        <v>4860349465</v>
+      </c>
+      <c r="E319" s="15">
+        <v>4860349569</v>
+      </c>
+      <c r="F319" s="15">
+        <v>4964036218</v>
+      </c>
+      <c r="G319" s="15">
+        <v>5960108906</v>
+      </c>
+      <c r="H319" s="15">
+        <v>5563669139</v>
+      </c>
       <c r="I319" s="15"/>
       <c r="J319" s="15"/>
       <c r="K319" s="15"/>
@@ -10196,10 +10358,18 @@
       <c r="B320" s="13">
         <v>3691842819</v>
       </c>
-      <c r="C320" s="15"/>
-      <c r="D320" s="15"/>
-      <c r="E320" s="15"/>
-      <c r="F320" s="15"/>
+      <c r="C320" s="15">
+        <v>5152533862</v>
+      </c>
+      <c r="D320" s="15">
+        <v>4860336460</v>
+      </c>
+      <c r="E320" s="15">
+        <v>4860344072</v>
+      </c>
+      <c r="F320" s="15">
+        <v>4964033216</v>
+      </c>
       <c r="G320" s="15"/>
       <c r="H320" s="15"/>
       <c r="I320" s="15"/>
@@ -10223,12 +10393,24 @@
       <c r="B321" s="13">
         <v>3691843282</v>
       </c>
-      <c r="C321" s="15"/>
-      <c r="D321" s="15"/>
-      <c r="E321" s="15"/>
-      <c r="F321" s="15"/>
-      <c r="G321" s="15"/>
-      <c r="H321" s="15"/>
+      <c r="C321" s="15">
+        <v>5152592577</v>
+      </c>
+      <c r="D321" s="15">
+        <v>5526281268</v>
+      </c>
+      <c r="E321" s="15">
+        <v>4860352753</v>
+      </c>
+      <c r="F321" s="15">
+        <v>4860354935</v>
+      </c>
+      <c r="G321" s="15">
+        <v>4964036697</v>
+      </c>
+      <c r="H321" s="15">
+        <v>5960096898</v>
+      </c>
       <c r="I321" s="15"/>
       <c r="J321" s="15"/>
       <c r="K321" s="15"/>
@@ -10250,9 +10432,15 @@
       <c r="B322" s="13">
         <v>3691843233</v>
       </c>
-      <c r="C322" s="15"/>
-      <c r="D322" s="15"/>
-      <c r="E322" s="15"/>
+      <c r="C322" s="15">
+        <v>5535489468</v>
+      </c>
+      <c r="D322" s="15">
+        <v>4860338782</v>
+      </c>
+      <c r="E322" s="15">
+        <v>4964036466</v>
+      </c>
       <c r="F322" s="15"/>
       <c r="G322" s="15"/>
       <c r="H322" s="15"/>
@@ -10277,9 +10465,15 @@
       <c r="B323" s="13">
         <v>3691843824</v>
       </c>
-      <c r="C323" s="15"/>
-      <c r="D323" s="15"/>
-      <c r="E323" s="15"/>
+      <c r="C323" s="15">
+        <v>5152694641</v>
+      </c>
+      <c r="D323" s="15">
+        <v>5526466609</v>
+      </c>
+      <c r="E323" s="15">
+        <v>4860353279</v>
+      </c>
       <c r="F323" s="15"/>
       <c r="G323" s="15"/>
       <c r="H323" s="15"/>
@@ -10331,13 +10525,16 @@
       <c r="B325" s="13">
         <v>3691843333</v>
       </c>
-      <c r="C325" s="15"/>
-      <c r="D325" s="15"/>
-      <c r="E325" s="15"/>
+      <c r="C325" s="15">
+        <v>4964036092</v>
+      </c>
+      <c r="D325" s="15">
+        <v>5960100354</v>
+      </c>
+      <c r="E325" s="15">
+        <v>5563667676</v>
+      </c>
       <c r="F325" s="15"/>
-      <c r="G325" s="15"/>
-      <c r="H325" s="15"/>
-      <c r="I325" s="15"/>
       <c r="J325" s="15"/>
       <c r="K325" s="15"/>
       <c r="L325" s="15"/>
@@ -10424,9 +10621,15 @@
       <c r="B328" s="13">
         <v>3691843793</v>
       </c>
-      <c r="C328" s="15"/>
-      <c r="D328" s="15"/>
-      <c r="E328" s="15"/>
+      <c r="C328" s="15">
+        <v>5152542788</v>
+      </c>
+      <c r="D328" s="15">
+        <v>5526207109</v>
+      </c>
+      <c r="E328" s="15">
+        <v>4860341482</v>
+      </c>
       <c r="F328" s="15"/>
       <c r="G328" s="15"/>
       <c r="H328" s="15"/>
@@ -10451,9 +10654,15 @@
       <c r="B329" s="13">
         <v>3691844110</v>
       </c>
-      <c r="C329" s="15"/>
-      <c r="D329" s="15"/>
-      <c r="E329" s="15"/>
+      <c r="C329" s="15">
+        <v>5152552045</v>
+      </c>
+      <c r="D329" s="15">
+        <v>4860337452</v>
+      </c>
+      <c r="E329" s="15">
+        <v>4860338862</v>
+      </c>
       <c r="F329" s="15"/>
       <c r="G329" s="15"/>
       <c r="H329" s="15"/>
@@ -10478,9 +10687,15 @@
       <c r="B330" s="13">
         <v>3691844929</v>
       </c>
-      <c r="C330" s="15"/>
-      <c r="D330" s="15"/>
-      <c r="E330" s="15"/>
+      <c r="C330" s="15">
+        <v>5152653667</v>
+      </c>
+      <c r="D330" s="15">
+        <v>5535510237</v>
+      </c>
+      <c r="E330" s="15">
+        <v>4860352426</v>
+      </c>
       <c r="F330" s="15"/>
       <c r="G330" s="15"/>
       <c r="H330" s="15"/>
@@ -10505,11 +10720,21 @@
       <c r="B331" s="13">
         <v>3691844839</v>
       </c>
-      <c r="C331" s="15"/>
-      <c r="D331" s="15"/>
-      <c r="E331" s="15"/>
-      <c r="F331" s="15"/>
-      <c r="G331" s="15"/>
+      <c r="C331" s="15">
+        <v>5152606344</v>
+      </c>
+      <c r="D331" s="15">
+        <v>5535536654</v>
+      </c>
+      <c r="E331" s="15">
+        <v>5152605404</v>
+      </c>
+      <c r="F331" s="15">
+        <v>4860335668</v>
+      </c>
+      <c r="G331" s="15">
+        <v>4860338275</v>
+      </c>
       <c r="H331" s="15"/>
       <c r="I331" s="15"/>
       <c r="J331" s="15"/>
@@ -10532,10 +10757,18 @@
       <c r="B332" s="13">
         <v>3691843907</v>
       </c>
-      <c r="C332" s="16"/>
-      <c r="D332" s="15"/>
-      <c r="E332" s="15"/>
-      <c r="F332" s="15"/>
+      <c r="C332" s="16">
+        <v>5152564128</v>
+      </c>
+      <c r="D332" s="15">
+        <v>4860349462</v>
+      </c>
+      <c r="E332" s="15">
+        <v>4860350149</v>
+      </c>
+      <c r="F332" s="15">
+        <v>4964035035</v>
+      </c>
       <c r="G332" s="15"/>
       <c r="H332" s="15"/>
       <c r="I332" s="15"/>
@@ -12486,13 +12719,27 @@
       <c r="B394" s="13">
         <v>3697504996</v>
       </c>
-      <c r="C394" s="15"/>
-      <c r="D394" s="15"/>
-      <c r="E394" s="15"/>
-      <c r="F394" s="15"/>
-      <c r="G394" s="15"/>
-      <c r="H394" s="15"/>
-      <c r="I394" s="15"/>
+      <c r="C394" s="15">
+        <v>5152547543</v>
+      </c>
+      <c r="D394" s="15">
+        <v>5534875016</v>
+      </c>
+      <c r="E394" s="15">
+        <v>5152635814</v>
+      </c>
+      <c r="F394" s="15">
+        <v>4860351913</v>
+      </c>
+      <c r="G394" s="15">
+        <v>4964035409</v>
+      </c>
+      <c r="H394" s="15">
+        <v>5960096320</v>
+      </c>
+      <c r="I394" s="15">
+        <v>5563682254</v>
+      </c>
       <c r="J394" s="15"/>
       <c r="K394" s="15"/>
       <c r="L394" s="15"/>
@@ -12513,11 +12760,21 @@
       <c r="B395" s="13">
         <v>3697504363</v>
       </c>
-      <c r="C395" s="16"/>
-      <c r="D395" s="15"/>
-      <c r="E395" s="15"/>
-      <c r="F395" s="15"/>
-      <c r="G395" s="15"/>
+      <c r="C395" s="16">
+        <v>5152666473</v>
+      </c>
+      <c r="D395" s="15">
+        <v>5526215018</v>
+      </c>
+      <c r="E395" s="15">
+        <v>4860355922</v>
+      </c>
+      <c r="F395" s="15">
+        <v>5960099989</v>
+      </c>
+      <c r="G395" s="15">
+        <v>5563670332</v>
+      </c>
       <c r="H395" s="15"/>
       <c r="I395" s="15"/>
       <c r="J395" s="15"/>
@@ -12540,8 +12797,12 @@
       <c r="B396" s="13">
         <v>3697505978</v>
       </c>
-      <c r="C396" s="15"/>
-      <c r="D396" s="15"/>
+      <c r="C396" s="15">
+        <v>5152544007</v>
+      </c>
+      <c r="D396" s="15">
+        <v>5960098646</v>
+      </c>
       <c r="E396" s="15"/>
       <c r="F396" s="15"/>
       <c r="G396" s="15"/>
@@ -12567,9 +12828,15 @@
       <c r="B397" s="13">
         <v>3697504998</v>
       </c>
-      <c r="C397" s="15"/>
-      <c r="D397" s="15"/>
-      <c r="E397" s="15"/>
+      <c r="C397" s="15">
+        <v>5152544942</v>
+      </c>
+      <c r="D397" s="15">
+        <v>5960097951</v>
+      </c>
+      <c r="E397" s="15">
+        <v>5563678263</v>
+      </c>
       <c r="F397" s="15"/>
       <c r="G397" s="15"/>
       <c r="H397" s="15"/>
@@ -12594,9 +12861,15 @@
       <c r="B398" s="13">
         <v>3697504814</v>
       </c>
-      <c r="C398" s="15"/>
-      <c r="D398" s="15"/>
-      <c r="E398" s="15"/>
+      <c r="C398" s="15">
+        <v>5526507678</v>
+      </c>
+      <c r="D398" s="15">
+        <v>5960097051</v>
+      </c>
+      <c r="E398" s="15">
+        <v>5563676577</v>
+      </c>
       <c r="F398" s="15"/>
       <c r="G398" s="15"/>
       <c r="H398" s="15"/>
@@ -12621,10 +12894,18 @@
       <c r="B399" s="13">
         <v>3697505764</v>
       </c>
-      <c r="C399" s="15"/>
-      <c r="D399" s="15"/>
-      <c r="E399" s="15"/>
-      <c r="F399" s="15"/>
+      <c r="C399" s="15">
+        <v>5534886498</v>
+      </c>
+      <c r="D399" s="15">
+        <v>4860341632</v>
+      </c>
+      <c r="E399" s="15">
+        <v>5960099631</v>
+      </c>
+      <c r="F399" s="15">
+        <v>5563677097</v>
+      </c>
       <c r="G399" s="15"/>
       <c r="H399" s="15"/>
       <c r="I399" s="15"/>
@@ -12648,8 +12929,12 @@
       <c r="B400" s="13">
         <v>3697506004</v>
       </c>
-      <c r="C400" s="15"/>
-      <c r="D400" s="15"/>
+      <c r="C400" s="15">
+        <v>5551065875</v>
+      </c>
+      <c r="D400" s="15">
+        <v>5960098689</v>
+      </c>
       <c r="E400" s="15"/>
       <c r="F400" s="15"/>
       <c r="G400" s="15"/>
@@ -12675,7 +12960,9 @@
       <c r="B401" s="13">
         <v>3697505436</v>
       </c>
-      <c r="C401" s="15"/>
+      <c r="C401" s="15">
+        <v>5960094846</v>
+      </c>
       <c r="D401" s="15"/>
       <c r="E401" s="15"/>
       <c r="F401" s="15"/>
@@ -12729,9 +13016,15 @@
       <c r="B403" s="13">
         <v>3697505575</v>
       </c>
-      <c r="C403" s="15"/>
-      <c r="D403" s="15"/>
-      <c r="E403" s="15"/>
+      <c r="C403" s="15">
+        <v>5535033445</v>
+      </c>
+      <c r="D403" s="15">
+        <v>5960102387</v>
+      </c>
+      <c r="E403" s="15">
+        <v>5563676115</v>
+      </c>
       <c r="F403" s="15"/>
       <c r="G403" s="15"/>
       <c r="H403" s="15"/>
@@ -12756,8 +13049,12 @@
       <c r="B404" s="13">
         <v>3701081855</v>
       </c>
-      <c r="C404" s="15"/>
-      <c r="D404" s="15"/>
+      <c r="C404" s="15">
+        <v>5960100802</v>
+      </c>
+      <c r="D404" s="15">
+        <v>5563677766</v>
+      </c>
       <c r="E404" s="15"/>
       <c r="F404" s="15"/>
       <c r="G404" s="15"/>

--- a/воры/Amazing_Pics_SKU ALL_06.10.2026.xlsx
+++ b/воры/Amazing_Pics_SKU ALL_06.10.2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\воры\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A4DB10-8233-4F3A-92AB-9A2B044EBE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D2CC68-220B-44C2-BB8B-A5F5E460136E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5920,10 +5920,18 @@
       <c r="B160" s="13">
         <v>1626838871</v>
       </c>
-      <c r="C160" s="15"/>
-      <c r="D160" s="15"/>
-      <c r="E160" s="15"/>
-      <c r="F160" s="15"/>
+      <c r="C160" s="15">
+        <v>4860264810</v>
+      </c>
+      <c r="D160" s="15">
+        <v>4890100126</v>
+      </c>
+      <c r="E160" s="15">
+        <v>4890110820</v>
+      </c>
+      <c r="F160" s="15">
+        <v>5563962713</v>
+      </c>
       <c r="G160" s="15"/>
       <c r="H160" s="15"/>
       <c r="I160" s="15"/>
@@ -5946,10 +5954,18 @@
       <c r="B161" s="13">
         <v>1626838489</v>
       </c>
-      <c r="C161" s="15"/>
-      <c r="D161" s="15"/>
-      <c r="E161" s="15"/>
-      <c r="F161" s="15"/>
+      <c r="C161" s="15">
+        <v>5259992780</v>
+      </c>
+      <c r="D161" s="15">
+        <v>5868082769</v>
+      </c>
+      <c r="E161" s="15">
+        <v>5868083327</v>
+      </c>
+      <c r="F161" s="15">
+        <v>5563974534</v>
+      </c>
       <c r="G161" s="15"/>
       <c r="H161" s="15"/>
       <c r="I161" s="15"/>
@@ -5972,7 +5988,9 @@
       <c r="B162" s="13">
         <v>1626838716</v>
       </c>
-      <c r="C162" s="15"/>
+      <c r="C162" s="15">
+        <v>5563979496</v>
+      </c>
       <c r="D162" s="15"/>
       <c r="E162" s="15"/>
       <c r="F162" s="15"/>
@@ -5998,9 +6016,15 @@
       <c r="B163" s="13">
         <v>1626838872</v>
       </c>
-      <c r="C163" s="15"/>
-      <c r="D163" s="15"/>
-      <c r="E163" s="15"/>
+      <c r="C163" s="15">
+        <v>4890086083</v>
+      </c>
+      <c r="D163" s="15">
+        <v>4890086482</v>
+      </c>
+      <c r="E163" s="15">
+        <v>5563977704</v>
+      </c>
       <c r="F163" s="15"/>
       <c r="G163" s="15"/>
       <c r="H163" s="15"/>
@@ -6024,9 +6048,15 @@
       <c r="B164" s="13">
         <v>1626838767</v>
       </c>
-      <c r="C164" s="15"/>
-      <c r="D164" s="15"/>
-      <c r="E164" s="15"/>
+      <c r="C164" s="15">
+        <v>4890098085</v>
+      </c>
+      <c r="D164" s="15">
+        <v>5868067377</v>
+      </c>
+      <c r="E164" s="15">
+        <v>5563976331</v>
+      </c>
       <c r="F164" s="15"/>
       <c r="G164" s="15"/>
       <c r="H164" s="15"/>
@@ -6050,10 +6080,18 @@
       <c r="B165" s="13">
         <v>1626838847</v>
       </c>
-      <c r="C165" s="15"/>
-      <c r="D165" s="15"/>
-      <c r="E165" s="15"/>
-      <c r="F165" s="15"/>
+      <c r="C165" s="15">
+        <v>4890102327</v>
+      </c>
+      <c r="D165" s="15">
+        <v>5876579984</v>
+      </c>
+      <c r="E165" s="15">
+        <v>5876581229</v>
+      </c>
+      <c r="F165" s="15">
+        <v>5563963226</v>
+      </c>
       <c r="G165" s="15"/>
       <c r="H165" s="15"/>
       <c r="I165" s="15"/>
@@ -6210,8 +6248,6 @@
       <c r="D171" s="15"/>
       <c r="E171" s="15"/>
       <c r="F171" s="15"/>
-      <c r="G171" s="15"/>
-      <c r="H171" s="15"/>
       <c r="I171" s="15"/>
       <c r="J171" s="15"/>
       <c r="K171" s="15"/>
@@ -6232,10 +6268,18 @@
       <c r="B172" s="13">
         <v>1738651525</v>
       </c>
-      <c r="C172" s="15"/>
-      <c r="D172" s="15"/>
-      <c r="E172" s="15"/>
-      <c r="F172" s="15"/>
+      <c r="C172" s="15">
+        <v>4890086750</v>
+      </c>
+      <c r="D172" s="15">
+        <v>5019508589</v>
+      </c>
+      <c r="E172" s="15">
+        <v>5563975017</v>
+      </c>
+      <c r="F172" s="15">
+        <v>5739124078</v>
+      </c>
       <c r="G172" s="15"/>
       <c r="H172" s="15"/>
       <c r="I172" s="15"/>
@@ -6258,9 +6302,15 @@
       <c r="B173" s="13">
         <v>1738652819</v>
       </c>
-      <c r="C173" s="15"/>
-      <c r="D173" s="15"/>
-      <c r="E173" s="15"/>
+      <c r="C173" s="15">
+        <v>4850064636</v>
+      </c>
+      <c r="D173" s="15">
+        <v>4890103488</v>
+      </c>
+      <c r="E173" s="15">
+        <v>5876597180</v>
+      </c>
       <c r="F173" s="15"/>
       <c r="G173" s="15"/>
       <c r="H173" s="15"/>
@@ -6284,10 +6334,18 @@
       <c r="B174" s="13">
         <v>1738652561</v>
       </c>
-      <c r="C174" s="15"/>
-      <c r="D174" s="15"/>
-      <c r="E174" s="15"/>
-      <c r="F174" s="15"/>
+      <c r="C174" s="15">
+        <v>4964346222</v>
+      </c>
+      <c r="D174" s="15">
+        <v>4850067005</v>
+      </c>
+      <c r="E174" s="15">
+        <v>4890089832</v>
+      </c>
+      <c r="F174" s="15">
+        <v>4890096142</v>
+      </c>
       <c r="G174" s="15"/>
       <c r="H174" s="15"/>
       <c r="I174" s="15"/>
@@ -6310,11 +6368,21 @@
       <c r="B175" s="13">
         <v>1738651871</v>
       </c>
-      <c r="C175" s="15"/>
-      <c r="D175" s="15"/>
-      <c r="E175" s="15"/>
-      <c r="F175" s="15"/>
-      <c r="G175" s="15"/>
+      <c r="C175" s="15">
+        <v>4964343602</v>
+      </c>
+      <c r="D175" s="15">
+        <v>4860259940</v>
+      </c>
+      <c r="E175" s="15">
+        <v>4890090020</v>
+      </c>
+      <c r="F175" s="15">
+        <v>4890091507</v>
+      </c>
+      <c r="G175" s="15">
+        <v>4890091507</v>
+      </c>
       <c r="H175" s="15"/>
       <c r="I175" s="15"/>
       <c r="J175" s="15"/>
@@ -6336,9 +6404,15 @@
       <c r="B176" s="13">
         <v>1738652486</v>
       </c>
-      <c r="C176" s="15"/>
-      <c r="D176" s="15"/>
-      <c r="E176" s="15"/>
+      <c r="C176" s="15">
+        <v>5868092998</v>
+      </c>
+      <c r="D176" s="15">
+        <v>5868090530</v>
+      </c>
+      <c r="E176" s="15">
+        <v>5019794884</v>
+      </c>
       <c r="F176" s="15"/>
       <c r="G176" s="15"/>
       <c r="H176" s="15"/>
@@ -6362,13 +6436,22 @@
       <c r="B177" s="13">
         <v>1738652399</v>
       </c>
-      <c r="C177" s="15"/>
-      <c r="D177" s="15"/>
-      <c r="E177" s="15"/>
-      <c r="F177" s="15"/>
-      <c r="G177" s="15"/>
+      <c r="C177" s="15">
+        <v>4860258801</v>
+      </c>
+      <c r="D177" s="15">
+        <v>4890091217</v>
+      </c>
+      <c r="E177" s="15">
+        <v>5019506258</v>
+      </c>
+      <c r="F177" s="15">
+        <v>5563973614</v>
+      </c>
+      <c r="G177" s="15">
+        <v>5739123193</v>
+      </c>
       <c r="H177" s="15"/>
-      <c r="I177" s="15"/>
       <c r="J177" s="15"/>
       <c r="K177" s="15"/>
       <c r="L177" s="15"/>
@@ -6388,13 +6471,27 @@
       <c r="B178" s="13">
         <v>1738651921</v>
       </c>
-      <c r="C178" s="15"/>
-      <c r="D178" s="15"/>
-      <c r="E178" s="15"/>
-      <c r="F178" s="15"/>
-      <c r="G178" s="15"/>
-      <c r="H178" s="15"/>
-      <c r="I178" s="15"/>
+      <c r="C178" s="15">
+        <v>4964346295</v>
+      </c>
+      <c r="D178" s="15">
+        <v>4890106703</v>
+      </c>
+      <c r="E178" s="15">
+        <v>4890089950</v>
+      </c>
+      <c r="F178" s="15">
+        <v>5876580455</v>
+      </c>
+      <c r="G178" s="3">
+        <v>5876580627</v>
+      </c>
+      <c r="H178" s="3">
+        <v>5020352125</v>
+      </c>
+      <c r="I178" s="3">
+        <v>5739123681</v>
+      </c>
       <c r="J178" s="15"/>
       <c r="K178" s="15"/>
       <c r="L178" s="15"/>
@@ -6414,8 +6511,12 @@
       <c r="B179" s="13">
         <v>1738651917</v>
       </c>
-      <c r="C179" s="15"/>
-      <c r="D179" s="15"/>
+      <c r="C179" s="15">
+        <v>4860263661</v>
+      </c>
+      <c r="D179" s="15">
+        <v>4890095617</v>
+      </c>
       <c r="E179" s="15"/>
       <c r="F179" s="15"/>
       <c r="G179" s="15"/>
@@ -6440,9 +6541,15 @@
       <c r="B180" s="13">
         <v>1738651829</v>
       </c>
-      <c r="C180" s="15"/>
-      <c r="D180" s="15"/>
-      <c r="E180" s="15"/>
+      <c r="C180" s="15">
+        <v>4860257084</v>
+      </c>
+      <c r="D180" s="15">
+        <v>4860259708</v>
+      </c>
+      <c r="E180" s="15">
+        <v>4964343440</v>
+      </c>
       <c r="F180" s="15"/>
       <c r="G180" s="15"/>
       <c r="H180" s="15"/>
@@ -6466,10 +6573,18 @@
       <c r="B181" s="13">
         <v>1738651613</v>
       </c>
-      <c r="C181" s="15"/>
-      <c r="D181" s="15"/>
-      <c r="E181" s="15"/>
-      <c r="F181" s="15"/>
+      <c r="C181" s="15">
+        <v>4860265354</v>
+      </c>
+      <c r="D181" s="15">
+        <v>4964343453</v>
+      </c>
+      <c r="E181" s="15">
+        <v>4860259863</v>
+      </c>
+      <c r="F181" s="15">
+        <v>4890089760</v>
+      </c>
       <c r="G181" s="15"/>
       <c r="H181" s="15"/>
       <c r="I181" s="15"/>
@@ -6518,9 +6633,15 @@
       <c r="B183" s="13">
         <v>1738651975</v>
       </c>
-      <c r="C183" s="15"/>
-      <c r="D183" s="15"/>
-      <c r="E183" s="15"/>
+      <c r="C183" s="15">
+        <v>4964342505</v>
+      </c>
+      <c r="D183" s="15">
+        <v>4890098879</v>
+      </c>
+      <c r="E183" s="15">
+        <v>5020361857</v>
+      </c>
       <c r="F183" s="15"/>
       <c r="G183" s="15"/>
       <c r="H183" s="15"/>
@@ -6544,10 +6665,18 @@
       <c r="B184" s="13">
         <v>1738652535</v>
       </c>
-      <c r="C184" s="15"/>
-      <c r="D184" s="15"/>
-      <c r="E184" s="15"/>
-      <c r="F184" s="15"/>
+      <c r="C184" s="15">
+        <v>4890089551</v>
+      </c>
+      <c r="D184" s="15">
+        <v>4915322400</v>
+      </c>
+      <c r="E184" s="15">
+        <v>5868056968</v>
+      </c>
+      <c r="F184" s="15">
+        <v>5868053659</v>
+      </c>
       <c r="G184" s="15"/>
       <c r="H184" s="15"/>
       <c r="I184" s="15"/>
@@ -6570,9 +6699,15 @@
       <c r="B185" s="13">
         <v>1738652490</v>
       </c>
-      <c r="C185" s="15"/>
-      <c r="D185" s="15"/>
-      <c r="E185" s="15"/>
+      <c r="C185" s="15">
+        <v>4890095156</v>
+      </c>
+      <c r="D185" s="15">
+        <v>5563970965</v>
+      </c>
+      <c r="E185" s="15">
+        <v>5739122882</v>
+      </c>
       <c r="F185" s="15"/>
       <c r="G185" s="15"/>
       <c r="H185" s="15"/>
@@ -6596,8 +6731,12 @@
       <c r="B186" s="13">
         <v>1738651416</v>
       </c>
-      <c r="C186" s="15"/>
-      <c r="D186" s="15"/>
+      <c r="C186" s="15">
+        <v>4860259602</v>
+      </c>
+      <c r="D186" s="15">
+        <v>4964341621</v>
+      </c>
       <c r="E186" s="15"/>
       <c r="F186" s="15"/>
       <c r="G186" s="15"/>
@@ -6622,10 +6761,18 @@
       <c r="B187" s="13">
         <v>1738652147</v>
       </c>
-      <c r="C187" s="15"/>
-      <c r="D187" s="15"/>
-      <c r="E187" s="15"/>
-      <c r="F187" s="15"/>
+      <c r="C187" s="15">
+        <v>4850057880</v>
+      </c>
+      <c r="D187" s="15">
+        <v>4860256380</v>
+      </c>
+      <c r="E187" s="15">
+        <v>4964345883</v>
+      </c>
+      <c r="F187" s="15">
+        <v>4890108591</v>
+      </c>
       <c r="G187" s="15"/>
       <c r="H187" s="15"/>
       <c r="I187" s="15"/>
@@ -6648,9 +6795,15 @@
       <c r="B188" s="13">
         <v>1738652745</v>
       </c>
-      <c r="C188" s="15"/>
-      <c r="D188" s="15"/>
-      <c r="E188" s="15"/>
+      <c r="C188" s="15">
+        <v>4890088766</v>
+      </c>
+      <c r="D188" s="15">
+        <v>4890092483</v>
+      </c>
+      <c r="E188" s="15">
+        <v>5868092421</v>
+      </c>
       <c r="F188" s="15"/>
       <c r="G188" s="15"/>
       <c r="H188" s="15"/>
@@ -6674,9 +6827,15 @@
       <c r="B189" s="13">
         <v>1738652902</v>
       </c>
-      <c r="C189" s="15"/>
-      <c r="D189" s="15"/>
-      <c r="E189" s="15"/>
+      <c r="C189" s="15">
+        <v>4860270967</v>
+      </c>
+      <c r="D189" s="15">
+        <v>4964344959</v>
+      </c>
+      <c r="E189" s="15">
+        <v>4890096730</v>
+      </c>
       <c r="F189" s="15"/>
       <c r="G189" s="15"/>
       <c r="H189" s="15"/>
@@ -6700,10 +6859,18 @@
       <c r="B190" s="13">
         <v>1738653148</v>
       </c>
-      <c r="C190" s="15"/>
-      <c r="D190" s="15"/>
-      <c r="E190" s="15"/>
-      <c r="F190" s="15"/>
+      <c r="C190" s="15">
+        <v>5868049911</v>
+      </c>
+      <c r="D190" s="15">
+        <v>5868049626</v>
+      </c>
+      <c r="E190" s="15">
+        <v>5563969425</v>
+      </c>
+      <c r="F190" s="15">
+        <v>5739125769</v>
+      </c>
       <c r="G190" s="15"/>
       <c r="H190" s="15"/>
       <c r="I190" s="15"/>
@@ -6726,10 +6893,18 @@
       <c r="B191" s="13">
         <v>1738652878</v>
       </c>
-      <c r="C191" s="15"/>
-      <c r="D191" s="15"/>
-      <c r="E191" s="15"/>
-      <c r="F191" s="15"/>
+      <c r="C191" s="15">
+        <v>5868061841</v>
+      </c>
+      <c r="D191" s="15">
+        <v>5868065742</v>
+      </c>
+      <c r="E191" s="15">
+        <v>5563975185</v>
+      </c>
+      <c r="F191" s="15">
+        <v>5739122944</v>
+      </c>
       <c r="G191" s="15"/>
       <c r="H191" s="15"/>
       <c r="I191" s="15"/>
@@ -6777,11 +6952,21 @@
       <c r="B193" s="13">
         <v>1738651926</v>
       </c>
-      <c r="C193" s="15"/>
-      <c r="D193" s="15"/>
-      <c r="E193" s="15"/>
-      <c r="F193" s="15"/>
-      <c r="G193" s="15"/>
+      <c r="C193" s="15">
+        <v>4964347571</v>
+      </c>
+      <c r="D193" s="15">
+        <v>4890106754</v>
+      </c>
+      <c r="E193" s="15">
+        <v>4915353873</v>
+      </c>
+      <c r="F193" s="15">
+        <v>5563967751</v>
+      </c>
+      <c r="G193" s="15">
+        <v>5739125473</v>
+      </c>
       <c r="H193" s="15"/>
       <c r="I193" s="15"/>
       <c r="J193" s="15"/>
@@ -6803,11 +6988,21 @@
       <c r="B194" s="13">
         <v>1738652063</v>
       </c>
-      <c r="C194" s="15"/>
-      <c r="D194" s="15"/>
-      <c r="E194" s="15"/>
-      <c r="F194" s="15"/>
-      <c r="G194" s="15"/>
+      <c r="C194" s="15">
+        <v>4964343337</v>
+      </c>
+      <c r="D194" s="15">
+        <v>5868040467</v>
+      </c>
+      <c r="E194" s="15">
+        <v>5019830078</v>
+      </c>
+      <c r="F194" s="15">
+        <v>5563967919</v>
+      </c>
+      <c r="G194" s="15">
+        <v>5739127911</v>
+      </c>
       <c r="H194" s="15"/>
       <c r="I194" s="15"/>
       <c r="J194" s="15"/>
@@ -6829,9 +7024,15 @@
       <c r="B195" s="13">
         <v>1738652367</v>
       </c>
-      <c r="C195" s="15"/>
-      <c r="D195" s="15"/>
-      <c r="E195" s="15"/>
+      <c r="C195" s="15">
+        <v>5019506503</v>
+      </c>
+      <c r="D195" s="15">
+        <v>5563974252</v>
+      </c>
+      <c r="E195" s="15">
+        <v>5739122067</v>
+      </c>
       <c r="F195" s="15"/>
       <c r="G195" s="15"/>
       <c r="H195" s="15"/>
@@ -6933,7 +7134,9 @@
       <c r="B199" s="13">
         <v>1750746301</v>
       </c>
-      <c r="C199" s="15"/>
+      <c r="C199" s="15">
+        <v>5550877291</v>
+      </c>
       <c r="D199" s="15"/>
       <c r="E199" s="15"/>
       <c r="F199" s="15"/>
@@ -6985,8 +7188,12 @@
       <c r="B201" s="13">
         <v>1750745576</v>
       </c>
-      <c r="C201" s="15"/>
-      <c r="D201" s="15"/>
+      <c r="C201" s="15">
+        <v>5550899733</v>
+      </c>
+      <c r="D201" s="15">
+        <v>4860833835</v>
+      </c>
       <c r="E201" s="15"/>
       <c r="F201" s="15"/>
       <c r="G201" s="15"/>
@@ -7011,10 +7218,18 @@
       <c r="B202" s="13">
         <v>1849771468</v>
       </c>
-      <c r="C202" s="15"/>
-      <c r="D202" s="15"/>
-      <c r="E202" s="15"/>
-      <c r="F202" s="15"/>
+      <c r="C202" s="15">
+        <v>5052626728</v>
+      </c>
+      <c r="D202" s="15">
+        <v>4860257053</v>
+      </c>
+      <c r="E202" s="15">
+        <v>4860257462</v>
+      </c>
+      <c r="F202" s="15">
+        <v>4850055969</v>
+      </c>
       <c r="G202" s="15"/>
       <c r="H202" s="15"/>
       <c r="I202" s="15"/>
@@ -7037,11 +7252,21 @@
       <c r="B203" s="13">
         <v>1849777829</v>
       </c>
-      <c r="C203" s="15"/>
-      <c r="D203" s="15"/>
-      <c r="E203" s="15"/>
-      <c r="F203" s="15"/>
-      <c r="G203" s="15"/>
+      <c r="C203" s="15">
+        <v>5534854487</v>
+      </c>
+      <c r="D203" s="15">
+        <v>5052657579</v>
+      </c>
+      <c r="E203" s="15">
+        <v>4850070999</v>
+      </c>
+      <c r="F203" s="15">
+        <v>4860259102</v>
+      </c>
+      <c r="G203" s="15">
+        <v>4860263157</v>
+      </c>
       <c r="H203" s="15"/>
       <c r="I203" s="15"/>
       <c r="J203" s="15"/>
@@ -7063,9 +7288,15 @@
       <c r="B204" s="13">
         <v>1849777981</v>
       </c>
-      <c r="C204" s="15"/>
-      <c r="D204" s="15"/>
-      <c r="E204" s="15"/>
+      <c r="C204" s="15">
+        <v>5052686555</v>
+      </c>
+      <c r="D204" s="15">
+        <v>5526286446</v>
+      </c>
+      <c r="E204" s="15">
+        <v>4850080183</v>
+      </c>
       <c r="F204" s="15"/>
       <c r="G204" s="15"/>
       <c r="H204" s="15"/>
@@ -7089,11 +7320,21 @@
       <c r="B205" s="13">
         <v>1849778110</v>
       </c>
-      <c r="C205" s="15"/>
-      <c r="D205" s="15"/>
-      <c r="E205" s="15"/>
-      <c r="F205" s="15"/>
-      <c r="G205" s="15"/>
+      <c r="C205" s="15">
+        <v>5535486927</v>
+      </c>
+      <c r="D205" s="15">
+        <v>5052691191</v>
+      </c>
+      <c r="E205" s="15">
+        <v>5152127710</v>
+      </c>
+      <c r="F205" s="15">
+        <v>5152127710</v>
+      </c>
+      <c r="G205" s="15">
+        <v>4850073051</v>
+      </c>
       <c r="H205" s="15"/>
       <c r="I205" s="15"/>
       <c r="J205" s="15"/>
@@ -7115,10 +7356,18 @@
       <c r="B206" s="13">
         <v>1849777791</v>
       </c>
-      <c r="C206" s="15"/>
-      <c r="D206" s="15"/>
-      <c r="E206" s="15"/>
-      <c r="F206" s="15"/>
+      <c r="C206" s="15">
+        <v>4850068837</v>
+      </c>
+      <c r="D206" s="15">
+        <v>4860265890</v>
+      </c>
+      <c r="E206" s="15">
+        <v>4890102570</v>
+      </c>
+      <c r="F206" s="15">
+        <v>4890098701</v>
+      </c>
       <c r="G206" s="15"/>
       <c r="H206" s="15"/>
       <c r="I206" s="15"/>
@@ -7141,9 +7390,15 @@
       <c r="B207" s="13">
         <v>1849777893</v>
       </c>
-      <c r="C207" s="15"/>
-      <c r="D207" s="15"/>
-      <c r="E207" s="15"/>
+      <c r="C207" s="15">
+        <v>5052691323</v>
+      </c>
+      <c r="D207" s="15">
+        <v>4850070619</v>
+      </c>
+      <c r="E207" s="15">
+        <v>4850082845</v>
+      </c>
       <c r="F207" s="15"/>
       <c r="G207" s="15"/>
       <c r="H207" s="15"/>
@@ -7167,10 +7422,18 @@
       <c r="B208" s="13">
         <v>1849777815</v>
       </c>
-      <c r="C208" s="15"/>
-      <c r="D208" s="15"/>
-      <c r="E208" s="15"/>
-      <c r="F208" s="15"/>
+      <c r="C208" s="15">
+        <v>5152590675</v>
+      </c>
+      <c r="D208" s="15">
+        <v>5526410659</v>
+      </c>
+      <c r="E208" s="15">
+        <v>4860352054</v>
+      </c>
+      <c r="F208" s="15">
+        <v>4860354079</v>
+      </c>
       <c r="G208" s="15"/>
       <c r="H208" s="15"/>
       <c r="I208" s="15"/>
@@ -7193,12 +7456,24 @@
       <c r="B209" s="13">
         <v>1849777581</v>
       </c>
-      <c r="C209" s="15"/>
-      <c r="D209" s="15"/>
-      <c r="E209" s="15"/>
-      <c r="F209" s="15"/>
-      <c r="G209" s="15"/>
-      <c r="H209" s="15"/>
+      <c r="C209" s="15">
+        <v>5052650742</v>
+      </c>
+      <c r="D209" s="15">
+        <v>5526350580</v>
+      </c>
+      <c r="E209" s="15">
+        <v>5151978855</v>
+      </c>
+      <c r="F209" s="15">
+        <v>4850061237</v>
+      </c>
+      <c r="G209" s="15">
+        <v>4850072095</v>
+      </c>
+      <c r="H209" s="15">
+        <v>4860261667</v>
+      </c>
       <c r="I209" s="15"/>
       <c r="J209" s="15"/>
       <c r="K209" s="15"/>
@@ -7219,11 +7494,21 @@
       <c r="B210" s="13">
         <v>1849777716</v>
       </c>
-      <c r="C210" s="15"/>
-      <c r="D210" s="15"/>
-      <c r="E210" s="15"/>
-      <c r="F210" s="15"/>
-      <c r="G210" s="15"/>
+      <c r="C210" s="15">
+        <v>5052637004</v>
+      </c>
+      <c r="D210" s="15">
+        <v>5151992169</v>
+      </c>
+      <c r="E210" s="15">
+        <v>4860258515</v>
+      </c>
+      <c r="F210" s="15">
+        <v>4890095766</v>
+      </c>
+      <c r="G210" s="15">
+        <v>4890100064</v>
+      </c>
       <c r="H210" s="15"/>
       <c r="I210" s="15"/>
       <c r="J210" s="15"/>
@@ -7245,12 +7530,24 @@
       <c r="B211" s="13">
         <v>1849777650</v>
       </c>
-      <c r="C211" s="15"/>
-      <c r="D211" s="15"/>
-      <c r="E211" s="15"/>
-      <c r="F211" s="15"/>
-      <c r="G211" s="15"/>
-      <c r="H211" s="15"/>
+      <c r="C211" s="15">
+        <v>5052714253</v>
+      </c>
+      <c r="D211" s="15">
+        <v>4860267881</v>
+      </c>
+      <c r="E211" s="15">
+        <v>4890100795</v>
+      </c>
+      <c r="F211" s="15">
+        <v>5876604052</v>
+      </c>
+      <c r="G211" s="15">
+        <v>5876602738</v>
+      </c>
+      <c r="H211" s="15">
+        <v>5563962115</v>
+      </c>
       <c r="I211" s="15"/>
       <c r="J211" s="15"/>
       <c r="K211" s="15"/>
@@ -7271,9 +7568,15 @@
       <c r="B212" s="13">
         <v>1849778040</v>
       </c>
-      <c r="C212" s="15"/>
-      <c r="D212" s="15"/>
-      <c r="E212" s="15"/>
+      <c r="C212" s="15">
+        <v>5052649542</v>
+      </c>
+      <c r="D212" s="15">
+        <v>5151941910</v>
+      </c>
+      <c r="E212" s="15">
+        <v>4850055818</v>
+      </c>
       <c r="F212" s="15"/>
       <c r="G212" s="15"/>
       <c r="H212" s="15"/>
@@ -7297,10 +7600,18 @@
       <c r="B213" s="13">
         <v>1849777940</v>
       </c>
-      <c r="C213" s="15"/>
-      <c r="D213" s="15"/>
-      <c r="E213" s="15"/>
-      <c r="F213" s="15"/>
+      <c r="C213" s="15">
+        <v>5526480988</v>
+      </c>
+      <c r="D213" s="15">
+        <v>5052684087</v>
+      </c>
+      <c r="E213" s="15">
+        <v>4850059812</v>
+      </c>
+      <c r="F213" s="15">
+        <v>4860260473</v>
+      </c>
       <c r="G213" s="15"/>
       <c r="H213" s="15"/>
       <c r="I213" s="15"/>
@@ -7323,10 +7634,18 @@
       <c r="B214" s="13">
         <v>1849778044</v>
       </c>
-      <c r="C214" s="15"/>
-      <c r="D214" s="15"/>
-      <c r="E214" s="15"/>
-      <c r="F214" s="15"/>
+      <c r="C214" s="15">
+        <v>5534569906</v>
+      </c>
+      <c r="D214" s="15">
+        <v>5052680357</v>
+      </c>
+      <c r="E214" s="15">
+        <v>4850069652</v>
+      </c>
+      <c r="F214" s="15">
+        <v>4860264759</v>
+      </c>
       <c r="G214" s="15"/>
       <c r="H214" s="15"/>
       <c r="I214" s="15"/>
@@ -7349,8 +7668,12 @@
       <c r="B215" s="13">
         <v>1849777586</v>
       </c>
-      <c r="C215" s="15"/>
-      <c r="D215" s="15"/>
+      <c r="C215" s="15">
+        <v>5052687037</v>
+      </c>
+      <c r="D215" s="15">
+        <v>5052687037</v>
+      </c>
       <c r="E215" s="15"/>
       <c r="F215" s="15"/>
       <c r="G215" s="15"/>
@@ -7375,10 +7698,18 @@
       <c r="B216" s="13">
         <v>1849778023</v>
       </c>
-      <c r="C216" s="15"/>
-      <c r="D216" s="15"/>
-      <c r="E216" s="15"/>
-      <c r="F216" s="15"/>
+      <c r="C216" s="15">
+        <v>5052661484</v>
+      </c>
+      <c r="D216" s="15">
+        <v>4860260190</v>
+      </c>
+      <c r="E216" s="15">
+        <v>4860268434</v>
+      </c>
+      <c r="F216" s="15">
+        <v>5563972066</v>
+      </c>
       <c r="G216" s="15"/>
       <c r="H216" s="15"/>
       <c r="I216" s="15"/>
@@ -7401,10 +7732,18 @@
       <c r="B217" s="13">
         <v>1849777600</v>
       </c>
-      <c r="C217" s="15"/>
-      <c r="D217" s="15"/>
-      <c r="E217" s="15"/>
-      <c r="F217" s="15"/>
+      <c r="C217" s="15">
+        <v>5534874952</v>
+      </c>
+      <c r="D217" s="15">
+        <v>5052648548</v>
+      </c>
+      <c r="E217" s="15">
+        <v>4860260217</v>
+      </c>
+      <c r="F217" s="15">
+        <v>4860261398</v>
+      </c>
       <c r="G217" s="15"/>
       <c r="H217" s="15"/>
       <c r="I217" s="15"/>
@@ -7427,11 +7766,21 @@
       <c r="B218" s="13">
         <v>1849777647</v>
       </c>
-      <c r="C218" s="15"/>
-      <c r="D218" s="15"/>
-      <c r="E218" s="15"/>
-      <c r="F218" s="15"/>
-      <c r="G218" s="15"/>
+      <c r="C218" s="15">
+        <v>5526395826</v>
+      </c>
+      <c r="D218" s="15">
+        <v>5052620393</v>
+      </c>
+      <c r="E218" s="15">
+        <v>5151983412</v>
+      </c>
+      <c r="F218" s="15">
+        <v>4850054200</v>
+      </c>
+      <c r="G218" s="15">
+        <v>4860257545</v>
+      </c>
       <c r="H218" s="15"/>
       <c r="I218" s="15"/>
       <c r="J218" s="15"/>
@@ -7453,9 +7802,15 @@
       <c r="B219" s="13">
         <v>1849777720</v>
       </c>
-      <c r="C219" s="15"/>
-      <c r="D219" s="15"/>
-      <c r="E219" s="15"/>
+      <c r="C219" s="15">
+        <v>5534806044</v>
+      </c>
+      <c r="D219" s="15">
+        <v>5052687056</v>
+      </c>
+      <c r="E219" s="15">
+        <v>4850079803</v>
+      </c>
       <c r="F219" s="15"/>
       <c r="G219" s="15"/>
       <c r="H219" s="15"/>
@@ -7479,11 +7834,21 @@
       <c r="B220" s="13">
         <v>1849777551</v>
       </c>
-      <c r="C220" s="15"/>
-      <c r="D220" s="15"/>
-      <c r="E220" s="15"/>
-      <c r="F220" s="15"/>
-      <c r="G220" s="15"/>
+      <c r="C220" s="15">
+        <v>5534713003</v>
+      </c>
+      <c r="D220" s="15">
+        <v>5052632931</v>
+      </c>
+      <c r="E220" s="15">
+        <v>4850110100</v>
+      </c>
+      <c r="F220" s="15">
+        <v>4860275725</v>
+      </c>
+      <c r="G220" s="15">
+        <v>4860282553</v>
+      </c>
       <c r="H220" s="15"/>
       <c r="I220" s="15"/>
       <c r="J220" s="15"/>
@@ -7505,10 +7870,18 @@
       <c r="B221" s="13">
         <v>1849778151</v>
       </c>
-      <c r="C221" s="15"/>
-      <c r="D221" s="15"/>
-      <c r="E221" s="15"/>
-      <c r="F221" s="15"/>
+      <c r="C221" s="15">
+        <v>5052655978</v>
+      </c>
+      <c r="D221" s="15">
+        <v>5534874064</v>
+      </c>
+      <c r="E221" s="15">
+        <v>4860258048</v>
+      </c>
+      <c r="F221" s="15">
+        <v>4860259864</v>
+      </c>
       <c r="G221" s="15"/>
       <c r="H221" s="15"/>
       <c r="I221" s="15"/>
@@ -7531,10 +7904,18 @@
       <c r="B222" s="13">
         <v>1849777651</v>
       </c>
-      <c r="C222" s="15"/>
-      <c r="D222" s="15"/>
-      <c r="E222" s="15"/>
-      <c r="F222" s="15"/>
+      <c r="C222" s="15">
+        <v>5526339780</v>
+      </c>
+      <c r="D222" s="15">
+        <v>5052637156</v>
+      </c>
+      <c r="E222" s="15">
+        <v>4850060262</v>
+      </c>
+      <c r="F222" s="15">
+        <v>4860262354</v>
+      </c>
       <c r="G222" s="15"/>
       <c r="H222" s="15"/>
       <c r="I222" s="15"/>
@@ -7557,11 +7938,21 @@
       <c r="B223" s="13">
         <v>1849777656</v>
       </c>
-      <c r="C223" s="15"/>
-      <c r="D223" s="15"/>
-      <c r="E223" s="15"/>
-      <c r="F223" s="15"/>
-      <c r="G223" s="15"/>
+      <c r="C223" s="15">
+        <v>4860258314</v>
+      </c>
+      <c r="D223" s="15">
+        <v>4860258331</v>
+      </c>
+      <c r="E223" s="15">
+        <v>4890107681</v>
+      </c>
+      <c r="F223" s="15">
+        <v>4890102085</v>
+      </c>
+      <c r="G223" s="15">
+        <v>5563976036</v>
+      </c>
       <c r="H223" s="15"/>
       <c r="I223" s="15"/>
       <c r="J223" s="15"/>
@@ -7583,9 +7974,15 @@
       <c r="B224" s="13">
         <v>1849777833</v>
       </c>
-      <c r="C224" s="15"/>
-      <c r="D224" s="15"/>
-      <c r="E224" s="15"/>
+      <c r="C224" s="15">
+        <v>4860260536</v>
+      </c>
+      <c r="D224" s="15">
+        <v>4890091018</v>
+      </c>
+      <c r="E224" s="15">
+        <v>4890097690</v>
+      </c>
       <c r="F224" s="15"/>
       <c r="G224" s="15"/>
       <c r="H224" s="15"/>
@@ -7609,13 +8006,27 @@
       <c r="B225" s="13">
         <v>1849777906</v>
       </c>
-      <c r="C225" s="15"/>
-      <c r="D225" s="15"/>
-      <c r="E225" s="15"/>
-      <c r="F225" s="15"/>
-      <c r="G225" s="15"/>
-      <c r="H225" s="15"/>
-      <c r="I225" s="15"/>
+      <c r="C225" s="15">
+        <v>4850062482</v>
+      </c>
+      <c r="D225" s="15">
+        <v>4860264003</v>
+      </c>
+      <c r="E225" s="15">
+        <v>4890100271</v>
+      </c>
+      <c r="F225" s="15">
+        <v>4890112252</v>
+      </c>
+      <c r="G225" s="15">
+        <v>5876595389</v>
+      </c>
+      <c r="H225" s="15">
+        <v>5876595709</v>
+      </c>
+      <c r="I225" s="15">
+        <v>5563972627</v>
+      </c>
       <c r="J225" s="15"/>
       <c r="K225" s="15"/>
       <c r="L225" s="15"/>
@@ -7635,10 +8046,18 @@
       <c r="B226" s="13">
         <v>1849777862</v>
       </c>
-      <c r="C226" s="15"/>
-      <c r="D226" s="15"/>
-      <c r="E226" s="15"/>
-      <c r="F226" s="15"/>
+      <c r="C226" s="15">
+        <v>4860265158</v>
+      </c>
+      <c r="D226" s="15">
+        <v>4890098945</v>
+      </c>
+      <c r="E226" s="15">
+        <v>4890099372</v>
+      </c>
+      <c r="F226" s="15">
+        <v>5563963162</v>
+      </c>
       <c r="G226" s="15"/>
       <c r="H226" s="15"/>
       <c r="I226" s="15"/>
@@ -7661,8 +8080,12 @@
       <c r="B227" s="13">
         <v>1912188679</v>
       </c>
-      <c r="C227" s="15"/>
-      <c r="D227" s="15"/>
+      <c r="C227" s="15">
+        <v>5551173838</v>
+      </c>
+      <c r="D227" s="15">
+        <v>5739121495</v>
+      </c>
       <c r="E227" s="15"/>
       <c r="F227" s="15"/>
       <c r="G227" s="15"/>
@@ -7687,8 +8110,12 @@
       <c r="B228" s="13">
         <v>1912201998</v>
       </c>
-      <c r="C228" s="15"/>
-      <c r="D228" s="15"/>
+      <c r="C228" s="15">
+        <v>5563647206</v>
+      </c>
+      <c r="D228" s="15">
+        <v>5739119047</v>
+      </c>
       <c r="E228" s="15"/>
       <c r="F228" s="15"/>
       <c r="G228" s="15"/>
@@ -8077,15 +8504,9 @@
       <c r="B243" s="13">
         <v>1912202150</v>
       </c>
-      <c r="C243" s="15">
-        <v>5550990571</v>
-      </c>
-      <c r="D243" s="15">
-        <v>5563643576</v>
-      </c>
-      <c r="E243" s="15">
-        <v>5739119917</v>
-      </c>
+      <c r="C243" s="15"/>
+      <c r="D243" s="15"/>
+      <c r="E243" s="15"/>
       <c r="F243" s="15"/>
       <c r="G243" s="15"/>
       <c r="H243" s="15"/>
@@ -8135,12 +8556,8 @@
       <c r="B245" s="13">
         <v>1912202516</v>
       </c>
-      <c r="C245" s="15">
-        <v>5260051785</v>
-      </c>
-      <c r="D245" s="15">
-        <v>5563644796</v>
-      </c>
+      <c r="C245" s="15"/>
+      <c r="D245" s="15"/>
       <c r="E245" s="15"/>
       <c r="F245" s="15"/>
       <c r="G245" s="15"/>
@@ -8165,12 +8582,8 @@
       <c r="B246" s="13">
         <v>1912202637</v>
       </c>
-      <c r="C246" s="15">
-        <v>5563647744</v>
-      </c>
-      <c r="D246" s="15">
-        <v>5739118888</v>
-      </c>
+      <c r="C246" s="15"/>
+      <c r="D246" s="15"/>
       <c r="E246" s="15"/>
       <c r="F246" s="15"/>
       <c r="G246" s="15"/>
@@ -8195,9 +8608,7 @@
       <c r="B247" s="13">
         <v>1912201812</v>
       </c>
-      <c r="C247" s="15">
-        <v>5739118581</v>
-      </c>
+      <c r="C247" s="15"/>
       <c r="D247" s="15"/>
       <c r="E247" s="15"/>
       <c r="F247" s="15"/>
@@ -8223,12 +8634,8 @@
       <c r="B248" s="13">
         <v>1912202756</v>
       </c>
-      <c r="C248" s="15">
-        <v>5260238915</v>
-      </c>
-      <c r="D248" s="15">
-        <v>5563642466</v>
-      </c>
+      <c r="C248" s="15"/>
+      <c r="D248" s="15"/>
       <c r="E248" s="15"/>
       <c r="F248" s="15"/>
       <c r="G248" s="15"/>
@@ -8279,9 +8686,7 @@
       <c r="B250" s="13">
         <v>1912202058</v>
       </c>
-      <c r="C250" s="15">
-        <v>5739118779</v>
-      </c>
+      <c r="C250" s="15"/>
       <c r="D250" s="15"/>
       <c r="E250" s="15"/>
       <c r="F250" s="15"/>
@@ -8308,13 +8713,13 @@
         <v>2449977854</v>
       </c>
       <c r="C251" s="15">
-        <v>4860283414</v>
+        <v>5876580602</v>
       </c>
       <c r="D251" s="15">
-        <v>4850262687</v>
+        <v>5876580644</v>
       </c>
       <c r="E251" s="15">
-        <v>4927493709</v>
+        <v>5563954693</v>
       </c>
       <c r="F251" s="15"/>
       <c r="G251" s="15"/>
@@ -8341,17 +8746,15 @@
         <v>2449977213</v>
       </c>
       <c r="C252" s="15">
-        <v>5534248382</v>
+        <v>4850253942</v>
       </c>
       <c r="D252" s="15">
-        <v>4860284001</v>
+        <v>4927494497</v>
       </c>
       <c r="E252" s="15">
-        <v>5051064345</v>
-      </c>
-      <c r="F252" s="15">
-        <v>5051053774</v>
-      </c>
+        <v>5563955988</v>
+      </c>
+      <c r="F252" s="15"/>
       <c r="G252" s="15"/>
       <c r="H252" s="15"/>
       <c r="I252" s="15"/>
@@ -8376,12 +8779,20 @@
         <v>2449975997</v>
       </c>
       <c r="C253" s="15">
-        <v>4927493679</v>
-      </c>
-      <c r="D253" s="15"/>
-      <c r="E253" s="15"/>
-      <c r="F253" s="15"/>
-      <c r="G253" s="15"/>
+        <v>4850286060</v>
+      </c>
+      <c r="D253" s="15">
+        <v>4860282949</v>
+      </c>
+      <c r="E253" s="15">
+        <v>5051048783</v>
+      </c>
+      <c r="F253" s="15">
+        <v>4850265777</v>
+      </c>
+      <c r="G253" s="15">
+        <v>5563955456</v>
+      </c>
       <c r="H253" s="15"/>
       <c r="I253" s="15"/>
       <c r="J253" s="15"/>
@@ -8405,17 +8816,23 @@
         <v>2449977489</v>
       </c>
       <c r="C254" s="15">
-        <v>4850250121</v>
+        <v>4860283612</v>
       </c>
       <c r="D254" s="15">
-        <v>4850285957</v>
+        <v>5051051826</v>
       </c>
       <c r="E254" s="15">
-        <v>5876617261</v>
-      </c>
-      <c r="F254" s="15"/>
-      <c r="G254" s="15"/>
-      <c r="H254" s="15"/>
+        <v>5051054047</v>
+      </c>
+      <c r="F254" s="15">
+        <v>4927493660</v>
+      </c>
+      <c r="G254" s="15">
+        <v>5876616021</v>
+      </c>
+      <c r="H254" s="15">
+        <v>5563955694</v>
+      </c>
       <c r="I254" s="15"/>
       <c r="J254" s="15"/>
       <c r="K254" s="15"/>
@@ -8438,20 +8855,16 @@
         <v>2449979646</v>
       </c>
       <c r="C255" s="15">
-        <v>4850254194</v>
+        <v>5876620563</v>
       </c>
       <c r="D255" s="15">
-        <v>4850265345</v>
+        <v>5876621588</v>
       </c>
       <c r="E255" s="15">
-        <v>4860282968</v>
-      </c>
-      <c r="F255" s="15">
-        <v>4927492131</v>
-      </c>
-      <c r="G255" s="15">
-        <v>5643125807</v>
-      </c>
+        <v>5563955773</v>
+      </c>
+      <c r="F255" s="15"/>
+      <c r="G255" s="15"/>
       <c r="H255" s="15"/>
       <c r="I255" s="15"/>
       <c r="J255" s="15"/>
@@ -8475,17 +8888,15 @@
         <v>2449977972</v>
       </c>
       <c r="C256" s="16">
-        <v>4927493514</v>
+        <v>4860283801</v>
       </c>
       <c r="D256" s="15">
-        <v>5534875329</v>
+        <v>4927491947</v>
       </c>
       <c r="E256" s="15">
-        <v>4850259702</v>
-      </c>
-      <c r="F256" s="15">
-        <v>4850263574</v>
-      </c>
+        <v>5563961658</v>
+      </c>
+      <c r="F256" s="15"/>
       <c r="G256" s="15"/>
       <c r="H256" s="15"/>
       <c r="I256" s="15"/>
@@ -8510,15 +8921,23 @@
         <v>2449976830</v>
       </c>
       <c r="C257" s="15">
-        <v>4850254382</v>
+        <v>5051088866</v>
       </c>
       <c r="D257" s="15">
-        <v>4927493905</v>
-      </c>
-      <c r="E257" s="15"/>
-      <c r="F257" s="15"/>
-      <c r="G257" s="15"/>
-      <c r="H257" s="15"/>
+        <v>4927493895</v>
+      </c>
+      <c r="E257" s="15">
+        <v>5868062209</v>
+      </c>
+      <c r="F257" s="15">
+        <v>5868064684</v>
+      </c>
+      <c r="G257" s="15">
+        <v>5563953061</v>
+      </c>
+      <c r="H257" s="15">
+        <v>5682479041</v>
+      </c>
       <c r="I257" s="15"/>
       <c r="J257" s="15"/>
       <c r="K257" s="15"/>
@@ -8567,12 +8986,8 @@
       <c r="B259" s="13">
         <v>2449978096</v>
       </c>
-      <c r="C259" s="15">
-        <v>5868083016</v>
-      </c>
-      <c r="D259" s="15">
-        <v>5563955559</v>
-      </c>
+      <c r="C259" s="15"/>
+      <c r="D259" s="15"/>
       <c r="E259" s="15"/>
       <c r="F259" s="15"/>
       <c r="G259" s="15"/>
@@ -8598,18 +9013,10 @@
       <c r="B260" s="13">
         <v>2449977830</v>
       </c>
-      <c r="C260" s="15">
-        <v>4927494260</v>
-      </c>
-      <c r="D260" s="15">
-        <v>5868083357</v>
-      </c>
-      <c r="E260" s="15">
-        <v>5563954952</v>
-      </c>
-      <c r="F260" s="15">
-        <v>5682481768</v>
-      </c>
+      <c r="C260" s="15"/>
+      <c r="D260" s="15"/>
+      <c r="E260" s="15"/>
+      <c r="F260" s="15"/>
       <c r="G260" s="15"/>
       <c r="H260" s="15"/>
       <c r="I260" s="15"/>
@@ -8633,12 +9040,8 @@
       <c r="B261" s="13">
         <v>2449979383</v>
       </c>
-      <c r="C261" s="16">
-        <v>4927495342</v>
-      </c>
-      <c r="D261" s="15">
-        <v>5563958107</v>
-      </c>
+      <c r="C261" s="16"/>
+      <c r="D261" s="15"/>
       <c r="E261" s="15"/>
       <c r="F261" s="15"/>
       <c r="G261" s="15"/>
@@ -8664,15 +9067,9 @@
       <c r="B262" s="13">
         <v>2449977151</v>
       </c>
-      <c r="C262" s="15">
-        <v>5868025182</v>
-      </c>
-      <c r="D262" s="15">
-        <v>5868025782</v>
-      </c>
-      <c r="E262" s="15">
-        <v>5563961243</v>
-      </c>
+      <c r="C262" s="15"/>
+      <c r="D262" s="15"/>
+      <c r="E262" s="15"/>
       <c r="F262" s="15"/>
       <c r="G262" s="15"/>
       <c r="H262" s="15"/>
@@ -9695,7 +10092,9 @@
       <c r="B297" s="13">
         <v>2474254390</v>
       </c>
-      <c r="C297" s="15"/>
+      <c r="C297" s="15">
+        <v>5639401044</v>
+      </c>
       <c r="D297" s="15"/>
       <c r="E297" s="15"/>
       <c r="F297" s="15"/>
@@ -9722,7 +10121,9 @@
       <c r="B298" s="13">
         <v>2474254998</v>
       </c>
-      <c r="C298" s="15"/>
+      <c r="C298" s="15">
+        <v>5639405494</v>
+      </c>
       <c r="D298" s="15"/>
       <c r="E298" s="15"/>
       <c r="F298" s="15"/>
@@ -9749,8 +10150,12 @@
       <c r="B299" s="13">
         <v>2474254021</v>
       </c>
-      <c r="C299" s="15"/>
-      <c r="D299" s="15"/>
+      <c r="C299" s="15">
+        <v>4860784281</v>
+      </c>
+      <c r="D299" s="15">
+        <v>5639406596</v>
+      </c>
       <c r="E299" s="15"/>
       <c r="F299" s="15"/>
       <c r="G299" s="15"/>
@@ -9776,7 +10181,9 @@
       <c r="B300" s="13">
         <v>2474251925</v>
       </c>
-      <c r="C300" s="15"/>
+      <c r="C300" s="15">
+        <v>5639404401</v>
+      </c>
       <c r="D300" s="15"/>
       <c r="E300" s="15"/>
       <c r="F300" s="15"/>
@@ -9830,9 +10237,15 @@
       <c r="B302" s="13">
         <v>2474254585</v>
       </c>
-      <c r="C302" s="15"/>
-      <c r="D302" s="15"/>
-      <c r="E302" s="15"/>
+      <c r="C302" s="15">
+        <v>5551362427</v>
+      </c>
+      <c r="D302" s="15">
+        <v>4860780494</v>
+      </c>
+      <c r="E302" s="15">
+        <v>5639403011</v>
+      </c>
       <c r="F302" s="15"/>
       <c r="G302" s="15"/>
       <c r="H302" s="15"/>
@@ -9857,8 +10270,12 @@
       <c r="B303" s="13">
         <v>2474252626</v>
       </c>
-      <c r="C303" s="15"/>
-      <c r="D303" s="15"/>
+      <c r="C303" s="15">
+        <v>4860785874</v>
+      </c>
+      <c r="D303" s="15">
+        <v>5639403579</v>
+      </c>
       <c r="E303" s="15"/>
       <c r="F303" s="15"/>
       <c r="G303" s="15"/>
@@ -9884,8 +10301,12 @@
       <c r="B304" s="13">
         <v>2474251481</v>
       </c>
-      <c r="C304" s="15"/>
-      <c r="D304" s="15"/>
+      <c r="C304" s="15">
+        <v>4860784321</v>
+      </c>
+      <c r="D304" s="15">
+        <v>5639403371</v>
+      </c>
       <c r="E304" s="15"/>
       <c r="F304" s="15"/>
       <c r="G304" s="15"/>

--- a/воры/Amazing_Pics_SKU ALL_06.10.2026.xlsx
+++ b/воры/Amazing_Pics_SKU ALL_06.10.2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\воры\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D2CC68-220B-44C2-BB8B-A5F5E460136E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02139394-0A62-4166-903C-7270757F4F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1345,7 +1345,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1400,6 +1400,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -1448,7 +1454,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1475,6 +1481,7 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="4" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2901,7 +2908,7 @@
       <c r="A44" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B44" s="13">
+      <c r="B44" s="20">
         <v>1506332421</v>
       </c>
       <c r="C44" s="15"/>
@@ -3424,7 +3431,9 @@
       <c r="B64" s="13">
         <v>1506372679</v>
       </c>
-      <c r="C64" s="16"/>
+      <c r="C64" s="16">
+        <v>5739111156</v>
+      </c>
       <c r="D64" s="15"/>
       <c r="E64" s="15"/>
       <c r="F64" s="15"/>
@@ -3450,8 +3459,12 @@
       <c r="B65" s="13">
         <v>1522021181</v>
       </c>
-      <c r="C65" s="15"/>
-      <c r="D65" s="15"/>
+      <c r="C65" s="15">
+        <v>5628264773</v>
+      </c>
+      <c r="D65" s="15">
+        <v>5628267469</v>
+      </c>
       <c r="E65" s="15"/>
       <c r="F65" s="15"/>
       <c r="G65" s="15"/>
@@ -3476,9 +3489,15 @@
       <c r="B66" s="13">
         <v>1522019560</v>
       </c>
-      <c r="C66" s="15"/>
-      <c r="D66" s="15"/>
-      <c r="E66" s="15"/>
+      <c r="C66" s="15">
+        <v>5535005981</v>
+      </c>
+      <c r="D66" s="15">
+        <v>5628265150</v>
+      </c>
+      <c r="E66" s="15">
+        <v>5628263024</v>
+      </c>
       <c r="F66" s="15"/>
       <c r="G66" s="15"/>
       <c r="H66" s="15"/>
@@ -3502,9 +3521,15 @@
       <c r="B67" s="13">
         <v>1522019577</v>
       </c>
-      <c r="C67" s="15"/>
-      <c r="D67" s="15"/>
-      <c r="E67" s="15"/>
+      <c r="C67" s="15">
+        <v>5534505192</v>
+      </c>
+      <c r="D67" s="15">
+        <v>5628266891</v>
+      </c>
+      <c r="E67" s="15">
+        <v>5628264167</v>
+      </c>
       <c r="F67" s="15"/>
       <c r="G67" s="15"/>
       <c r="H67" s="15"/>
@@ -3528,9 +3553,15 @@
       <c r="B68" s="13">
         <v>1522021741</v>
       </c>
-      <c r="C68" s="15"/>
-      <c r="D68" s="15"/>
-      <c r="E68" s="15"/>
+      <c r="C68" s="15">
+        <v>5534925467</v>
+      </c>
+      <c r="D68" s="15">
+        <v>5628266143</v>
+      </c>
+      <c r="E68" s="15">
+        <v>5628263053</v>
+      </c>
       <c r="F68" s="15"/>
       <c r="G68" s="15"/>
       <c r="H68" s="15"/>
@@ -3554,8 +3585,12 @@
       <c r="B69" s="13">
         <v>1522019667</v>
       </c>
-      <c r="C69" s="15"/>
-      <c r="D69" s="15"/>
+      <c r="C69" s="15">
+        <v>5628262497</v>
+      </c>
+      <c r="D69" s="15">
+        <v>5628262695</v>
+      </c>
       <c r="E69" s="15"/>
       <c r="F69" s="15"/>
       <c r="G69" s="15"/>
@@ -3580,9 +3615,15 @@
       <c r="B70" s="13">
         <v>1522019647</v>
       </c>
-      <c r="C70" s="15"/>
-      <c r="D70" s="15"/>
-      <c r="E70" s="15"/>
+      <c r="C70" s="15">
+        <v>5534703150</v>
+      </c>
+      <c r="D70" s="15">
+        <v>5628264119</v>
+      </c>
+      <c r="E70" s="15">
+        <v>5628264383</v>
+      </c>
       <c r="F70" s="15"/>
       <c r="G70" s="15"/>
       <c r="H70" s="15"/>
@@ -3606,9 +3647,15 @@
       <c r="B71" s="13">
         <v>1522022092</v>
       </c>
-      <c r="C71" s="15"/>
-      <c r="D71" s="15"/>
-      <c r="E71" s="15"/>
+      <c r="C71" s="15">
+        <v>5628265843</v>
+      </c>
+      <c r="D71" s="15">
+        <v>5628265806</v>
+      </c>
+      <c r="E71" s="15">
+        <v>5655666802</v>
+      </c>
       <c r="F71" s="15"/>
       <c r="G71" s="15"/>
       <c r="H71" s="15"/>
@@ -3632,10 +3679,18 @@
       <c r="B72" s="13">
         <v>1522019312</v>
       </c>
-      <c r="C72" s="15"/>
-      <c r="D72" s="15"/>
-      <c r="E72" s="15"/>
-      <c r="F72" s="15"/>
+      <c r="C72" s="15">
+        <v>5534502496</v>
+      </c>
+      <c r="D72" s="15">
+        <v>5628263907</v>
+      </c>
+      <c r="E72" s="15">
+        <v>5628266825</v>
+      </c>
+      <c r="F72" s="15">
+        <v>5655659486</v>
+      </c>
       <c r="G72" s="15"/>
       <c r="H72" s="15"/>
       <c r="I72" s="15"/>
@@ -3658,9 +3713,15 @@
       <c r="B73" s="13">
         <v>1522019474</v>
       </c>
-      <c r="C73" s="15"/>
-      <c r="D73" s="15"/>
-      <c r="E73" s="15"/>
+      <c r="C73" s="15">
+        <v>5526376339</v>
+      </c>
+      <c r="D73" s="15">
+        <v>5628264478</v>
+      </c>
+      <c r="E73" s="15">
+        <v>5628262379</v>
+      </c>
       <c r="F73" s="15"/>
       <c r="G73" s="15"/>
       <c r="H73" s="15"/>
@@ -3684,9 +3745,15 @@
       <c r="B74" s="13">
         <v>1522020629</v>
       </c>
-      <c r="C74" s="15"/>
-      <c r="D74" s="15"/>
-      <c r="E74" s="15"/>
+      <c r="C74" s="15">
+        <v>5628262861</v>
+      </c>
+      <c r="D74" s="15">
+        <v>5628264197</v>
+      </c>
+      <c r="E74" s="15">
+        <v>5655660068</v>
+      </c>
       <c r="F74" s="15"/>
       <c r="G74" s="15"/>
       <c r="H74" s="15"/>
@@ -3710,8 +3777,12 @@
       <c r="B75" s="13">
         <v>1522020596</v>
       </c>
-      <c r="C75" s="15"/>
-      <c r="D75" s="15"/>
+      <c r="C75" s="15">
+        <v>5628262674</v>
+      </c>
+      <c r="D75" s="15">
+        <v>5628261767</v>
+      </c>
       <c r="E75" s="15"/>
       <c r="F75" s="15"/>
       <c r="G75" s="15"/>
@@ -3736,9 +3807,15 @@
       <c r="B76" s="13">
         <v>1522019498</v>
       </c>
-      <c r="C76" s="15"/>
-      <c r="D76" s="15"/>
-      <c r="E76" s="15"/>
+      <c r="C76" s="15">
+        <v>5526485693</v>
+      </c>
+      <c r="D76" s="15">
+        <v>5628260776</v>
+      </c>
+      <c r="E76" s="15">
+        <v>5628265982</v>
+      </c>
       <c r="F76" s="15"/>
       <c r="G76" s="15"/>
       <c r="H76" s="15"/>
@@ -3762,9 +3839,15 @@
       <c r="B77" s="13">
         <v>1522019450</v>
       </c>
-      <c r="C77" s="15"/>
-      <c r="D77" s="15"/>
-      <c r="E77" s="15"/>
+      <c r="C77" s="15">
+        <v>5526548017</v>
+      </c>
+      <c r="D77" s="15">
+        <v>5631026741</v>
+      </c>
+      <c r="E77" s="15">
+        <v>5638861221</v>
+      </c>
       <c r="F77" s="15"/>
       <c r="G77" s="15"/>
       <c r="H77" s="15"/>
@@ -3788,10 +3871,18 @@
       <c r="B78" s="13">
         <v>1522019276</v>
       </c>
-      <c r="C78" s="15"/>
-      <c r="D78" s="15"/>
-      <c r="E78" s="15"/>
-      <c r="F78" s="15"/>
+      <c r="C78" s="15">
+        <v>5526252823</v>
+      </c>
+      <c r="D78" s="15">
+        <v>5628266131</v>
+      </c>
+      <c r="E78" s="15">
+        <v>5628266387</v>
+      </c>
+      <c r="F78" s="15">
+        <v>5655657210</v>
+      </c>
       <c r="G78" s="15"/>
       <c r="H78" s="15"/>
       <c r="I78" s="15"/>
@@ -3814,8 +3905,12 @@
       <c r="B79" s="13">
         <v>1522019477</v>
       </c>
-      <c r="C79" s="15"/>
-      <c r="D79" s="15"/>
+      <c r="C79" s="15">
+        <v>5628267805</v>
+      </c>
+      <c r="D79" s="15">
+        <v>5655660316</v>
+      </c>
       <c r="E79" s="15"/>
       <c r="F79" s="15"/>
       <c r="G79" s="15"/>
@@ -3840,9 +3935,15 @@
       <c r="B80" s="13">
         <v>1522019374</v>
       </c>
-      <c r="C80" s="15"/>
-      <c r="D80" s="15"/>
-      <c r="E80" s="15"/>
+      <c r="C80" s="15">
+        <v>5628267806</v>
+      </c>
+      <c r="D80" s="15">
+        <v>5628267899</v>
+      </c>
+      <c r="E80" s="15">
+        <v>5655662541</v>
+      </c>
       <c r="F80" s="15"/>
       <c r="G80" s="15"/>
       <c r="H80" s="15"/>
@@ -3866,10 +3967,18 @@
       <c r="B81" s="13">
         <v>1522020719</v>
       </c>
-      <c r="C81" s="15"/>
-      <c r="D81" s="15"/>
-      <c r="E81" s="15"/>
-      <c r="F81" s="15"/>
+      <c r="C81" s="15">
+        <v>5526616753</v>
+      </c>
+      <c r="D81" s="15">
+        <v>5628263531</v>
+      </c>
+      <c r="E81" s="15">
+        <v>5628264935</v>
+      </c>
+      <c r="F81" s="15">
+        <v>5655660338</v>
+      </c>
       <c r="G81" s="15"/>
       <c r="H81" s="15"/>
       <c r="I81" s="15"/>
@@ -3892,9 +4001,15 @@
       <c r="B82" s="13">
         <v>1522021003</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="15"/>
-      <c r="E82" s="15"/>
+      <c r="C82" s="16">
+        <v>5628266911</v>
+      </c>
+      <c r="D82" s="15">
+        <v>5628264813</v>
+      </c>
+      <c r="E82" s="15">
+        <v>5655655770</v>
+      </c>
       <c r="F82" s="15"/>
       <c r="G82" s="15"/>
       <c r="H82" s="15"/>
@@ -3918,9 +4033,15 @@
       <c r="B83" s="13">
         <v>1522019733</v>
       </c>
-      <c r="C83" s="15"/>
-      <c r="D83" s="15"/>
-      <c r="E83" s="15"/>
+      <c r="C83" s="15">
+        <v>5628267778</v>
+      </c>
+      <c r="D83" s="15">
+        <v>5628267861</v>
+      </c>
+      <c r="E83" s="15">
+        <v>5655656645</v>
+      </c>
       <c r="F83" s="15"/>
       <c r="G83" s="15"/>
       <c r="H83" s="15"/>
@@ -3944,9 +4065,15 @@
       <c r="B84" s="13">
         <v>1522019774</v>
       </c>
-      <c r="C84" s="15"/>
-      <c r="D84" s="15"/>
-      <c r="E84" s="15"/>
+      <c r="C84" s="15">
+        <v>5628266467</v>
+      </c>
+      <c r="D84" s="15">
+        <v>5628263404</v>
+      </c>
+      <c r="E84" s="15">
+        <v>5655660014</v>
+      </c>
       <c r="F84" s="15"/>
       <c r="G84" s="15"/>
       <c r="H84" s="15"/>
@@ -3970,9 +4097,15 @@
       <c r="B85" s="13">
         <v>1522020277</v>
       </c>
-      <c r="C85" s="15"/>
-      <c r="D85" s="15"/>
-      <c r="E85" s="15"/>
+      <c r="C85" s="15">
+        <v>5628265031</v>
+      </c>
+      <c r="D85" s="15">
+        <v>5628267862</v>
+      </c>
+      <c r="E85" s="15">
+        <v>5655662421</v>
+      </c>
       <c r="F85" s="15"/>
       <c r="G85" s="15"/>
       <c r="H85" s="15"/>
@@ -3996,8 +4129,12 @@
       <c r="B86" s="13">
         <v>1522021193</v>
       </c>
-      <c r="C86" s="15"/>
-      <c r="D86" s="15"/>
+      <c r="C86" s="15">
+        <v>5628266572</v>
+      </c>
+      <c r="D86" s="15">
+        <v>5628267545</v>
+      </c>
       <c r="E86" s="15"/>
       <c r="F86" s="15"/>
       <c r="G86" s="15"/>
@@ -4022,10 +4159,18 @@
       <c r="B87" s="13">
         <v>1522020909</v>
       </c>
-      <c r="C87" s="15"/>
-      <c r="D87" s="15"/>
-      <c r="E87" s="15"/>
-      <c r="F87" s="15"/>
+      <c r="C87" s="15">
+        <v>4891848773</v>
+      </c>
+      <c r="D87" s="15">
+        <v>5628261475</v>
+      </c>
+      <c r="E87" s="15">
+        <v>5628263686</v>
+      </c>
+      <c r="F87" s="15">
+        <v>5655660367</v>
+      </c>
       <c r="G87" s="15"/>
       <c r="H87" s="15"/>
       <c r="I87" s="15"/>
@@ -4048,7 +4193,9 @@
       <c r="B88" s="13">
         <v>1522019550</v>
       </c>
-      <c r="C88" s="15"/>
+      <c r="C88" s="15">
+        <v>5628261845</v>
+      </c>
       <c r="D88" s="15"/>
       <c r="E88" s="15"/>
       <c r="F88" s="15"/>
@@ -4100,8 +4247,12 @@
       <c r="B90" s="13">
         <v>1522019564</v>
       </c>
-      <c r="C90" s="15"/>
-      <c r="D90" s="15"/>
+      <c r="C90" s="15">
+        <v>5628267049</v>
+      </c>
+      <c r="D90" s="15">
+        <v>5655658784</v>
+      </c>
       <c r="E90" s="15"/>
       <c r="F90" s="15"/>
       <c r="G90" s="15"/>
@@ -4152,10 +4303,18 @@
       <c r="B92" s="13">
         <v>1522019636</v>
       </c>
-      <c r="C92" s="15"/>
-      <c r="D92" s="15"/>
-      <c r="E92" s="15"/>
-      <c r="F92" s="15"/>
+      <c r="C92" s="15">
+        <v>5526636865</v>
+      </c>
+      <c r="D92" s="15">
+        <v>5628267864</v>
+      </c>
+      <c r="E92" s="15">
+        <v>5628264994</v>
+      </c>
+      <c r="F92" s="15">
+        <v>5655666543</v>
+      </c>
       <c r="G92" s="15"/>
       <c r="H92" s="15"/>
       <c r="I92" s="15"/>
@@ -4178,10 +4337,18 @@
       <c r="B93" s="13">
         <v>1522019666</v>
       </c>
-      <c r="C93" s="15"/>
-      <c r="D93" s="15"/>
-      <c r="E93" s="15"/>
-      <c r="F93" s="15"/>
+      <c r="C93" s="15">
+        <v>5534992435</v>
+      </c>
+      <c r="D93" s="15">
+        <v>4891848437</v>
+      </c>
+      <c r="E93" s="15">
+        <v>5628264629</v>
+      </c>
+      <c r="F93" s="15">
+        <v>5628264778</v>
+      </c>
       <c r="G93" s="15"/>
       <c r="H93" s="15"/>
       <c r="I93" s="15"/>
@@ -4204,9 +4371,15 @@
       <c r="B94" s="13">
         <v>1522019730</v>
       </c>
-      <c r="C94" s="15"/>
-      <c r="D94" s="15"/>
-      <c r="E94" s="15"/>
+      <c r="C94" s="15">
+        <v>5535094833</v>
+      </c>
+      <c r="D94" s="15">
+        <v>5628266397</v>
+      </c>
+      <c r="E94" s="15">
+        <v>5628266511</v>
+      </c>
       <c r="F94" s="15"/>
       <c r="G94" s="15"/>
       <c r="H94" s="15"/>
@@ -4230,8 +4403,12 @@
       <c r="B95" s="13">
         <v>1522019906</v>
       </c>
-      <c r="C95" s="15"/>
-      <c r="D95" s="15"/>
+      <c r="C95" s="15">
+        <v>5628265650</v>
+      </c>
+      <c r="D95" s="15">
+        <v>5628265267</v>
+      </c>
       <c r="E95" s="15"/>
       <c r="F95" s="15"/>
       <c r="G95" s="15"/>
@@ -4256,9 +4433,15 @@
       <c r="B96" s="13">
         <v>1522020325</v>
       </c>
-      <c r="C96" s="15"/>
-      <c r="D96" s="15"/>
-      <c r="E96" s="15"/>
+      <c r="C96" s="15">
+        <v>5628267604</v>
+      </c>
+      <c r="D96" s="15">
+        <v>5628263326</v>
+      </c>
+      <c r="E96" s="15">
+        <v>5655667252</v>
+      </c>
       <c r="F96" s="15"/>
       <c r="G96" s="15"/>
       <c r="H96" s="15"/>
@@ -4282,9 +4465,15 @@
       <c r="B97" s="13">
         <v>1522019613</v>
       </c>
-      <c r="C97" s="15"/>
-      <c r="D97" s="15"/>
-      <c r="E97" s="15"/>
+      <c r="C97" s="15">
+        <v>5628265657</v>
+      </c>
+      <c r="D97" s="15">
+        <v>5628265928</v>
+      </c>
+      <c r="E97" s="15">
+        <v>5655657671</v>
+      </c>
       <c r="F97" s="15"/>
       <c r="G97" s="15"/>
       <c r="H97" s="15"/>
@@ -4308,7 +4497,9 @@
       <c r="B98" s="13">
         <v>1522019292</v>
       </c>
-      <c r="C98" s="15"/>
+      <c r="C98" s="15">
+        <v>5628264812</v>
+      </c>
       <c r="D98" s="15"/>
       <c r="E98" s="15"/>
       <c r="F98" s="15"/>
@@ -4334,10 +4525,18 @@
       <c r="B99" s="13">
         <v>1522020897</v>
       </c>
-      <c r="C99" s="15"/>
-      <c r="D99" s="15"/>
-      <c r="E99" s="15"/>
-      <c r="F99" s="15"/>
+      <c r="C99" s="15">
+        <v>5551374827</v>
+      </c>
+      <c r="D99" s="15">
+        <v>5628265460</v>
+      </c>
+      <c r="E99" s="15">
+        <v>5628269096</v>
+      </c>
+      <c r="F99" s="15">
+        <v>5655665666</v>
+      </c>
       <c r="G99" s="15"/>
       <c r="H99" s="15"/>
       <c r="I99" s="15"/>
@@ -4386,9 +4585,15 @@
       <c r="B101" s="13">
         <v>1522020599</v>
       </c>
-      <c r="C101" s="16"/>
-      <c r="D101" s="15"/>
-      <c r="E101" s="15"/>
+      <c r="C101" s="16">
+        <v>5628267591</v>
+      </c>
+      <c r="D101" s="15">
+        <v>5628266376</v>
+      </c>
+      <c r="E101" s="15">
+        <v>5655658931</v>
+      </c>
       <c r="F101" s="15"/>
       <c r="G101" s="15"/>
       <c r="H101" s="15"/>
@@ -4412,10 +4617,18 @@
       <c r="B102" s="13">
         <v>1522019725</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="15"/>
-      <c r="E102" s="15"/>
-      <c r="F102" s="15"/>
+      <c r="C102" s="16">
+        <v>5535025640</v>
+      </c>
+      <c r="D102" s="15">
+        <v>5628267355</v>
+      </c>
+      <c r="E102" s="15">
+        <v>5628266748</v>
+      </c>
+      <c r="F102" s="15">
+        <v>5655666377</v>
+      </c>
       <c r="G102" s="15"/>
       <c r="H102" s="15"/>
       <c r="I102" s="15"/>
@@ -4438,10 +4651,18 @@
       <c r="B103" s="13">
         <v>1522067175</v>
       </c>
-      <c r="C103" s="15"/>
-      <c r="D103" s="15"/>
-      <c r="E103" s="15"/>
-      <c r="F103" s="15"/>
+      <c r="C103" s="15">
+        <v>5526304024</v>
+      </c>
+      <c r="D103" s="15">
+        <v>5897697939</v>
+      </c>
+      <c r="E103" s="15">
+        <v>5897698368</v>
+      </c>
+      <c r="F103" s="15">
+        <v>4891847609</v>
+      </c>
       <c r="G103" s="15"/>
       <c r="H103" s="15"/>
       <c r="I103" s="15"/>
@@ -4464,11 +4685,21 @@
       <c r="B104" s="13">
         <v>1532938950</v>
       </c>
-      <c r="C104" s="15"/>
-      <c r="D104" s="15"/>
-      <c r="E104" s="15"/>
-      <c r="F104" s="15"/>
-      <c r="G104" s="15"/>
+      <c r="C104" s="15">
+        <v>5526603591</v>
+      </c>
+      <c r="D104" s="15">
+        <v>4891852066</v>
+      </c>
+      <c r="E104" s="15">
+        <v>5628269709</v>
+      </c>
+      <c r="F104" s="15">
+        <v>5628265842</v>
+      </c>
+      <c r="G104" s="15">
+        <v>5655665799</v>
+      </c>
       <c r="H104" s="15"/>
       <c r="I104" s="15"/>
       <c r="J104" s="15"/>
@@ -4490,10 +4721,18 @@
       <c r="B105" s="13">
         <v>1532937945</v>
       </c>
-      <c r="C105" s="15"/>
-      <c r="D105" s="15"/>
-      <c r="E105" s="15"/>
-      <c r="F105" s="15"/>
+      <c r="C105" s="15">
+        <v>5526518592</v>
+      </c>
+      <c r="D105" s="15">
+        <v>5628264786</v>
+      </c>
+      <c r="E105" s="15">
+        <v>5628268193</v>
+      </c>
+      <c r="F105" s="15">
+        <v>5655659283</v>
+      </c>
       <c r="G105" s="15"/>
       <c r="H105" s="15"/>
       <c r="I105" s="15"/>
@@ -4516,8 +4755,12 @@
       <c r="B106" s="13">
         <v>1532936652</v>
       </c>
-      <c r="C106" s="15"/>
-      <c r="D106" s="15"/>
+      <c r="C106" s="15">
+        <v>5550689157</v>
+      </c>
+      <c r="D106" s="15">
+        <v>5739111991</v>
+      </c>
       <c r="E106" s="15"/>
       <c r="F106" s="15"/>
       <c r="G106" s="15"/>
@@ -4542,9 +4785,15 @@
       <c r="B107" s="13">
         <v>1532938508</v>
       </c>
-      <c r="C107" s="15"/>
-      <c r="D107" s="15"/>
-      <c r="E107" s="15"/>
+      <c r="C107" s="15">
+        <v>5628263505</v>
+      </c>
+      <c r="D107" s="15">
+        <v>5628267578</v>
+      </c>
+      <c r="E107" s="15">
+        <v>5655661774</v>
+      </c>
       <c r="F107" s="15"/>
       <c r="G107" s="15"/>
       <c r="H107" s="15"/>
@@ -4594,8 +4843,12 @@
       <c r="B109" s="13">
         <v>1532938265</v>
       </c>
-      <c r="C109" s="15"/>
-      <c r="D109" s="15"/>
+      <c r="C109" s="15">
+        <v>5628265648</v>
+      </c>
+      <c r="D109" s="15">
+        <v>5655657380</v>
+      </c>
       <c r="E109" s="15"/>
       <c r="F109" s="15"/>
       <c r="G109" s="15"/>
@@ -4620,8 +4873,12 @@
       <c r="B110" s="13">
         <v>1532938234</v>
       </c>
-      <c r="C110" s="15"/>
-      <c r="D110" s="15"/>
+      <c r="C110" s="15">
+        <v>5550657136</v>
+      </c>
+      <c r="D110" s="15">
+        <v>5739113055</v>
+      </c>
       <c r="E110" s="15"/>
       <c r="F110" s="15"/>
       <c r="G110" s="15"/>
@@ -4646,7 +4903,9 @@
       <c r="B111" s="13">
         <v>1532937049</v>
       </c>
-      <c r="C111" s="15"/>
+      <c r="C111" s="15">
+        <v>5739111256</v>
+      </c>
       <c r="D111" s="15"/>
       <c r="E111" s="15"/>
       <c r="F111" s="15"/>
@@ -4672,7 +4931,9 @@
       <c r="B112" s="13">
         <v>1532937844</v>
       </c>
-      <c r="C112" s="15"/>
+      <c r="C112" s="15">
+        <v>5739114223</v>
+      </c>
       <c r="D112" s="15"/>
       <c r="E112" s="15"/>
       <c r="F112" s="15"/>
@@ -4724,10 +4985,18 @@
       <c r="B114" s="13">
         <v>1532936693</v>
       </c>
-      <c r="C114" s="15"/>
-      <c r="D114" s="15"/>
-      <c r="E114" s="15"/>
-      <c r="F114" s="15"/>
+      <c r="C114" s="15">
+        <v>5551139783</v>
+      </c>
+      <c r="D114" s="15">
+        <v>1625083201</v>
+      </c>
+      <c r="E114" s="15">
+        <v>2900204768</v>
+      </c>
+      <c r="F114" s="15">
+        <v>5739113981</v>
+      </c>
       <c r="G114" s="15"/>
       <c r="H114" s="15"/>
       <c r="I114" s="15"/>
@@ -4750,7 +5019,9 @@
       <c r="B115" s="13">
         <v>1533013698</v>
       </c>
-      <c r="C115" s="15"/>
+      <c r="C115" s="15">
+        <v>5739116530</v>
+      </c>
       <c r="D115" s="15"/>
       <c r="E115" s="15"/>
       <c r="F115" s="15"/>
@@ -4880,8 +5151,12 @@
       <c r="B120" s="13">
         <v>1532937395</v>
       </c>
-      <c r="C120" s="15"/>
-      <c r="D120" s="15"/>
+      <c r="C120" s="15">
+        <v>5550839654</v>
+      </c>
+      <c r="D120" s="15">
+        <v>5739115870</v>
+      </c>
       <c r="E120" s="15"/>
       <c r="F120" s="15"/>
       <c r="G120" s="15"/>
@@ -4906,7 +5181,9 @@
       <c r="B121" s="13">
         <v>1532936207</v>
       </c>
-      <c r="C121" s="15"/>
+      <c r="C121" s="15">
+        <v>1130307158</v>
+      </c>
       <c r="D121" s="15"/>
       <c r="E121" s="15"/>
       <c r="F121" s="15"/>
@@ -4932,9 +5209,15 @@
       <c r="B122" s="13">
         <v>1532938186</v>
       </c>
-      <c r="C122" s="15"/>
-      <c r="D122" s="15"/>
-      <c r="E122" s="15"/>
+      <c r="C122" s="15">
+        <v>5534823042</v>
+      </c>
+      <c r="D122" s="15">
+        <v>5628262147</v>
+      </c>
+      <c r="E122" s="15">
+        <v>5628267162</v>
+      </c>
       <c r="F122" s="15"/>
       <c r="G122" s="15"/>
       <c r="H122" s="15"/>
@@ -4958,7 +5241,9 @@
       <c r="B123" s="13">
         <v>1532938464</v>
       </c>
-      <c r="C123" s="15"/>
+      <c r="C123" s="15">
+        <v>5739111511</v>
+      </c>
       <c r="D123" s="15"/>
       <c r="E123" s="15"/>
       <c r="F123" s="15"/>
@@ -4984,8 +5269,12 @@
       <c r="B124" s="13">
         <v>1532939087</v>
       </c>
-      <c r="C124" s="15"/>
-      <c r="D124" s="15"/>
+      <c r="C124" s="15">
+        <v>5628262396</v>
+      </c>
+      <c r="D124" s="15">
+        <v>5628264220</v>
+      </c>
       <c r="E124" s="15"/>
       <c r="F124" s="15"/>
       <c r="G124" s="15"/>
@@ -5062,9 +5351,15 @@
       <c r="B127" s="13">
         <v>1532939316</v>
       </c>
-      <c r="C127" s="15"/>
-      <c r="D127" s="15"/>
-      <c r="E127" s="15"/>
+      <c r="C127" s="15">
+        <v>5526461558</v>
+      </c>
+      <c r="D127" s="15">
+        <v>5628265700</v>
+      </c>
+      <c r="E127" s="15">
+        <v>5628266923</v>
+      </c>
       <c r="F127" s="15"/>
       <c r="G127" s="15"/>
       <c r="H127" s="15"/>
@@ -5088,9 +5383,15 @@
       <c r="B128" s="13">
         <v>1532938476</v>
       </c>
-      <c r="C128" s="15"/>
-      <c r="D128" s="15"/>
-      <c r="E128" s="15"/>
+      <c r="C128" s="15">
+        <v>4891846240</v>
+      </c>
+      <c r="D128" s="15">
+        <v>5628260648</v>
+      </c>
+      <c r="E128" s="15">
+        <v>5628262845</v>
+      </c>
       <c r="F128" s="15"/>
       <c r="G128" s="15"/>
       <c r="H128" s="15"/>
@@ -5114,8 +5415,12 @@
       <c r="B129" s="13">
         <v>1532938049</v>
       </c>
-      <c r="C129" s="15"/>
-      <c r="D129" s="15"/>
+      <c r="C129" s="15">
+        <v>5551202044</v>
+      </c>
+      <c r="D129" s="15">
+        <v>5739118091</v>
+      </c>
       <c r="E129" s="15"/>
       <c r="F129" s="15"/>
       <c r="G129" s="15"/>
@@ -5140,10 +5445,18 @@
       <c r="B130" s="13">
         <v>1532938204</v>
       </c>
-      <c r="C130" s="15"/>
-      <c r="D130" s="15"/>
-      <c r="E130" s="15"/>
-      <c r="F130" s="15"/>
+      <c r="C130" s="15">
+        <v>5526592975</v>
+      </c>
+      <c r="D130" s="15">
+        <v>5628264336</v>
+      </c>
+      <c r="E130" s="15">
+        <v>5628263231</v>
+      </c>
+      <c r="F130" s="15">
+        <v>5655661263</v>
+      </c>
       <c r="G130" s="15"/>
       <c r="H130" s="15"/>
       <c r="I130" s="15"/>
@@ -5166,9 +5479,15 @@
       <c r="B131" s="13">
         <v>1532937525</v>
       </c>
-      <c r="C131" s="15"/>
-      <c r="D131" s="15"/>
-      <c r="E131" s="15"/>
+      <c r="C131" s="15">
+        <v>5550654766</v>
+      </c>
+      <c r="D131" s="15">
+        <v>4860836871</v>
+      </c>
+      <c r="E131" s="15">
+        <v>5739114719</v>
+      </c>
       <c r="F131" s="15"/>
       <c r="G131" s="15"/>
       <c r="H131" s="15"/>
@@ -5192,9 +5511,15 @@
       <c r="B132" s="13">
         <v>1532938598</v>
       </c>
-      <c r="C132" s="15"/>
-      <c r="D132" s="15"/>
-      <c r="E132" s="15"/>
+      <c r="C132" s="15">
+        <v>5631040396</v>
+      </c>
+      <c r="D132" s="15">
+        <v>5638865312</v>
+      </c>
+      <c r="E132" s="15">
+        <v>5738219706</v>
+      </c>
       <c r="F132" s="15"/>
       <c r="G132" s="15"/>
       <c r="H132" s="15"/>
@@ -5244,11 +5569,21 @@
       <c r="B134" s="19">
         <v>1532939681</v>
       </c>
-      <c r="C134" s="15"/>
-      <c r="D134" s="15"/>
-      <c r="E134" s="15"/>
-      <c r="F134" s="15"/>
-      <c r="G134" s="15"/>
+      <c r="C134" s="15">
+        <v>5534927651</v>
+      </c>
+      <c r="D134" s="15">
+        <v>4860264628</v>
+      </c>
+      <c r="E134" s="15">
+        <v>4850065510</v>
+      </c>
+      <c r="F134" s="15">
+        <v>6000759047</v>
+      </c>
+      <c r="G134" s="15">
+        <v>6018381214</v>
+      </c>
       <c r="H134" s="15"/>
       <c r="I134" s="15"/>
       <c r="J134" s="15"/>
@@ -5842,8 +6177,12 @@
       <c r="B157" s="13">
         <v>1625431121</v>
       </c>
-      <c r="C157" s="15"/>
-      <c r="D157" s="15"/>
+      <c r="C157" s="15">
+        <v>6000760195</v>
+      </c>
+      <c r="D157" s="15">
+        <v>6018389240</v>
+      </c>
       <c r="E157" s="15"/>
       <c r="F157" s="15"/>
       <c r="G157" s="15"/>
@@ -5868,8 +6207,12 @@
       <c r="B158" s="13">
         <v>1625431048</v>
       </c>
-      <c r="C158" s="15"/>
-      <c r="D158" s="15"/>
+      <c r="C158" s="15">
+        <v>6000754255</v>
+      </c>
+      <c r="D158" s="15">
+        <v>6018380826</v>
+      </c>
       <c r="E158" s="15"/>
       <c r="F158" s="15"/>
       <c r="G158" s="15"/>
@@ -5894,8 +6237,12 @@
       <c r="B159" s="13">
         <v>1626838878</v>
       </c>
-      <c r="C159" s="15"/>
-      <c r="D159" s="15"/>
+      <c r="C159" s="15">
+        <v>6000760308</v>
+      </c>
+      <c r="D159" s="15">
+        <v>6018389560</v>
+      </c>
       <c r="E159" s="15"/>
       <c r="F159" s="15"/>
       <c r="G159" s="15"/>
@@ -5921,17 +6268,11 @@
         <v>1626838871</v>
       </c>
       <c r="C160" s="15">
-        <v>4860264810</v>
-      </c>
-      <c r="D160" s="15">
-        <v>4890100126</v>
-      </c>
-      <c r="E160" s="15">
-        <v>4890110820</v>
-      </c>
-      <c r="F160" s="15">
-        <v>5563962713</v>
-      </c>
+        <v>6000760938</v>
+      </c>
+      <c r="D160" s="15"/>
+      <c r="E160" s="15"/>
+      <c r="F160" s="15"/>
       <c r="G160" s="15"/>
       <c r="H160" s="15"/>
       <c r="I160" s="15"/>
@@ -5955,17 +6296,13 @@
         <v>1626838489</v>
       </c>
       <c r="C161" s="15">
-        <v>5259992780</v>
+        <v>6000753372</v>
       </c>
       <c r="D161" s="15">
-        <v>5868082769</v>
-      </c>
-      <c r="E161" s="15">
-        <v>5868083327</v>
-      </c>
-      <c r="F161" s="15">
-        <v>5563974534</v>
-      </c>
+        <v>6018335909</v>
+      </c>
+      <c r="E161" s="15"/>
+      <c r="F161" s="15"/>
       <c r="G161" s="15"/>
       <c r="H161" s="15"/>
       <c r="I161" s="15"/>
@@ -5989,9 +6326,11 @@
         <v>1626838716</v>
       </c>
       <c r="C162" s="15">
-        <v>5563979496</v>
-      </c>
-      <c r="D162" s="15"/>
+        <v>6000753657</v>
+      </c>
+      <c r="D162" s="15">
+        <v>6018339579</v>
+      </c>
       <c r="E162" s="15"/>
       <c r="F162" s="15"/>
       <c r="G162" s="15"/>
@@ -6017,14 +6356,12 @@
         <v>1626838872</v>
       </c>
       <c r="C163" s="15">
-        <v>4890086083</v>
+        <v>6000753728</v>
       </c>
       <c r="D163" s="15">
-        <v>4890086482</v>
-      </c>
-      <c r="E163" s="15">
-        <v>5563977704</v>
-      </c>
+        <v>6018333775</v>
+      </c>
+      <c r="E163" s="15"/>
       <c r="F163" s="15"/>
       <c r="G163" s="15"/>
       <c r="H163" s="15"/>
@@ -6049,14 +6386,12 @@
         <v>1626838767</v>
       </c>
       <c r="C164" s="15">
-        <v>4890098085</v>
+        <v>6000760013</v>
       </c>
       <c r="D164" s="15">
-        <v>5868067377</v>
-      </c>
-      <c r="E164" s="15">
-        <v>5563976331</v>
-      </c>
+        <v>6018382008</v>
+      </c>
+      <c r="E164" s="15"/>
       <c r="F164" s="15"/>
       <c r="G164" s="15"/>
       <c r="H164" s="15"/>
@@ -6080,18 +6415,10 @@
       <c r="B165" s="13">
         <v>1626838847</v>
       </c>
-      <c r="C165" s="15">
-        <v>4890102327</v>
-      </c>
-      <c r="D165" s="15">
-        <v>5876579984</v>
-      </c>
-      <c r="E165" s="15">
-        <v>5876581229</v>
-      </c>
-      <c r="F165" s="15">
-        <v>5563963226</v>
-      </c>
+      <c r="C165" s="15"/>
+      <c r="D165" s="15"/>
+      <c r="E165" s="15"/>
+      <c r="F165" s="15"/>
       <c r="G165" s="15"/>
       <c r="H165" s="15"/>
       <c r="I165" s="15"/>
@@ -6114,7 +6441,9 @@
       <c r="B166" s="13">
         <v>1626838664</v>
       </c>
-      <c r="C166" s="15"/>
+      <c r="C166" s="15">
+        <v>6018379698</v>
+      </c>
       <c r="D166" s="15"/>
       <c r="E166" s="15"/>
       <c r="F166" s="15"/>
@@ -6140,7 +6469,9 @@
       <c r="B167" s="13">
         <v>1626838959</v>
       </c>
-      <c r="C167" s="15"/>
+      <c r="C167" s="15">
+        <v>6018336743</v>
+      </c>
       <c r="D167" s="15"/>
       <c r="E167" s="15"/>
       <c r="F167" s="15"/>
@@ -6268,18 +6599,10 @@
       <c r="B172" s="13">
         <v>1738651525</v>
       </c>
-      <c r="C172" s="15">
-        <v>4890086750</v>
-      </c>
-      <c r="D172" s="15">
-        <v>5019508589</v>
-      </c>
-      <c r="E172" s="15">
-        <v>5563975017</v>
-      </c>
-      <c r="F172" s="15">
-        <v>5739124078</v>
-      </c>
+      <c r="C172" s="15"/>
+      <c r="D172" s="15"/>
+      <c r="E172" s="15"/>
+      <c r="F172" s="15"/>
       <c r="G172" s="15"/>
       <c r="H172" s="15"/>
       <c r="I172" s="15"/>
@@ -6302,15 +6625,9 @@
       <c r="B173" s="13">
         <v>1738652819</v>
       </c>
-      <c r="C173" s="15">
-        <v>4850064636</v>
-      </c>
-      <c r="D173" s="15">
-        <v>4890103488</v>
-      </c>
-      <c r="E173" s="15">
-        <v>5876597180</v>
-      </c>
+      <c r="C173" s="15"/>
+      <c r="D173" s="15"/>
+      <c r="E173" s="15"/>
       <c r="F173" s="15"/>
       <c r="G173" s="15"/>
       <c r="H173" s="15"/>
@@ -6334,18 +6651,10 @@
       <c r="B174" s="13">
         <v>1738652561</v>
       </c>
-      <c r="C174" s="15">
-        <v>4964346222</v>
-      </c>
-      <c r="D174" s="15">
-        <v>4850067005</v>
-      </c>
-      <c r="E174" s="15">
-        <v>4890089832</v>
-      </c>
-      <c r="F174" s="15">
-        <v>4890096142</v>
-      </c>
+      <c r="C174" s="15"/>
+      <c r="D174" s="15"/>
+      <c r="E174" s="15"/>
+      <c r="F174" s="15"/>
       <c r="G174" s="15"/>
       <c r="H174" s="15"/>
       <c r="I174" s="15"/>
@@ -6368,21 +6677,11 @@
       <c r="B175" s="13">
         <v>1738651871</v>
       </c>
-      <c r="C175" s="15">
-        <v>4964343602</v>
-      </c>
-      <c r="D175" s="15">
-        <v>4860259940</v>
-      </c>
-      <c r="E175" s="15">
-        <v>4890090020</v>
-      </c>
-      <c r="F175" s="15">
-        <v>4890091507</v>
-      </c>
-      <c r="G175" s="15">
-        <v>4890091507</v>
-      </c>
+      <c r="C175" s="15"/>
+      <c r="D175" s="15"/>
+      <c r="E175" s="15"/>
+      <c r="F175" s="15"/>
+      <c r="G175" s="15"/>
       <c r="H175" s="15"/>
       <c r="I175" s="15"/>
       <c r="J175" s="15"/>
@@ -6404,15 +6703,9 @@
       <c r="B176" s="13">
         <v>1738652486</v>
       </c>
-      <c r="C176" s="15">
-        <v>5868092998</v>
-      </c>
-      <c r="D176" s="15">
-        <v>5868090530</v>
-      </c>
-      <c r="E176" s="15">
-        <v>5019794884</v>
-      </c>
+      <c r="C176" s="15"/>
+      <c r="D176" s="15"/>
+      <c r="E176" s="15"/>
       <c r="F176" s="15"/>
       <c r="G176" s="15"/>
       <c r="H176" s="15"/>
@@ -6436,21 +6729,11 @@
       <c r="B177" s="13">
         <v>1738652399</v>
       </c>
-      <c r="C177" s="15">
-        <v>4860258801</v>
-      </c>
-      <c r="D177" s="15">
-        <v>4890091217</v>
-      </c>
-      <c r="E177" s="15">
-        <v>5019506258</v>
-      </c>
-      <c r="F177" s="15">
-        <v>5563973614</v>
-      </c>
-      <c r="G177" s="15">
-        <v>5739123193</v>
-      </c>
+      <c r="C177" s="15"/>
+      <c r="D177" s="15"/>
+      <c r="E177" s="15"/>
+      <c r="F177" s="15"/>
+      <c r="G177" s="15"/>
       <c r="H177" s="15"/>
       <c r="J177" s="15"/>
       <c r="K177" s="15"/>
@@ -6471,27 +6754,8 @@
       <c r="B178" s="13">
         <v>1738651921</v>
       </c>
-      <c r="C178" s="15">
-        <v>4964346295</v>
-      </c>
-      <c r="D178" s="15">
-        <v>4890106703</v>
-      </c>
-      <c r="E178" s="15">
-        <v>4890089950</v>
-      </c>
-      <c r="F178" s="15">
-        <v>5876580455</v>
-      </c>
-      <c r="G178" s="3">
-        <v>5876580627</v>
-      </c>
-      <c r="H178" s="3">
-        <v>5020352125</v>
-      </c>
-      <c r="I178" s="3">
-        <v>5739123681</v>
-      </c>
+      <c r="C178" s="15"/>
+      <c r="D178" s="15"/>
       <c r="J178" s="15"/>
       <c r="K178" s="15"/>
       <c r="L178" s="15"/>
@@ -6511,12 +6775,8 @@
       <c r="B179" s="13">
         <v>1738651917</v>
       </c>
-      <c r="C179" s="15">
-        <v>4860263661</v>
-      </c>
-      <c r="D179" s="15">
-        <v>4890095617</v>
-      </c>
+      <c r="C179" s="15"/>
+      <c r="D179" s="15"/>
       <c r="E179" s="15"/>
       <c r="F179" s="15"/>
       <c r="G179" s="15"/>
@@ -6541,15 +6801,9 @@
       <c r="B180" s="13">
         <v>1738651829</v>
       </c>
-      <c r="C180" s="15">
-        <v>4860257084</v>
-      </c>
-      <c r="D180" s="15">
-        <v>4860259708</v>
-      </c>
-      <c r="E180" s="15">
-        <v>4964343440</v>
-      </c>
+      <c r="C180" s="15"/>
+      <c r="D180" s="15"/>
+      <c r="E180" s="15"/>
       <c r="F180" s="15"/>
       <c r="G180" s="15"/>
       <c r="H180" s="15"/>
@@ -6573,18 +6827,10 @@
       <c r="B181" s="13">
         <v>1738651613</v>
       </c>
-      <c r="C181" s="15">
-        <v>4860265354</v>
-      </c>
-      <c r="D181" s="15">
-        <v>4964343453</v>
-      </c>
-      <c r="E181" s="15">
-        <v>4860259863</v>
-      </c>
-      <c r="F181" s="15">
-        <v>4890089760</v>
-      </c>
+      <c r="C181" s="15"/>
+      <c r="D181" s="15"/>
+      <c r="E181" s="15"/>
+      <c r="F181" s="15"/>
       <c r="G181" s="15"/>
       <c r="H181" s="15"/>
       <c r="I181" s="15"/>
@@ -6633,15 +6879,9 @@
       <c r="B183" s="13">
         <v>1738651975</v>
       </c>
-      <c r="C183" s="15">
-        <v>4964342505</v>
-      </c>
-      <c r="D183" s="15">
-        <v>4890098879</v>
-      </c>
-      <c r="E183" s="15">
-        <v>5020361857</v>
-      </c>
+      <c r="C183" s="15"/>
+      <c r="D183" s="15"/>
+      <c r="E183" s="15"/>
       <c r="F183" s="15"/>
       <c r="G183" s="15"/>
       <c r="H183" s="15"/>
@@ -6665,18 +6905,10 @@
       <c r="B184" s="13">
         <v>1738652535</v>
       </c>
-      <c r="C184" s="15">
-        <v>4890089551</v>
-      </c>
-      <c r="D184" s="15">
-        <v>4915322400</v>
-      </c>
-      <c r="E184" s="15">
-        <v>5868056968</v>
-      </c>
-      <c r="F184" s="15">
-        <v>5868053659</v>
-      </c>
+      <c r="C184" s="15"/>
+      <c r="D184" s="15"/>
+      <c r="E184" s="15"/>
+      <c r="F184" s="15"/>
       <c r="G184" s="15"/>
       <c r="H184" s="15"/>
       <c r="I184" s="15"/>
@@ -6699,15 +6931,9 @@
       <c r="B185" s="13">
         <v>1738652490</v>
       </c>
-      <c r="C185" s="15">
-        <v>4890095156</v>
-      </c>
-      <c r="D185" s="15">
-        <v>5563970965</v>
-      </c>
-      <c r="E185" s="15">
-        <v>5739122882</v>
-      </c>
+      <c r="C185" s="15"/>
+      <c r="D185" s="15"/>
+      <c r="E185" s="15"/>
       <c r="F185" s="15"/>
       <c r="G185" s="15"/>
       <c r="H185" s="15"/>
@@ -6731,12 +6957,8 @@
       <c r="B186" s="13">
         <v>1738651416</v>
       </c>
-      <c r="C186" s="15">
-        <v>4860259602</v>
-      </c>
-      <c r="D186" s="15">
-        <v>4964341621</v>
-      </c>
+      <c r="C186" s="15"/>
+      <c r="D186" s="15"/>
       <c r="E186" s="15"/>
       <c r="F186" s="15"/>
       <c r="G186" s="15"/>
@@ -6761,18 +6983,10 @@
       <c r="B187" s="13">
         <v>1738652147</v>
       </c>
-      <c r="C187" s="15">
-        <v>4850057880</v>
-      </c>
-      <c r="D187" s="15">
-        <v>4860256380</v>
-      </c>
-      <c r="E187" s="15">
-        <v>4964345883</v>
-      </c>
-      <c r="F187" s="15">
-        <v>4890108591</v>
-      </c>
+      <c r="C187" s="15"/>
+      <c r="D187" s="15"/>
+      <c r="E187" s="15"/>
+      <c r="F187" s="15"/>
       <c r="G187" s="15"/>
       <c r="H187" s="15"/>
       <c r="I187" s="15"/>
@@ -6795,15 +7009,9 @@
       <c r="B188" s="13">
         <v>1738652745</v>
       </c>
-      <c r="C188" s="15">
-        <v>4890088766</v>
-      </c>
-      <c r="D188" s="15">
-        <v>4890092483</v>
-      </c>
-      <c r="E188" s="15">
-        <v>5868092421</v>
-      </c>
+      <c r="C188" s="15"/>
+      <c r="D188" s="15"/>
+      <c r="E188" s="15"/>
       <c r="F188" s="15"/>
       <c r="G188" s="15"/>
       <c r="H188" s="15"/>
@@ -6827,15 +7035,9 @@
       <c r="B189" s="13">
         <v>1738652902</v>
       </c>
-      <c r="C189" s="15">
-        <v>4860270967</v>
-      </c>
-      <c r="D189" s="15">
-        <v>4964344959</v>
-      </c>
-      <c r="E189" s="15">
-        <v>4890096730</v>
-      </c>
+      <c r="C189" s="15"/>
+      <c r="D189" s="15"/>
+      <c r="E189" s="15"/>
       <c r="F189" s="15"/>
       <c r="G189" s="15"/>
       <c r="H189" s="15"/>
@@ -6859,18 +7061,10 @@
       <c r="B190" s="13">
         <v>1738653148</v>
       </c>
-      <c r="C190" s="15">
-        <v>5868049911</v>
-      </c>
-      <c r="D190" s="15">
-        <v>5868049626</v>
-      </c>
-      <c r="E190" s="15">
-        <v>5563969425</v>
-      </c>
-      <c r="F190" s="15">
-        <v>5739125769</v>
-      </c>
+      <c r="C190" s="15"/>
+      <c r="D190" s="15"/>
+      <c r="E190" s="15"/>
+      <c r="F190" s="15"/>
       <c r="G190" s="15"/>
       <c r="H190" s="15"/>
       <c r="I190" s="15"/>
@@ -6893,18 +7087,10 @@
       <c r="B191" s="13">
         <v>1738652878</v>
       </c>
-      <c r="C191" s="15">
-        <v>5868061841</v>
-      </c>
-      <c r="D191" s="15">
-        <v>5868065742</v>
-      </c>
-      <c r="E191" s="15">
-        <v>5563975185</v>
-      </c>
-      <c r="F191" s="15">
-        <v>5739122944</v>
-      </c>
+      <c r="C191" s="15"/>
+      <c r="D191" s="15"/>
+      <c r="E191" s="15"/>
+      <c r="F191" s="15"/>
       <c r="G191" s="15"/>
       <c r="H191" s="15"/>
       <c r="I191" s="15"/>
@@ -6952,21 +7138,11 @@
       <c r="B193" s="13">
         <v>1738651926</v>
       </c>
-      <c r="C193" s="15">
-        <v>4964347571</v>
-      </c>
-      <c r="D193" s="15">
-        <v>4890106754</v>
-      </c>
-      <c r="E193" s="15">
-        <v>4915353873</v>
-      </c>
-      <c r="F193" s="15">
-        <v>5563967751</v>
-      </c>
-      <c r="G193" s="15">
-        <v>5739125473</v>
-      </c>
+      <c r="C193" s="15"/>
+      <c r="D193" s="15"/>
+      <c r="E193" s="15"/>
+      <c r="F193" s="15"/>
+      <c r="G193" s="15"/>
       <c r="H193" s="15"/>
       <c r="I193" s="15"/>
       <c r="J193" s="15"/>
@@ -6988,21 +7164,11 @@
       <c r="B194" s="13">
         <v>1738652063</v>
       </c>
-      <c r="C194" s="15">
-        <v>4964343337</v>
-      </c>
-      <c r="D194" s="15">
-        <v>5868040467</v>
-      </c>
-      <c r="E194" s="15">
-        <v>5019830078</v>
-      </c>
-      <c r="F194" s="15">
-        <v>5563967919</v>
-      </c>
-      <c r="G194" s="15">
-        <v>5739127911</v>
-      </c>
+      <c r="C194" s="15"/>
+      <c r="D194" s="15"/>
+      <c r="E194" s="15"/>
+      <c r="F194" s="15"/>
+      <c r="G194" s="15"/>
       <c r="H194" s="15"/>
       <c r="I194" s="15"/>
       <c r="J194" s="15"/>
@@ -7024,15 +7190,9 @@
       <c r="B195" s="13">
         <v>1738652367</v>
       </c>
-      <c r="C195" s="15">
-        <v>5019506503</v>
-      </c>
-      <c r="D195" s="15">
-        <v>5563974252</v>
-      </c>
-      <c r="E195" s="15">
-        <v>5739122067</v>
-      </c>
+      <c r="C195" s="15"/>
+      <c r="D195" s="15"/>
+      <c r="E195" s="15"/>
       <c r="F195" s="15"/>
       <c r="G195" s="15"/>
       <c r="H195" s="15"/>
@@ -7134,9 +7294,7 @@
       <c r="B199" s="13">
         <v>1750746301</v>
       </c>
-      <c r="C199" s="15">
-        <v>5550877291</v>
-      </c>
+      <c r="C199" s="15"/>
       <c r="D199" s="15"/>
       <c r="E199" s="15"/>
       <c r="F199" s="15"/>
@@ -7188,12 +7346,8 @@
       <c r="B201" s="13">
         <v>1750745576</v>
       </c>
-      <c r="C201" s="15">
-        <v>5550899733</v>
-      </c>
-      <c r="D201" s="15">
-        <v>4860833835</v>
-      </c>
+      <c r="C201" s="15"/>
+      <c r="D201" s="15"/>
       <c r="E201" s="15"/>
       <c r="F201" s="15"/>
       <c r="G201" s="15"/>
@@ -7218,18 +7372,10 @@
       <c r="B202" s="13">
         <v>1849771468</v>
       </c>
-      <c r="C202" s="15">
-        <v>5052626728</v>
-      </c>
-      <c r="D202" s="15">
-        <v>4860257053</v>
-      </c>
-      <c r="E202" s="15">
-        <v>4860257462</v>
-      </c>
-      <c r="F202" s="15">
-        <v>4850055969</v>
-      </c>
+      <c r="C202" s="15"/>
+      <c r="D202" s="15"/>
+      <c r="E202" s="15"/>
+      <c r="F202" s="15"/>
       <c r="G202" s="15"/>
       <c r="H202" s="15"/>
       <c r="I202" s="15"/>
@@ -7252,21 +7398,11 @@
       <c r="B203" s="13">
         <v>1849777829</v>
       </c>
-      <c r="C203" s="15">
-        <v>5534854487</v>
-      </c>
-      <c r="D203" s="15">
-        <v>5052657579</v>
-      </c>
-      <c r="E203" s="15">
-        <v>4850070999</v>
-      </c>
-      <c r="F203" s="15">
-        <v>4860259102</v>
-      </c>
-      <c r="G203" s="15">
-        <v>4860263157</v>
-      </c>
+      <c r="C203" s="15"/>
+      <c r="D203" s="15"/>
+      <c r="E203" s="15"/>
+      <c r="F203" s="15"/>
+      <c r="G203" s="15"/>
       <c r="H203" s="15"/>
       <c r="I203" s="15"/>
       <c r="J203" s="15"/>
@@ -7288,15 +7424,9 @@
       <c r="B204" s="13">
         <v>1849777981</v>
       </c>
-      <c r="C204" s="15">
-        <v>5052686555</v>
-      </c>
-      <c r="D204" s="15">
-        <v>5526286446</v>
-      </c>
-      <c r="E204" s="15">
-        <v>4850080183</v>
-      </c>
+      <c r="C204" s="15"/>
+      <c r="D204" s="15"/>
+      <c r="E204" s="15"/>
       <c r="F204" s="15"/>
       <c r="G204" s="15"/>
       <c r="H204" s="15"/>
@@ -7320,21 +7450,11 @@
       <c r="B205" s="13">
         <v>1849778110</v>
       </c>
-      <c r="C205" s="15">
-        <v>5535486927</v>
-      </c>
-      <c r="D205" s="15">
-        <v>5052691191</v>
-      </c>
-      <c r="E205" s="15">
-        <v>5152127710</v>
-      </c>
-      <c r="F205" s="15">
-        <v>5152127710</v>
-      </c>
-      <c r="G205" s="15">
-        <v>4850073051</v>
-      </c>
+      <c r="C205" s="15"/>
+      <c r="D205" s="15"/>
+      <c r="E205" s="15"/>
+      <c r="F205" s="15"/>
+      <c r="G205" s="15"/>
       <c r="H205" s="15"/>
       <c r="I205" s="15"/>
       <c r="J205" s="15"/>
@@ -7356,18 +7476,10 @@
       <c r="B206" s="13">
         <v>1849777791</v>
       </c>
-      <c r="C206" s="15">
-        <v>4850068837</v>
-      </c>
-      <c r="D206" s="15">
-        <v>4860265890</v>
-      </c>
-      <c r="E206" s="15">
-        <v>4890102570</v>
-      </c>
-      <c r="F206" s="15">
-        <v>4890098701</v>
-      </c>
+      <c r="C206" s="15"/>
+      <c r="D206" s="15"/>
+      <c r="E206" s="15"/>
+      <c r="F206" s="15"/>
       <c r="G206" s="15"/>
       <c r="H206" s="15"/>
       <c r="I206" s="15"/>
@@ -7390,15 +7502,9 @@
       <c r="B207" s="13">
         <v>1849777893</v>
       </c>
-      <c r="C207" s="15">
-        <v>5052691323</v>
-      </c>
-      <c r="D207" s="15">
-        <v>4850070619</v>
-      </c>
-      <c r="E207" s="15">
-        <v>4850082845</v>
-      </c>
+      <c r="C207" s="15"/>
+      <c r="D207" s="15"/>
+      <c r="E207" s="15"/>
       <c r="F207" s="15"/>
       <c r="G207" s="15"/>
       <c r="H207" s="15"/>
@@ -7422,18 +7528,10 @@
       <c r="B208" s="13">
         <v>1849777815</v>
       </c>
-      <c r="C208" s="15">
-        <v>5152590675</v>
-      </c>
-      <c r="D208" s="15">
-        <v>5526410659</v>
-      </c>
-      <c r="E208" s="15">
-        <v>4860352054</v>
-      </c>
-      <c r="F208" s="15">
-        <v>4860354079</v>
-      </c>
+      <c r="C208" s="15"/>
+      <c r="D208" s="15"/>
+      <c r="E208" s="15"/>
+      <c r="F208" s="15"/>
       <c r="G208" s="15"/>
       <c r="H208" s="15"/>
       <c r="I208" s="15"/>
@@ -7456,24 +7554,12 @@
       <c r="B209" s="13">
         <v>1849777581</v>
       </c>
-      <c r="C209" s="15">
-        <v>5052650742</v>
-      </c>
-      <c r="D209" s="15">
-        <v>5526350580</v>
-      </c>
-      <c r="E209" s="15">
-        <v>5151978855</v>
-      </c>
-      <c r="F209" s="15">
-        <v>4850061237</v>
-      </c>
-      <c r="G209" s="15">
-        <v>4850072095</v>
-      </c>
-      <c r="H209" s="15">
-        <v>4860261667</v>
-      </c>
+      <c r="C209" s="15"/>
+      <c r="D209" s="15"/>
+      <c r="E209" s="15"/>
+      <c r="F209" s="15"/>
+      <c r="G209" s="15"/>
+      <c r="H209" s="15"/>
       <c r="I209" s="15"/>
       <c r="J209" s="15"/>
       <c r="K209" s="15"/>
@@ -7494,21 +7580,9 @@
       <c r="B210" s="13">
         <v>1849777716</v>
       </c>
-      <c r="C210" s="15">
-        <v>5052637004</v>
-      </c>
-      <c r="D210" s="15">
-        <v>5151992169</v>
-      </c>
-      <c r="E210" s="15">
-        <v>4860258515</v>
-      </c>
-      <c r="F210" s="15">
-        <v>4890095766</v>
-      </c>
-      <c r="G210" s="15">
-        <v>4890100064</v>
-      </c>
+      <c r="C210" s="15"/>
+      <c r="D210" s="15"/>
+      <c r="E210" s="15"/>
       <c r="H210" s="15"/>
       <c r="I210" s="15"/>
       <c r="J210" s="15"/>
@@ -7530,24 +7604,9 @@
       <c r="B211" s="13">
         <v>1849777650</v>
       </c>
-      <c r="C211" s="15">
-        <v>5052714253</v>
-      </c>
-      <c r="D211" s="15">
-        <v>4860267881</v>
-      </c>
-      <c r="E211" s="15">
-        <v>4890100795</v>
-      </c>
-      <c r="F211" s="15">
-        <v>5876604052</v>
-      </c>
-      <c r="G211" s="15">
-        <v>5876602738</v>
-      </c>
-      <c r="H211" s="15">
-        <v>5563962115</v>
-      </c>
+      <c r="C211" s="15"/>
+      <c r="D211" s="15"/>
+      <c r="E211" s="15"/>
       <c r="I211" s="15"/>
       <c r="J211" s="15"/>
       <c r="K211" s="15"/>
@@ -7568,15 +7627,9 @@
       <c r="B212" s="13">
         <v>1849778040</v>
       </c>
-      <c r="C212" s="15">
-        <v>5052649542</v>
-      </c>
-      <c r="D212" s="15">
-        <v>5151941910</v>
-      </c>
-      <c r="E212" s="15">
-        <v>4850055818</v>
-      </c>
+      <c r="C212" s="15"/>
+      <c r="D212" s="15"/>
+      <c r="E212" s="15"/>
       <c r="F212" s="15"/>
       <c r="G212" s="15"/>
       <c r="H212" s="15"/>
@@ -7600,18 +7653,10 @@
       <c r="B213" s="13">
         <v>1849777940</v>
       </c>
-      <c r="C213" s="15">
-        <v>5526480988</v>
-      </c>
-      <c r="D213" s="15">
-        <v>5052684087</v>
-      </c>
-      <c r="E213" s="15">
-        <v>4850059812</v>
-      </c>
-      <c r="F213" s="15">
-        <v>4860260473</v>
-      </c>
+      <c r="C213" s="15"/>
+      <c r="D213" s="15"/>
+      <c r="E213" s="15"/>
+      <c r="F213" s="15"/>
       <c r="G213" s="15"/>
       <c r="H213" s="15"/>
       <c r="I213" s="15"/>
@@ -7634,18 +7679,10 @@
       <c r="B214" s="13">
         <v>1849778044</v>
       </c>
-      <c r="C214" s="15">
-        <v>5534569906</v>
-      </c>
-      <c r="D214" s="15">
-        <v>5052680357</v>
-      </c>
-      <c r="E214" s="15">
-        <v>4850069652</v>
-      </c>
-      <c r="F214" s="15">
-        <v>4860264759</v>
-      </c>
+      <c r="C214" s="15"/>
+      <c r="D214" s="15"/>
+      <c r="E214" s="15"/>
+      <c r="F214" s="15"/>
       <c r="G214" s="15"/>
       <c r="H214" s="15"/>
       <c r="I214" s="15"/>
@@ -7668,12 +7705,8 @@
       <c r="B215" s="13">
         <v>1849777586</v>
       </c>
-      <c r="C215" s="15">
-        <v>5052687037</v>
-      </c>
-      <c r="D215" s="15">
-        <v>5052687037</v>
-      </c>
+      <c r="C215" s="15"/>
+      <c r="D215" s="15"/>
       <c r="E215" s="15"/>
       <c r="F215" s="15"/>
       <c r="G215" s="15"/>
@@ -7698,18 +7731,10 @@
       <c r="B216" s="13">
         <v>1849778023</v>
       </c>
-      <c r="C216" s="15">
-        <v>5052661484</v>
-      </c>
-      <c r="D216" s="15">
-        <v>4860260190</v>
-      </c>
-      <c r="E216" s="15">
-        <v>4860268434</v>
-      </c>
-      <c r="F216" s="15">
-        <v>5563972066</v>
-      </c>
+      <c r="C216" s="15"/>
+      <c r="D216" s="15"/>
+      <c r="E216" s="15"/>
+      <c r="F216" s="15"/>
       <c r="G216" s="15"/>
       <c r="H216" s="15"/>
       <c r="I216" s="15"/>
@@ -7732,18 +7757,10 @@
       <c r="B217" s="13">
         <v>1849777600</v>
       </c>
-      <c r="C217" s="15">
-        <v>5534874952</v>
-      </c>
-      <c r="D217" s="15">
-        <v>5052648548</v>
-      </c>
-      <c r="E217" s="15">
-        <v>4860260217</v>
-      </c>
-      <c r="F217" s="15">
-        <v>4860261398</v>
-      </c>
+      <c r="C217" s="15"/>
+      <c r="D217" s="15"/>
+      <c r="E217" s="15"/>
+      <c r="F217" s="15"/>
       <c r="G217" s="15"/>
       <c r="H217" s="15"/>
       <c r="I217" s="15"/>
@@ -7766,21 +7783,11 @@
       <c r="B218" s="13">
         <v>1849777647</v>
       </c>
-      <c r="C218" s="15">
-        <v>5526395826</v>
-      </c>
-      <c r="D218" s="15">
-        <v>5052620393</v>
-      </c>
-      <c r="E218" s="15">
-        <v>5151983412</v>
-      </c>
-      <c r="F218" s="15">
-        <v>4850054200</v>
-      </c>
-      <c r="G218" s="15">
-        <v>4860257545</v>
-      </c>
+      <c r="C218" s="15"/>
+      <c r="D218" s="15"/>
+      <c r="E218" s="15"/>
+      <c r="F218" s="15"/>
+      <c r="G218" s="15"/>
       <c r="H218" s="15"/>
       <c r="I218" s="15"/>
       <c r="J218" s="15"/>
@@ -7802,15 +7809,9 @@
       <c r="B219" s="13">
         <v>1849777720</v>
       </c>
-      <c r="C219" s="15">
-        <v>5534806044</v>
-      </c>
-      <c r="D219" s="15">
-        <v>5052687056</v>
-      </c>
-      <c r="E219" s="15">
-        <v>4850079803</v>
-      </c>
+      <c r="C219" s="15"/>
+      <c r="D219" s="15"/>
+      <c r="E219" s="15"/>
       <c r="F219" s="15"/>
       <c r="G219" s="15"/>
       <c r="H219" s="15"/>
@@ -7834,21 +7835,11 @@
       <c r="B220" s="13">
         <v>1849777551</v>
       </c>
-      <c r="C220" s="15">
-        <v>5534713003</v>
-      </c>
-      <c r="D220" s="15">
-        <v>5052632931</v>
-      </c>
-      <c r="E220" s="15">
-        <v>4850110100</v>
-      </c>
-      <c r="F220" s="15">
-        <v>4860275725</v>
-      </c>
-      <c r="G220" s="15">
-        <v>4860282553</v>
-      </c>
+      <c r="C220" s="15"/>
+      <c r="D220" s="15"/>
+      <c r="E220" s="15"/>
+      <c r="F220" s="15"/>
+      <c r="G220" s="15"/>
       <c r="H220" s="15"/>
       <c r="I220" s="15"/>
       <c r="J220" s="15"/>
@@ -7870,18 +7861,10 @@
       <c r="B221" s="13">
         <v>1849778151</v>
       </c>
-      <c r="C221" s="15">
-        <v>5052655978</v>
-      </c>
-      <c r="D221" s="15">
-        <v>5534874064</v>
-      </c>
-      <c r="E221" s="15">
-        <v>4860258048</v>
-      </c>
-      <c r="F221" s="15">
-        <v>4860259864</v>
-      </c>
+      <c r="C221" s="15"/>
+      <c r="D221" s="15"/>
+      <c r="E221" s="15"/>
+      <c r="F221" s="15"/>
       <c r="G221" s="15"/>
       <c r="H221" s="15"/>
       <c r="I221" s="15"/>
@@ -7904,18 +7887,10 @@
       <c r="B222" s="13">
         <v>1849777651</v>
       </c>
-      <c r="C222" s="15">
-        <v>5526339780</v>
-      </c>
-      <c r="D222" s="15">
-        <v>5052637156</v>
-      </c>
-      <c r="E222" s="15">
-        <v>4850060262</v>
-      </c>
-      <c r="F222" s="15">
-        <v>4860262354</v>
-      </c>
+      <c r="C222" s="15"/>
+      <c r="D222" s="15"/>
+      <c r="E222" s="15"/>
+      <c r="F222" s="15"/>
       <c r="G222" s="15"/>
       <c r="H222" s="15"/>
       <c r="I222" s="15"/>
@@ -7938,21 +7913,11 @@
       <c r="B223" s="13">
         <v>1849777656</v>
       </c>
-      <c r="C223" s="15">
-        <v>4860258314</v>
-      </c>
-      <c r="D223" s="15">
-        <v>4860258331</v>
-      </c>
-      <c r="E223" s="15">
-        <v>4890107681</v>
-      </c>
-      <c r="F223" s="15">
-        <v>4890102085</v>
-      </c>
-      <c r="G223" s="15">
-        <v>5563976036</v>
-      </c>
+      <c r="C223" s="15"/>
+      <c r="D223" s="15"/>
+      <c r="E223" s="15"/>
+      <c r="F223" s="15"/>
+      <c r="G223" s="15"/>
       <c r="H223" s="15"/>
       <c r="I223" s="15"/>
       <c r="J223" s="15"/>
@@ -7974,15 +7939,9 @@
       <c r="B224" s="13">
         <v>1849777833</v>
       </c>
-      <c r="C224" s="15">
-        <v>4860260536</v>
-      </c>
-      <c r="D224" s="15">
-        <v>4890091018</v>
-      </c>
-      <c r="E224" s="15">
-        <v>4890097690</v>
-      </c>
+      <c r="C224" s="15"/>
+      <c r="D224" s="15"/>
+      <c r="E224" s="15"/>
       <c r="F224" s="15"/>
       <c r="G224" s="15"/>
       <c r="H224" s="15"/>
@@ -8006,27 +7965,13 @@
       <c r="B225" s="13">
         <v>1849777906</v>
       </c>
-      <c r="C225" s="15">
-        <v>4850062482</v>
-      </c>
-      <c r="D225" s="15">
-        <v>4860264003</v>
-      </c>
-      <c r="E225" s="15">
-        <v>4890100271</v>
-      </c>
-      <c r="F225" s="15">
-        <v>4890112252</v>
-      </c>
-      <c r="G225" s="15">
-        <v>5876595389</v>
-      </c>
-      <c r="H225" s="15">
-        <v>5876595709</v>
-      </c>
-      <c r="I225" s="15">
-        <v>5563972627</v>
-      </c>
+      <c r="C225" s="15"/>
+      <c r="D225" s="15"/>
+      <c r="E225" s="15"/>
+      <c r="F225" s="15"/>
+      <c r="G225" s="15"/>
+      <c r="H225" s="15"/>
+      <c r="I225" s="15"/>
       <c r="J225" s="15"/>
       <c r="K225" s="15"/>
       <c r="L225" s="15"/>
@@ -8046,18 +7991,10 @@
       <c r="B226" s="13">
         <v>1849777862</v>
       </c>
-      <c r="C226" s="15">
-        <v>4860265158</v>
-      </c>
-      <c r="D226" s="15">
-        <v>4890098945</v>
-      </c>
-      <c r="E226" s="15">
-        <v>4890099372</v>
-      </c>
-      <c r="F226" s="15">
-        <v>5563963162</v>
-      </c>
+      <c r="C226" s="15"/>
+      <c r="D226" s="15"/>
+      <c r="E226" s="15"/>
+      <c r="F226" s="15"/>
       <c r="G226" s="15"/>
       <c r="H226" s="15"/>
       <c r="I226" s="15"/>
@@ -8080,12 +8017,8 @@
       <c r="B227" s="13">
         <v>1912188679</v>
       </c>
-      <c r="C227" s="15">
-        <v>5551173838</v>
-      </c>
-      <c r="D227" s="15">
-        <v>5739121495</v>
-      </c>
+      <c r="C227" s="15"/>
+      <c r="D227" s="15"/>
       <c r="E227" s="15"/>
       <c r="F227" s="15"/>
       <c r="G227" s="15"/>
@@ -8110,12 +8043,8 @@
       <c r="B228" s="13">
         <v>1912201998</v>
       </c>
-      <c r="C228" s="15">
-        <v>5563647206</v>
-      </c>
-      <c r="D228" s="15">
-        <v>5739119047</v>
-      </c>
+      <c r="C228" s="15"/>
+      <c r="D228" s="15"/>
       <c r="E228" s="15"/>
       <c r="F228" s="15"/>
       <c r="G228" s="15"/>
@@ -8712,15 +8641,9 @@
       <c r="B251" s="13">
         <v>2449977854</v>
       </c>
-      <c r="C251" s="15">
-        <v>5876580602</v>
-      </c>
-      <c r="D251" s="15">
-        <v>5876580644</v>
-      </c>
-      <c r="E251" s="15">
-        <v>5563954693</v>
-      </c>
+      <c r="C251" s="15"/>
+      <c r="D251" s="15"/>
+      <c r="E251" s="15"/>
       <c r="F251" s="15"/>
       <c r="G251" s="15"/>
       <c r="H251" s="15"/>
@@ -8745,15 +8668,9 @@
       <c r="B252" s="13">
         <v>2449977213</v>
       </c>
-      <c r="C252" s="15">
-        <v>4850253942</v>
-      </c>
-      <c r="D252" s="15">
-        <v>4927494497</v>
-      </c>
-      <c r="E252" s="15">
-        <v>5563955988</v>
-      </c>
+      <c r="C252" s="15"/>
+      <c r="D252" s="15"/>
+      <c r="E252" s="15"/>
       <c r="F252" s="15"/>
       <c r="G252" s="15"/>
       <c r="H252" s="15"/>
@@ -8778,21 +8695,11 @@
       <c r="B253" s="13">
         <v>2449975997</v>
       </c>
-      <c r="C253" s="15">
-        <v>4850286060</v>
-      </c>
-      <c r="D253" s="15">
-        <v>4860282949</v>
-      </c>
-      <c r="E253" s="15">
-        <v>5051048783</v>
-      </c>
-      <c r="F253" s="15">
-        <v>4850265777</v>
-      </c>
-      <c r="G253" s="15">
-        <v>5563955456</v>
-      </c>
+      <c r="C253" s="15"/>
+      <c r="D253" s="15"/>
+      <c r="E253" s="15"/>
+      <c r="F253" s="15"/>
+      <c r="G253" s="15"/>
       <c r="H253" s="15"/>
       <c r="I253" s="15"/>
       <c r="J253" s="15"/>
@@ -8815,24 +8722,12 @@
       <c r="B254" s="13">
         <v>2449977489</v>
       </c>
-      <c r="C254" s="15">
-        <v>4860283612</v>
-      </c>
-      <c r="D254" s="15">
-        <v>5051051826</v>
-      </c>
-      <c r="E254" s="15">
-        <v>5051054047</v>
-      </c>
-      <c r="F254" s="15">
-        <v>4927493660</v>
-      </c>
-      <c r="G254" s="15">
-        <v>5876616021</v>
-      </c>
-      <c r="H254" s="15">
-        <v>5563955694</v>
-      </c>
+      <c r="C254" s="15"/>
+      <c r="D254" s="15"/>
+      <c r="E254" s="15"/>
+      <c r="F254" s="15"/>
+      <c r="G254" s="15"/>
+      <c r="H254" s="15"/>
       <c r="I254" s="15"/>
       <c r="J254" s="15"/>
       <c r="K254" s="15"/>
@@ -8854,15 +8749,9 @@
       <c r="B255" s="13">
         <v>2449979646</v>
       </c>
-      <c r="C255" s="15">
-        <v>5876620563</v>
-      </c>
-      <c r="D255" s="15">
-        <v>5876621588</v>
-      </c>
-      <c r="E255" s="15">
-        <v>5563955773</v>
-      </c>
+      <c r="C255" s="15"/>
+      <c r="D255" s="15"/>
+      <c r="E255" s="15"/>
       <c r="F255" s="15"/>
       <c r="G255" s="15"/>
       <c r="H255" s="15"/>
@@ -8887,15 +8776,9 @@
       <c r="B256" s="13">
         <v>2449977972</v>
       </c>
-      <c r="C256" s="16">
-        <v>4860283801</v>
-      </c>
-      <c r="D256" s="15">
-        <v>4927491947</v>
-      </c>
-      <c r="E256" s="15">
-        <v>5563961658</v>
-      </c>
+      <c r="C256" s="16"/>
+      <c r="D256" s="15"/>
+      <c r="E256" s="15"/>
       <c r="F256" s="15"/>
       <c r="G256" s="15"/>
       <c r="H256" s="15"/>
@@ -8920,24 +8803,9 @@
       <c r="B257" s="13">
         <v>2449976830</v>
       </c>
-      <c r="C257" s="15">
-        <v>5051088866</v>
-      </c>
-      <c r="D257" s="15">
-        <v>4927493895</v>
-      </c>
-      <c r="E257" s="15">
-        <v>5868062209</v>
-      </c>
-      <c r="F257" s="15">
-        <v>5868064684</v>
-      </c>
-      <c r="G257" s="15">
-        <v>5563953061</v>
-      </c>
-      <c r="H257" s="15">
-        <v>5682479041</v>
-      </c>
+      <c r="C257" s="15"/>
+      <c r="D257" s="15"/>
+      <c r="E257" s="15"/>
       <c r="I257" s="15"/>
       <c r="J257" s="15"/>
       <c r="K257" s="15"/>
@@ -9094,12 +8962,8 @@
       <c r="B263" s="13">
         <v>2449977812</v>
       </c>
-      <c r="C263" s="16">
-        <v>4860284593</v>
-      </c>
-      <c r="D263" s="15">
-        <v>5563956295</v>
-      </c>
+      <c r="C263" s="16"/>
+      <c r="D263" s="15"/>
       <c r="E263" s="15"/>
       <c r="F263" s="15"/>
       <c r="G263" s="15"/>
@@ -9125,21 +8989,11 @@
       <c r="B264" s="13">
         <v>2449977848</v>
       </c>
-      <c r="C264" s="15">
-        <v>4860278760</v>
-      </c>
-      <c r="D264" s="15">
-        <v>5051048805</v>
-      </c>
-      <c r="E264" s="15">
-        <v>5167590180</v>
-      </c>
-      <c r="F264" s="15">
-        <v>5563961820</v>
-      </c>
-      <c r="G264" s="15">
-        <v>5591605465</v>
-      </c>
+      <c r="C264" s="15"/>
+      <c r="D264" s="15"/>
+      <c r="E264" s="15"/>
+      <c r="F264" s="15"/>
+      <c r="G264" s="15"/>
       <c r="H264" s="15"/>
       <c r="I264" s="15"/>
       <c r="J264" s="15"/>
@@ -9324,18 +9178,10 @@
       <c r="B271" s="13">
         <v>2449976986</v>
       </c>
-      <c r="C271" s="15">
-        <v>5051072453</v>
-      </c>
-      <c r="D271" s="15">
-        <v>5876578431</v>
-      </c>
-      <c r="E271" s="15">
-        <v>5876580808</v>
-      </c>
-      <c r="F271" s="15">
-        <v>5563954738</v>
-      </c>
+      <c r="C271" s="15"/>
+      <c r="D271" s="15"/>
+      <c r="E271" s="15"/>
+      <c r="F271" s="15"/>
       <c r="G271" s="15"/>
       <c r="H271" s="15"/>
       <c r="I271" s="15"/>
@@ -9359,12 +9205,8 @@
       <c r="B272" s="13">
         <v>2449979595</v>
       </c>
-      <c r="C272" s="15">
-        <v>4860284687</v>
-      </c>
-      <c r="D272" s="15">
-        <v>4927495338</v>
-      </c>
+      <c r="C272" s="15"/>
+      <c r="D272" s="15"/>
       <c r="E272" s="15"/>
       <c r="F272" s="15"/>
       <c r="G272" s="15"/>
@@ -9390,18 +9232,10 @@
       <c r="B273" s="13">
         <v>2449977394</v>
       </c>
-      <c r="C273" s="15">
-        <v>4860281785</v>
-      </c>
-      <c r="D273" s="15">
-        <v>4927493213</v>
-      </c>
-      <c r="E273" s="15">
-        <v>5876581017</v>
-      </c>
-      <c r="F273" s="15">
-        <v>5876581219</v>
-      </c>
+      <c r="C273" s="15"/>
+      <c r="D273" s="15"/>
+      <c r="E273" s="15"/>
+      <c r="F273" s="15"/>
       <c r="G273" s="15"/>
       <c r="H273" s="15"/>
       <c r="I273" s="15"/>
@@ -9452,21 +9286,11 @@
       <c r="B275" s="13">
         <v>2449977131</v>
       </c>
-      <c r="C275" s="15">
-        <v>5868030126</v>
-      </c>
-      <c r="D275" s="15">
-        <v>5868030966</v>
-      </c>
-      <c r="E275" s="15">
-        <v>5563955460</v>
-      </c>
-      <c r="F275" s="15">
-        <v>5682480813</v>
-      </c>
-      <c r="G275" s="15">
-        <v>5640688090</v>
-      </c>
+      <c r="C275" s="15"/>
+      <c r="D275" s="15"/>
+      <c r="E275" s="15"/>
+      <c r="F275" s="15"/>
+      <c r="G275" s="15"/>
       <c r="H275" s="15"/>
       <c r="I275" s="15"/>
       <c r="J275" s="15"/>
@@ -9489,15 +9313,9 @@
       <c r="B276" s="13">
         <v>2449977197</v>
       </c>
-      <c r="C276" s="15">
-        <v>5526236946</v>
-      </c>
-      <c r="D276" s="15">
-        <v>4850256119</v>
-      </c>
-      <c r="E276" s="15">
-        <v>4927492397</v>
-      </c>
+      <c r="C276" s="15"/>
+      <c r="D276" s="15"/>
+      <c r="E276" s="15"/>
       <c r="F276" s="15"/>
       <c r="G276" s="15"/>
       <c r="H276" s="15"/>
@@ -9549,12 +9367,8 @@
       <c r="B278" s="13">
         <v>2449977090</v>
       </c>
-      <c r="C278" s="15">
-        <v>4927491875</v>
-      </c>
-      <c r="D278" s="15">
-        <v>5876614967</v>
-      </c>
+      <c r="C278" s="15"/>
+      <c r="D278" s="15"/>
       <c r="E278" s="15"/>
       <c r="F278" s="15"/>
       <c r="G278" s="15"/>
@@ -9580,18 +9394,10 @@
       <c r="B279" s="13">
         <v>2449977863</v>
       </c>
-      <c r="C279" s="15">
-        <v>4927494198</v>
-      </c>
-      <c r="D279" s="15">
-        <v>4860283040</v>
-      </c>
-      <c r="E279" s="15">
-        <v>5051068883</v>
-      </c>
-      <c r="F279" s="15">
-        <v>5640688760</v>
-      </c>
+      <c r="C279" s="15"/>
+      <c r="D279" s="15"/>
+      <c r="E279" s="15"/>
+      <c r="F279" s="15"/>
       <c r="G279" s="15"/>
       <c r="H279" s="15"/>
       <c r="I279" s="15"/>
@@ -9615,12 +9421,8 @@
       <c r="B280" s="13">
         <v>2449977838</v>
       </c>
-      <c r="C280" s="15">
-        <v>5960098180</v>
-      </c>
-      <c r="D280" s="15">
-        <v>5563962605</v>
-      </c>
+      <c r="C280" s="15"/>
+      <c r="D280" s="15"/>
       <c r="E280" s="15"/>
       <c r="F280" s="15"/>
       <c r="G280" s="15"/>
@@ -9646,18 +9448,10 @@
       <c r="B281" s="13">
         <v>2449977504</v>
       </c>
-      <c r="C281" s="15">
-        <v>5051050320</v>
-      </c>
-      <c r="D281" s="15">
-        <v>5868040581</v>
-      </c>
-      <c r="E281" s="15">
-        <v>5868039742</v>
-      </c>
-      <c r="F281" s="15">
-        <v>5563957693</v>
-      </c>
+      <c r="C281" s="15"/>
+      <c r="D281" s="15"/>
+      <c r="E281" s="15"/>
+      <c r="F281" s="15"/>
       <c r="G281" s="15"/>
       <c r="H281" s="15"/>
       <c r="I281" s="15"/>
@@ -9735,15 +9529,9 @@
       <c r="B284" s="13">
         <v>2449978809</v>
       </c>
-      <c r="C284" s="15">
-        <v>5876580109</v>
-      </c>
-      <c r="D284" s="15">
-        <v>5876581359</v>
-      </c>
-      <c r="E284" s="15">
-        <v>5563958517</v>
-      </c>
+      <c r="C284" s="15"/>
+      <c r="D284" s="15"/>
+      <c r="E284" s="15"/>
       <c r="F284" s="15"/>
       <c r="G284" s="15"/>
       <c r="H284" s="15"/>
@@ -10092,9 +9880,7 @@
       <c r="B297" s="13">
         <v>2474254390</v>
       </c>
-      <c r="C297" s="15">
-        <v>5639401044</v>
-      </c>
+      <c r="C297" s="15"/>
       <c r="D297" s="15"/>
       <c r="E297" s="15"/>
       <c r="F297" s="15"/>
@@ -10121,9 +9907,7 @@
       <c r="B298" s="13">
         <v>2474254998</v>
       </c>
-      <c r="C298" s="15">
-        <v>5639405494</v>
-      </c>
+      <c r="C298" s="15"/>
       <c r="D298" s="15"/>
       <c r="E298" s="15"/>
       <c r="F298" s="15"/>
@@ -10150,12 +9934,8 @@
       <c r="B299" s="13">
         <v>2474254021</v>
       </c>
-      <c r="C299" s="15">
-        <v>4860784281</v>
-      </c>
-      <c r="D299" s="15">
-        <v>5639406596</v>
-      </c>
+      <c r="C299" s="15"/>
+      <c r="D299" s="15"/>
       <c r="E299" s="15"/>
       <c r="F299" s="15"/>
       <c r="G299" s="15"/>
@@ -10181,9 +9961,7 @@
       <c r="B300" s="13">
         <v>2474251925</v>
       </c>
-      <c r="C300" s="15">
-        <v>5639404401</v>
-      </c>
+      <c r="C300" s="15"/>
       <c r="D300" s="15"/>
       <c r="E300" s="15"/>
       <c r="F300" s="15"/>
@@ -10237,15 +10015,9 @@
       <c r="B302" s="13">
         <v>2474254585</v>
       </c>
-      <c r="C302" s="15">
-        <v>5551362427</v>
-      </c>
-      <c r="D302" s="15">
-        <v>4860780494</v>
-      </c>
-      <c r="E302" s="15">
-        <v>5639403011</v>
-      </c>
+      <c r="C302" s="15"/>
+      <c r="D302" s="15"/>
+      <c r="E302" s="15"/>
       <c r="F302" s="15"/>
       <c r="G302" s="15"/>
       <c r="H302" s="15"/>
@@ -10270,12 +10042,7 @@
       <c r="B303" s="13">
         <v>2474252626</v>
       </c>
-      <c r="C303" s="15">
-        <v>4860785874</v>
-      </c>
-      <c r="D303" s="15">
-        <v>5639403579</v>
-      </c>
+      <c r="C303" s="15"/>
       <c r="E303" s="15"/>
       <c r="F303" s="15"/>
       <c r="G303" s="15"/>
@@ -10301,12 +10068,8 @@
       <c r="B304" s="13">
         <v>2474251481</v>
       </c>
-      <c r="C304" s="15">
-        <v>4860784321</v>
-      </c>
-      <c r="D304" s="15">
-        <v>5639403371</v>
-      </c>
+      <c r="C304" s="15"/>
+      <c r="D304" s="15"/>
       <c r="E304" s="15"/>
       <c r="F304" s="15"/>
       <c r="G304" s="15"/>
@@ -10440,9 +10203,7 @@
       <c r="B309" s="13">
         <v>2474253289</v>
       </c>
-      <c r="C309" s="15">
-        <v>5639403097</v>
-      </c>
+      <c r="C309" s="15"/>
       <c r="D309" s="15"/>
       <c r="E309" s="15"/>
       <c r="F309" s="15"/>
@@ -10469,9 +10230,7 @@
       <c r="B310" s="13">
         <v>2474252601</v>
       </c>
-      <c r="C310" s="15">
-        <v>5639404537</v>
-      </c>
+      <c r="C310" s="15"/>
       <c r="D310" s="15"/>
       <c r="E310" s="15"/>
       <c r="F310" s="15"/>
@@ -10498,9 +10257,7 @@
       <c r="B311" s="13">
         <v>2474253325</v>
       </c>
-      <c r="C311" s="15">
-        <v>5639404856</v>
-      </c>
+      <c r="C311" s="15"/>
       <c r="D311" s="15"/>
       <c r="E311" s="15"/>
       <c r="F311" s="15"/>
@@ -10554,9 +10311,7 @@
       <c r="B313" s="13">
         <v>2474253913</v>
       </c>
-      <c r="C313" s="15">
-        <v>5639404135</v>
-      </c>
+      <c r="C313" s="15"/>
       <c r="D313" s="15"/>
       <c r="E313" s="15"/>
       <c r="F313" s="15"/>
@@ -10583,12 +10338,8 @@
       <c r="B314" s="13">
         <v>2474255236</v>
       </c>
-      <c r="C314" s="15">
-        <v>4860785253</v>
-      </c>
-      <c r="D314" s="15">
-        <v>5639402463</v>
-      </c>
+      <c r="C314" s="15"/>
+      <c r="D314" s="15"/>
       <c r="E314" s="15"/>
       <c r="F314" s="15"/>
       <c r="G314" s="15"/>
@@ -10641,15 +10392,9 @@
       <c r="B316" s="13">
         <v>2474431127</v>
       </c>
-      <c r="C316" s="15">
-        <v>5152013894</v>
-      </c>
-      <c r="D316" s="15">
-        <v>4860783086</v>
-      </c>
-      <c r="E316" s="15">
-        <v>5639405153</v>
-      </c>
+      <c r="C316" s="15"/>
+      <c r="D316" s="15"/>
+      <c r="E316" s="15"/>
       <c r="F316" s="15"/>
       <c r="G316" s="15"/>
       <c r="H316" s="15"/>
@@ -10674,15 +10419,9 @@
       <c r="B317" s="13">
         <v>3691738336</v>
       </c>
-      <c r="C317" s="15">
-        <v>5152576892</v>
-      </c>
-      <c r="D317" s="15">
-        <v>4860343586</v>
-      </c>
-      <c r="E317" s="15">
-        <v>4860347463</v>
-      </c>
+      <c r="C317" s="15"/>
+      <c r="D317" s="15"/>
+      <c r="E317" s="15"/>
       <c r="F317" s="15"/>
       <c r="G317" s="15"/>
       <c r="H317" s="15"/>
@@ -10707,15 +10446,9 @@
       <c r="B318" s="13">
         <v>3691841964</v>
       </c>
-      <c r="C318" s="15">
-        <v>4860351060</v>
-      </c>
-      <c r="D318" s="15">
-        <v>4860355743</v>
-      </c>
-      <c r="E318" s="15">
-        <v>4964035357</v>
-      </c>
+      <c r="C318" s="15"/>
+      <c r="D318" s="15"/>
+      <c r="E318" s="15"/>
       <c r="F318" s="15"/>
       <c r="G318" s="15"/>
       <c r="H318" s="15"/>
@@ -10740,24 +10473,12 @@
       <c r="B319" s="13">
         <v>3691844921</v>
       </c>
-      <c r="C319" s="15">
-        <v>5152564836</v>
-      </c>
-      <c r="D319" s="15">
-        <v>4860349465</v>
-      </c>
-      <c r="E319" s="15">
-        <v>4860349569</v>
-      </c>
-      <c r="F319" s="15">
-        <v>4964036218</v>
-      </c>
-      <c r="G319" s="15">
-        <v>5960108906</v>
-      </c>
-      <c r="H319" s="15">
-        <v>5563669139</v>
-      </c>
+      <c r="C319" s="15"/>
+      <c r="D319" s="15"/>
+      <c r="E319" s="15"/>
+      <c r="F319" s="15"/>
+      <c r="G319" s="15"/>
+      <c r="H319" s="15"/>
       <c r="I319" s="15"/>
       <c r="J319" s="15"/>
       <c r="K319" s="15"/>
@@ -10779,18 +10500,10 @@
       <c r="B320" s="13">
         <v>3691842819</v>
       </c>
-      <c r="C320" s="15">
-        <v>5152533862</v>
-      </c>
-      <c r="D320" s="15">
-        <v>4860336460</v>
-      </c>
-      <c r="E320" s="15">
-        <v>4860344072</v>
-      </c>
-      <c r="F320" s="15">
-        <v>4964033216</v>
-      </c>
+      <c r="C320" s="15"/>
+      <c r="D320" s="15"/>
+      <c r="E320" s="15"/>
+      <c r="F320" s="15"/>
       <c r="G320" s="15"/>
       <c r="H320" s="15"/>
       <c r="I320" s="15"/>
@@ -10814,24 +10527,12 @@
       <c r="B321" s="13">
         <v>3691843282</v>
       </c>
-      <c r="C321" s="15">
-        <v>5152592577</v>
-      </c>
-      <c r="D321" s="15">
-        <v>5526281268</v>
-      </c>
-      <c r="E321" s="15">
-        <v>4860352753</v>
-      </c>
-      <c r="F321" s="15">
-        <v>4860354935</v>
-      </c>
-      <c r="G321" s="15">
-        <v>4964036697</v>
-      </c>
-      <c r="H321" s="15">
-        <v>5960096898</v>
-      </c>
+      <c r="C321" s="15"/>
+      <c r="D321" s="15"/>
+      <c r="E321" s="15"/>
+      <c r="F321" s="15"/>
+      <c r="G321" s="15"/>
+      <c r="H321" s="15"/>
       <c r="I321" s="15"/>
       <c r="J321" s="15"/>
       <c r="K321" s="15"/>
@@ -10853,15 +10554,9 @@
       <c r="B322" s="13">
         <v>3691843233</v>
       </c>
-      <c r="C322" s="15">
-        <v>5535489468</v>
-      </c>
-      <c r="D322" s="15">
-        <v>4860338782</v>
-      </c>
-      <c r="E322" s="15">
-        <v>4964036466</v>
-      </c>
+      <c r="C322" s="15"/>
+      <c r="D322" s="15"/>
+      <c r="E322" s="15"/>
       <c r="F322" s="15"/>
       <c r="G322" s="15"/>
       <c r="H322" s="15"/>
@@ -10886,15 +10581,9 @@
       <c r="B323" s="13">
         <v>3691843824</v>
       </c>
-      <c r="C323" s="15">
-        <v>5152694641</v>
-      </c>
-      <c r="D323" s="15">
-        <v>5526466609</v>
-      </c>
-      <c r="E323" s="15">
-        <v>4860353279</v>
-      </c>
+      <c r="C323" s="15"/>
+      <c r="D323" s="15"/>
+      <c r="E323" s="15"/>
       <c r="F323" s="15"/>
       <c r="G323" s="15"/>
       <c r="H323" s="15"/>
@@ -10946,15 +10635,8 @@
       <c r="B325" s="13">
         <v>3691843333</v>
       </c>
-      <c r="C325" s="15">
-        <v>4964036092</v>
-      </c>
-      <c r="D325" s="15">
-        <v>5960100354</v>
-      </c>
-      <c r="E325" s="15">
-        <v>5563667676</v>
-      </c>
+      <c r="C325" s="15"/>
+      <c r="D325" s="15"/>
       <c r="F325" s="15"/>
       <c r="J325" s="15"/>
       <c r="K325" s="15"/>
@@ -10976,12 +10658,8 @@
       <c r="B326" s="13">
         <v>3691843790</v>
       </c>
-      <c r="C326" s="15">
-        <v>5526529225</v>
-      </c>
-      <c r="D326" s="15">
-        <v>5960097080</v>
-      </c>
+      <c r="C326" s="15"/>
+      <c r="D326" s="15"/>
       <c r="E326" s="15"/>
       <c r="F326" s="15"/>
       <c r="G326" s="15"/>
@@ -11007,18 +10685,10 @@
       <c r="B327" s="13">
         <v>3691842613</v>
       </c>
-      <c r="C327" s="15">
-        <v>5152651714</v>
-      </c>
-      <c r="D327" s="15">
-        <v>5152033839</v>
-      </c>
-      <c r="E327" s="15">
-        <v>5526131050</v>
-      </c>
-      <c r="F327" s="15">
-        <v>4860345229</v>
-      </c>
+      <c r="C327" s="15"/>
+      <c r="D327" s="15"/>
+      <c r="E327" s="15"/>
+      <c r="F327" s="15"/>
       <c r="G327" s="15"/>
       <c r="H327" s="15"/>
       <c r="I327" s="15"/>
@@ -11042,15 +10712,9 @@
       <c r="B328" s="13">
         <v>3691843793</v>
       </c>
-      <c r="C328" s="15">
-        <v>5152542788</v>
-      </c>
-      <c r="D328" s="15">
-        <v>5526207109</v>
-      </c>
-      <c r="E328" s="15">
-        <v>4860341482</v>
-      </c>
+      <c r="C328" s="15"/>
+      <c r="D328" s="15"/>
+      <c r="E328" s="15"/>
       <c r="F328" s="15"/>
       <c r="G328" s="15"/>
       <c r="H328" s="15"/>
@@ -11075,15 +10739,9 @@
       <c r="B329" s="13">
         <v>3691844110</v>
       </c>
-      <c r="C329" s="15">
-        <v>5152552045</v>
-      </c>
-      <c r="D329" s="15">
-        <v>4860337452</v>
-      </c>
-      <c r="E329" s="15">
-        <v>4860338862</v>
-      </c>
+      <c r="C329" s="15"/>
+      <c r="D329" s="15"/>
+      <c r="E329" s="15"/>
       <c r="F329" s="15"/>
       <c r="G329" s="15"/>
       <c r="H329" s="15"/>
@@ -11108,15 +10766,9 @@
       <c r="B330" s="13">
         <v>3691844929</v>
       </c>
-      <c r="C330" s="15">
-        <v>5152653667</v>
-      </c>
-      <c r="D330" s="15">
-        <v>5535510237</v>
-      </c>
-      <c r="E330" s="15">
-        <v>4860352426</v>
-      </c>
+      <c r="C330" s="15"/>
+      <c r="D330" s="15"/>
+      <c r="E330" s="15"/>
       <c r="F330" s="15"/>
       <c r="G330" s="15"/>
       <c r="H330" s="15"/>
@@ -11141,21 +10793,11 @@
       <c r="B331" s="13">
         <v>3691844839</v>
       </c>
-      <c r="C331" s="15">
-        <v>5152606344</v>
-      </c>
-      <c r="D331" s="15">
-        <v>5535536654</v>
-      </c>
-      <c r="E331" s="15">
-        <v>5152605404</v>
-      </c>
-      <c r="F331" s="15">
-        <v>4860335668</v>
-      </c>
-      <c r="G331" s="15">
-        <v>4860338275</v>
-      </c>
+      <c r="C331" s="15"/>
+      <c r="D331" s="15"/>
+      <c r="E331" s="15"/>
+      <c r="F331" s="15"/>
+      <c r="G331" s="15"/>
       <c r="H331" s="15"/>
       <c r="I331" s="15"/>
       <c r="J331" s="15"/>
@@ -11178,18 +10820,10 @@
       <c r="B332" s="13">
         <v>3691843907</v>
       </c>
-      <c r="C332" s="16">
-        <v>5152564128</v>
-      </c>
-      <c r="D332" s="15">
-        <v>4860349462</v>
-      </c>
-      <c r="E332" s="15">
-        <v>4860350149</v>
-      </c>
-      <c r="F332" s="15">
-        <v>4964035035</v>
-      </c>
+      <c r="C332" s="16"/>
+      <c r="D332" s="15"/>
+      <c r="E332" s="15"/>
+      <c r="F332" s="15"/>
       <c r="G332" s="15"/>
       <c r="H332" s="15"/>
       <c r="I332" s="15"/>
@@ -11216,8 +10850,6 @@
       <c r="C333" s="15"/>
       <c r="D333" s="15"/>
       <c r="E333" s="15"/>
-      <c r="F333" s="15"/>
-      <c r="G333" s="15"/>
       <c r="H333" s="15"/>
       <c r="I333" s="15"/>
       <c r="J333" s="15"/>
@@ -11244,9 +10876,6 @@
       <c r="D334" s="15"/>
       <c r="E334" s="15"/>
       <c r="F334" s="15"/>
-      <c r="G334" s="15"/>
-      <c r="H334" s="15"/>
-      <c r="I334" s="15"/>
       <c r="J334" s="15"/>
       <c r="K334" s="15"/>
       <c r="L334" s="15"/>
@@ -11321,15 +10950,9 @@
       <c r="B337" s="13">
         <v>3691842765</v>
       </c>
-      <c r="C337" s="15">
-        <v>5152632989</v>
-      </c>
-      <c r="D337" s="15">
-        <v>5960096703</v>
-      </c>
-      <c r="E337" s="15">
-        <v>4860336565</v>
-      </c>
+      <c r="C337" s="15"/>
+      <c r="D337" s="15"/>
+      <c r="E337" s="15"/>
       <c r="F337" s="15"/>
       <c r="G337" s="15"/>
       <c r="H337" s="15"/>
@@ -11354,15 +10977,9 @@
       <c r="B338" s="13">
         <v>3691844111</v>
       </c>
-      <c r="C338" s="16">
-        <v>5152552972</v>
-      </c>
-      <c r="D338" s="15">
-        <v>5960098274</v>
-      </c>
-      <c r="E338" s="15">
-        <v>4964035304</v>
-      </c>
+      <c r="C338" s="16"/>
+      <c r="D338" s="15"/>
+      <c r="E338" s="15"/>
       <c r="F338" s="15"/>
       <c r="G338" s="15"/>
       <c r="H338" s="15"/>
@@ -11387,15 +11004,9 @@
       <c r="B339" s="13">
         <v>3691844304</v>
       </c>
-      <c r="C339" s="16">
-        <v>5152672227</v>
-      </c>
-      <c r="D339" s="15">
-        <v>4860351407</v>
-      </c>
-      <c r="E339" s="15">
-        <v>4964035946</v>
-      </c>
+      <c r="C339" s="16"/>
+      <c r="D339" s="15"/>
+      <c r="E339" s="15"/>
       <c r="F339" s="15"/>
       <c r="G339" s="15"/>
       <c r="H339" s="15"/>
@@ -11420,15 +11031,9 @@
       <c r="B340" s="13">
         <v>3691844657</v>
       </c>
-      <c r="C340" s="15">
-        <v>5960098240</v>
-      </c>
-      <c r="D340" s="15">
-        <v>4860342850</v>
-      </c>
-      <c r="E340" s="15">
-        <v>4860344776</v>
-      </c>
+      <c r="C340" s="15"/>
+      <c r="D340" s="15"/>
+      <c r="E340" s="15"/>
       <c r="F340" s="15"/>
       <c r="G340" s="15"/>
       <c r="H340" s="15"/>
@@ -11453,15 +11058,9 @@
       <c r="B341" s="13">
         <v>3691844061</v>
       </c>
-      <c r="C341" s="15">
-        <v>5152580492</v>
-      </c>
-      <c r="D341" s="15">
-        <v>4860349644</v>
-      </c>
-      <c r="E341" s="15">
-        <v>5563666823</v>
-      </c>
+      <c r="C341" s="15"/>
+      <c r="D341" s="15"/>
+      <c r="E341" s="15"/>
       <c r="F341" s="15"/>
       <c r="G341" s="15"/>
       <c r="H341" s="15"/>
@@ -11513,12 +11112,8 @@
       <c r="B343" s="13">
         <v>3691843846</v>
       </c>
-      <c r="C343" s="15">
-        <v>5152653969</v>
-      </c>
-      <c r="D343" s="15">
-        <v>4860355373</v>
-      </c>
+      <c r="C343" s="15"/>
+      <c r="D343" s="15"/>
       <c r="E343" s="15"/>
       <c r="F343" s="15"/>
       <c r="G343" s="15"/>
@@ -11544,9 +11139,7 @@
       <c r="B344" s="13">
         <v>3691844082</v>
       </c>
-      <c r="C344" s="15">
-        <v>5152624934</v>
-      </c>
+      <c r="C344" s="15"/>
       <c r="D344" s="15"/>
       <c r="E344" s="15"/>
       <c r="F344" s="15"/>
@@ -11573,15 +11166,9 @@
       <c r="B345" s="13">
         <v>3691842493</v>
       </c>
-      <c r="C345" s="15">
-        <v>5152637550</v>
-      </c>
-      <c r="D345" s="15">
-        <v>4860340081</v>
-      </c>
-      <c r="E345" s="15">
-        <v>4964035160</v>
-      </c>
+      <c r="C345" s="15"/>
+      <c r="D345" s="15"/>
+      <c r="E345" s="15"/>
       <c r="F345" s="15"/>
       <c r="G345" s="15"/>
       <c r="H345" s="15"/>
@@ -11606,15 +11193,9 @@
       <c r="B346" s="13">
         <v>3691843045</v>
       </c>
-      <c r="C346" s="15">
-        <v>5152573932</v>
-      </c>
-      <c r="D346" s="15">
-        <v>5151856180</v>
-      </c>
-      <c r="E346" s="15">
-        <v>4964035655</v>
-      </c>
+      <c r="C346" s="15"/>
+      <c r="D346" s="15"/>
+      <c r="E346" s="15"/>
       <c r="F346" s="15"/>
       <c r="G346" s="15"/>
       <c r="H346" s="15"/>
@@ -11639,15 +11220,8 @@
       <c r="B347" s="13">
         <v>3697385068</v>
       </c>
-      <c r="C347" s="15">
-        <v>5152565738</v>
-      </c>
-      <c r="D347" s="15">
-        <v>4860355965</v>
-      </c>
-      <c r="E347" s="15">
-        <v>4964035153</v>
-      </c>
+      <c r="C347" s="15"/>
+      <c r="D347" s="15"/>
       <c r="F347" s="15"/>
       <c r="G347" s="15"/>
       <c r="H347" s="15"/>
@@ -11672,12 +11246,8 @@
       <c r="B348" s="13">
         <v>3697386937</v>
       </c>
-      <c r="C348" s="15">
-        <v>5152594716</v>
-      </c>
-      <c r="D348" s="15">
-        <v>5960102304</v>
-      </c>
+      <c r="C348" s="15"/>
+      <c r="D348" s="15"/>
       <c r="E348" s="15"/>
       <c r="F348" s="15"/>
       <c r="G348" s="15"/>
@@ -11703,18 +11273,8 @@
       <c r="B349" s="13">
         <v>3697377718</v>
       </c>
-      <c r="C349" s="15">
-        <v>5152633971</v>
-      </c>
-      <c r="D349" s="15">
-        <v>5551026135</v>
-      </c>
-      <c r="E349" s="15">
-        <v>4860339528</v>
-      </c>
-      <c r="F349" s="15">
-        <v>4964034252</v>
-      </c>
+      <c r="C349" s="15"/>
+      <c r="D349" s="15"/>
       <c r="G349" s="15"/>
       <c r="H349" s="15"/>
       <c r="I349" s="15"/>
@@ -11738,12 +11298,8 @@
       <c r="B350" s="13">
         <v>3697386081</v>
       </c>
-      <c r="C350" s="15">
-        <v>5152542271</v>
-      </c>
-      <c r="D350" s="15">
-        <v>4860337608</v>
-      </c>
+      <c r="C350" s="15"/>
+      <c r="D350" s="15"/>
       <c r="E350" s="15"/>
       <c r="F350" s="15"/>
       <c r="G350" s="15"/>
@@ -11769,9 +11325,7 @@
       <c r="B351" s="13">
         <v>3697386923</v>
       </c>
-      <c r="C351" s="15">
-        <v>5152557400</v>
-      </c>
+      <c r="C351" s="15"/>
       <c r="D351" s="15"/>
       <c r="E351" s="15"/>
       <c r="F351" s="15"/>
@@ -11798,9 +11352,7 @@
       <c r="B352" s="13">
         <v>3697385185</v>
       </c>
-      <c r="C352" s="15">
-        <v>5152592663</v>
-      </c>
+      <c r="C352" s="15"/>
       <c r="D352" s="15"/>
       <c r="E352" s="15"/>
       <c r="F352" s="15"/>
@@ -11827,9 +11379,7 @@
       <c r="B353" s="13">
         <v>3697385622</v>
       </c>
-      <c r="C353" s="15">
-        <v>5152654989</v>
-      </c>
+      <c r="C353" s="15"/>
       <c r="D353" s="15"/>
       <c r="E353" s="15"/>
       <c r="F353" s="15"/>
@@ -11856,12 +11406,8 @@
       <c r="B354" s="13">
         <v>3697387116</v>
       </c>
-      <c r="C354" s="15">
-        <v>5152647450</v>
-      </c>
-      <c r="D354" s="15">
-        <v>5526406428</v>
-      </c>
+      <c r="C354" s="15"/>
+      <c r="D354" s="15"/>
       <c r="E354" s="15"/>
       <c r="F354" s="15"/>
       <c r="G354" s="15"/>
@@ -11887,9 +11433,7 @@
       <c r="B355" s="13">
         <v>3697378793</v>
       </c>
-      <c r="C355" s="15">
-        <v>5152634960</v>
-      </c>
+      <c r="C355" s="15"/>
       <c r="D355" s="15"/>
       <c r="E355" s="15"/>
       <c r="F355" s="15"/>
@@ -11916,9 +11460,7 @@
       <c r="B356" s="13">
         <v>3697384946</v>
       </c>
-      <c r="C356" s="15">
-        <v>5152556613</v>
-      </c>
+      <c r="C356" s="15"/>
       <c r="D356" s="15"/>
       <c r="E356" s="15"/>
       <c r="F356" s="15"/>
@@ -11945,12 +11487,8 @@
       <c r="B357" s="13">
         <v>3697385546</v>
       </c>
-      <c r="C357" s="15">
-        <v>5152589207</v>
-      </c>
-      <c r="D357" s="15">
-        <v>4860356808</v>
-      </c>
+      <c r="C357" s="15"/>
+      <c r="D357" s="15"/>
       <c r="E357" s="15"/>
       <c r="F357" s="15"/>
       <c r="G357" s="15"/>
@@ -11976,15 +11514,9 @@
       <c r="B358" s="13">
         <v>3697386517</v>
       </c>
-      <c r="C358" s="15">
-        <v>5960094476</v>
-      </c>
-      <c r="D358" s="15">
-        <v>4964035051</v>
-      </c>
-      <c r="E358" s="15">
-        <v>5563684028</v>
-      </c>
+      <c r="C358" s="15"/>
+      <c r="D358" s="15"/>
+      <c r="E358" s="15"/>
       <c r="F358" s="15"/>
       <c r="G358" s="15"/>
       <c r="H358" s="15"/>
@@ -12036,9 +11568,7 @@
       <c r="B360" s="13">
         <v>3697386057</v>
       </c>
-      <c r="C360" s="15">
-        <v>5152633985</v>
-      </c>
+      <c r="C360" s="15"/>
       <c r="D360" s="15"/>
       <c r="E360" s="15"/>
       <c r="F360" s="15"/>
@@ -12065,9 +11595,7 @@
       <c r="B361" s="13">
         <v>3697386822</v>
       </c>
-      <c r="C361" s="15">
-        <v>4860351247</v>
-      </c>
+      <c r="C361" s="15"/>
       <c r="D361" s="15"/>
       <c r="E361" s="15"/>
       <c r="F361" s="15"/>
@@ -12094,12 +11622,8 @@
       <c r="B362" s="13">
         <v>3697386529</v>
       </c>
-      <c r="C362" s="15">
-        <v>5551360225</v>
-      </c>
-      <c r="D362" s="15">
-        <v>5960095247</v>
-      </c>
+      <c r="C362" s="15"/>
+      <c r="D362" s="15"/>
       <c r="E362" s="15"/>
       <c r="F362" s="15"/>
       <c r="G362" s="15"/>
@@ -12125,12 +11649,8 @@
       <c r="B363" s="13">
         <v>3697385541</v>
       </c>
-      <c r="C363" s="15">
-        <v>5152638516</v>
-      </c>
-      <c r="D363" s="15">
-        <v>4860340111</v>
-      </c>
+      <c r="C363" s="15"/>
+      <c r="D363" s="15"/>
       <c r="E363" s="15"/>
       <c r="F363" s="15"/>
       <c r="G363" s="15"/>
@@ -12156,9 +11676,7 @@
       <c r="B364" s="13">
         <v>3697384880</v>
       </c>
-      <c r="C364" s="15">
-        <v>5152632422</v>
-      </c>
+      <c r="C364" s="15"/>
       <c r="D364" s="15"/>
       <c r="E364" s="15"/>
       <c r="F364" s="15"/>
@@ -12185,18 +11703,10 @@
       <c r="B365" s="13">
         <v>3697386735</v>
       </c>
-      <c r="C365" s="15">
-        <v>5152556384</v>
-      </c>
-      <c r="D365" s="15">
-        <v>5526511597</v>
-      </c>
-      <c r="E365" s="15">
-        <v>5960098250</v>
-      </c>
-      <c r="F365" s="15">
-        <v>4860354912</v>
-      </c>
+      <c r="C365" s="15"/>
+      <c r="D365" s="15"/>
+      <c r="E365" s="15"/>
+      <c r="F365" s="15"/>
       <c r="G365" s="15"/>
       <c r="H365" s="15"/>
       <c r="I365" s="15"/>
@@ -12220,12 +11730,8 @@
       <c r="B366" s="13">
         <v>3697386369</v>
       </c>
-      <c r="C366" s="15">
-        <v>5152580752</v>
-      </c>
-      <c r="D366" s="15">
-        <v>5526501327</v>
-      </c>
+      <c r="C366" s="15"/>
+      <c r="D366" s="15"/>
       <c r="E366" s="15"/>
       <c r="F366" s="15"/>
       <c r="G366" s="15"/>
@@ -12251,18 +11757,10 @@
       <c r="B367" s="13">
         <v>3697386368</v>
       </c>
-      <c r="C367" s="15">
-        <v>5551318819</v>
-      </c>
-      <c r="D367" s="15">
-        <v>5960101807</v>
-      </c>
-      <c r="E367" s="15">
-        <v>4860353120</v>
-      </c>
-      <c r="F367" s="15">
-        <v>5563666278</v>
-      </c>
+      <c r="C367" s="15"/>
+      <c r="D367" s="15"/>
+      <c r="E367" s="15"/>
+      <c r="F367" s="15"/>
       <c r="G367" s="15"/>
       <c r="H367" s="15"/>
       <c r="I367" s="15"/>
@@ -12286,12 +11784,8 @@
       <c r="B368" s="13">
         <v>3697384419</v>
       </c>
-      <c r="C368" s="15">
-        <v>5152662657</v>
-      </c>
-      <c r="D368" s="15">
-        <v>4860356155</v>
-      </c>
+      <c r="C368" s="15"/>
+      <c r="D368" s="15"/>
       <c r="E368" s="15"/>
       <c r="F368" s="15"/>
       <c r="G368" s="15"/>
@@ -12317,15 +11811,9 @@
       <c r="B369" s="13">
         <v>3697386364</v>
       </c>
-      <c r="C369" s="15">
-        <v>5152592608</v>
-      </c>
-      <c r="D369" s="15">
-        <v>4860355456</v>
-      </c>
-      <c r="E369" s="15">
-        <v>4964035584</v>
-      </c>
+      <c r="C369" s="15"/>
+      <c r="D369" s="15"/>
+      <c r="E369" s="15"/>
       <c r="F369" s="15"/>
       <c r="G369" s="15"/>
       <c r="H369" s="15"/>
@@ -12350,15 +11838,9 @@
       <c r="B370" s="13">
         <v>3697386666</v>
       </c>
-      <c r="C370" s="15">
-        <v>5152587373</v>
-      </c>
-      <c r="D370" s="15">
-        <v>5534752505</v>
-      </c>
-      <c r="E370" s="15">
-        <v>4964036284</v>
-      </c>
+      <c r="C370" s="15"/>
+      <c r="D370" s="15"/>
+      <c r="E370" s="15"/>
       <c r="F370" s="15"/>
       <c r="G370" s="15"/>
       <c r="H370" s="15"/>
@@ -12383,18 +11865,10 @@
       <c r="B371" s="13">
         <v>3697386325</v>
       </c>
-      <c r="C371" s="15">
-        <v>5152569863</v>
-      </c>
-      <c r="D371" s="15">
-        <v>5550819181</v>
-      </c>
-      <c r="E371" s="15">
-        <v>4860351392</v>
-      </c>
-      <c r="F371" s="15">
-        <v>4964035631</v>
-      </c>
+      <c r="C371" s="15"/>
+      <c r="D371" s="15"/>
+      <c r="E371" s="15"/>
+      <c r="F371" s="15"/>
       <c r="G371" s="15"/>
       <c r="H371" s="15"/>
       <c r="I371" s="15"/>
@@ -12418,21 +11892,9 @@
       <c r="B372" s="13">
         <v>3697387233</v>
       </c>
-      <c r="C372" s="15">
-        <v>5526219486</v>
-      </c>
-      <c r="D372" s="15">
-        <v>5960098066</v>
-      </c>
-      <c r="E372" s="15">
-        <v>5152698422</v>
-      </c>
-      <c r="F372" s="15">
-        <v>4860343652</v>
-      </c>
-      <c r="G372" s="15">
-        <v>4964034696</v>
-      </c>
+      <c r="C372" s="15"/>
+      <c r="D372" s="15"/>
+      <c r="E372" s="15"/>
       <c r="H372" s="15"/>
       <c r="I372" s="15"/>
       <c r="J372" s="15"/>
@@ -12455,12 +11917,8 @@
       <c r="B373" s="13">
         <v>3697386036</v>
       </c>
-      <c r="C373" s="15">
-        <v>5152574966</v>
-      </c>
-      <c r="D373" s="15">
-        <v>4964033485</v>
-      </c>
+      <c r="C373" s="15"/>
+      <c r="D373" s="15"/>
       <c r="E373" s="15"/>
       <c r="F373" s="15"/>
       <c r="G373" s="15"/>
@@ -12486,15 +11944,9 @@
       <c r="B374" s="13">
         <v>3697387185</v>
       </c>
-      <c r="C374" s="15">
-        <v>5152580258</v>
-      </c>
-      <c r="D374" s="15">
-        <v>5526476740</v>
-      </c>
-      <c r="E374" s="15">
-        <v>4860347522</v>
-      </c>
+      <c r="C374" s="15"/>
+      <c r="D374" s="15"/>
+      <c r="E374" s="15"/>
       <c r="F374" s="15"/>
       <c r="G374" s="15"/>
       <c r="H374" s="15"/>
@@ -12519,9 +11971,7 @@
       <c r="B375" s="13">
         <v>3697387392</v>
       </c>
-      <c r="C375" s="15">
-        <v>4860354829</v>
-      </c>
+      <c r="C375" s="15"/>
       <c r="D375" s="15"/>
       <c r="E375" s="15"/>
       <c r="F375" s="15"/>
@@ -12548,9 +11998,7 @@
       <c r="B376" s="13">
         <v>3697504349</v>
       </c>
-      <c r="C376" s="16">
-        <v>5551072567</v>
-      </c>
+      <c r="C376" s="16"/>
       <c r="D376" s="15"/>
       <c r="E376" s="15"/>
       <c r="F376" s="15"/>
@@ -12577,15 +12025,9 @@
       <c r="B377" s="13">
         <v>3697505185</v>
       </c>
-      <c r="C377" s="15">
-        <v>5152565804</v>
-      </c>
-      <c r="D377" s="15">
-        <v>4860346007</v>
-      </c>
-      <c r="E377" s="15">
-        <v>4860347147</v>
-      </c>
+      <c r="C377" s="15"/>
+      <c r="D377" s="15"/>
+      <c r="E377" s="15"/>
       <c r="F377" s="15"/>
       <c r="G377" s="15"/>
       <c r="H377" s="15"/>
@@ -12610,15 +12052,8 @@
       <c r="B378" s="13">
         <v>3697504278</v>
       </c>
-      <c r="C378" s="15">
-        <v>5152603418</v>
-      </c>
-      <c r="D378" s="15">
-        <v>4860341448</v>
-      </c>
-      <c r="E378" s="15">
-        <v>4964035519</v>
-      </c>
+      <c r="C378" s="15"/>
+      <c r="D378" s="15"/>
       <c r="F378" s="15"/>
       <c r="G378" s="15"/>
       <c r="H378" s="15"/>
@@ -12643,15 +12078,9 @@
       <c r="B379" s="13">
         <v>3697504906</v>
       </c>
-      <c r="C379" s="15">
-        <v>5152559622</v>
-      </c>
-      <c r="D379" s="15">
-        <v>4860349353</v>
-      </c>
-      <c r="E379" s="15">
-        <v>4964037022</v>
-      </c>
+      <c r="C379" s="15"/>
+      <c r="D379" s="15"/>
+      <c r="E379" s="15"/>
       <c r="F379" s="15"/>
       <c r="G379" s="15"/>
       <c r="H379" s="15"/>
@@ -12676,18 +12105,10 @@
       <c r="B380" s="13">
         <v>3697505720</v>
       </c>
-      <c r="C380" s="15">
-        <v>5152634702</v>
-      </c>
-      <c r="D380" s="15">
-        <v>5960097809</v>
-      </c>
-      <c r="E380" s="15">
-        <v>4860336130</v>
-      </c>
-      <c r="F380" s="15">
-        <v>4964033021</v>
-      </c>
+      <c r="C380" s="15"/>
+      <c r="D380" s="15"/>
+      <c r="E380" s="15"/>
+      <c r="F380" s="15"/>
       <c r="G380" s="15"/>
       <c r="H380" s="15"/>
       <c r="I380" s="15"/>
@@ -12711,15 +12132,9 @@
       <c r="B381" s="13">
         <v>3697505355</v>
       </c>
-      <c r="C381" s="15">
-        <v>5152593456</v>
-      </c>
-      <c r="D381" s="15">
-        <v>4860353395</v>
-      </c>
-      <c r="E381" s="15">
-        <v>4964037137</v>
-      </c>
+      <c r="C381" s="15"/>
+      <c r="D381" s="15"/>
+      <c r="E381" s="15"/>
       <c r="F381" s="15"/>
       <c r="G381" s="15"/>
       <c r="H381" s="15"/>
@@ -12744,18 +12159,10 @@
       <c r="B382" s="13">
         <v>3697504484</v>
       </c>
-      <c r="C382" s="15">
-        <v>5152564856</v>
-      </c>
-      <c r="D382" s="15">
-        <v>5550906265</v>
-      </c>
-      <c r="E382" s="15">
-        <v>5960099834</v>
-      </c>
-      <c r="F382" s="15">
-        <v>4860358697</v>
-      </c>
+      <c r="C382" s="15"/>
+      <c r="D382" s="15"/>
+      <c r="E382" s="15"/>
+      <c r="F382" s="15"/>
       <c r="G382" s="15"/>
       <c r="H382" s="15"/>
       <c r="I382" s="15"/>
@@ -12779,18 +12186,10 @@
       <c r="B383" s="13">
         <v>3697504162</v>
       </c>
-      <c r="C383" s="15">
-        <v>5152566675</v>
-      </c>
-      <c r="D383" s="15">
-        <v>5526293508</v>
-      </c>
-      <c r="E383" s="15">
-        <v>5960094415</v>
-      </c>
-      <c r="F383" s="15">
-        <v>4860354715</v>
-      </c>
+      <c r="C383" s="15"/>
+      <c r="D383" s="15"/>
+      <c r="E383" s="15"/>
+      <c r="F383" s="15"/>
       <c r="G383" s="15"/>
       <c r="H383" s="15"/>
       <c r="I383" s="15"/>
@@ -12814,18 +12213,10 @@
       <c r="B384" s="13">
         <v>3697505218</v>
       </c>
-      <c r="C384" s="15">
-        <v>5152586855</v>
-      </c>
-      <c r="D384" s="15">
-        <v>4860354239</v>
-      </c>
-      <c r="E384" s="15">
-        <v>4964034515</v>
-      </c>
-      <c r="F384" s="15">
-        <v>5960098458</v>
-      </c>
+      <c r="C384" s="15"/>
+      <c r="D384" s="15"/>
+      <c r="E384" s="15"/>
+      <c r="F384" s="15"/>
       <c r="G384" s="15"/>
       <c r="H384" s="15"/>
       <c r="I384" s="15"/>
@@ -12849,9 +12240,7 @@
       <c r="B385" s="13">
         <v>3697505811</v>
       </c>
-      <c r="C385" s="15">
-        <v>5563645075</v>
-      </c>
+      <c r="C385" s="15"/>
       <c r="D385" s="15"/>
       <c r="E385" s="15"/>
       <c r="F385" s="15"/>
@@ -12878,18 +12267,10 @@
       <c r="B386" s="13">
         <v>3697504168</v>
       </c>
-      <c r="C386" s="15">
-        <v>5152558957</v>
-      </c>
-      <c r="D386" s="15">
-        <v>5535073512</v>
-      </c>
-      <c r="E386" s="15">
-        <v>5152032269</v>
-      </c>
-      <c r="F386" s="15">
-        <v>5152609270</v>
-      </c>
+      <c r="C386" s="15"/>
+      <c r="D386" s="15"/>
+      <c r="E386" s="15"/>
+      <c r="F386" s="15"/>
       <c r="G386" s="15"/>
       <c r="H386" s="15"/>
       <c r="I386" s="15"/>
@@ -12913,15 +12294,9 @@
       <c r="B387" s="13">
         <v>3697504479</v>
       </c>
-      <c r="C387" s="15">
-        <v>5152582424</v>
-      </c>
-      <c r="D387" s="15">
-        <v>4860348845</v>
-      </c>
-      <c r="E387" s="15">
-        <v>4860352132</v>
-      </c>
+      <c r="C387" s="15"/>
+      <c r="D387" s="15"/>
+      <c r="E387" s="15"/>
       <c r="F387" s="15"/>
       <c r="G387" s="15"/>
       <c r="H387" s="15"/>
@@ -12946,15 +12321,9 @@
       <c r="B388" s="13">
         <v>3697504448</v>
       </c>
-      <c r="C388" s="15">
-        <v>5152582989</v>
-      </c>
-      <c r="D388" s="15">
-        <v>5152572919</v>
-      </c>
-      <c r="E388" s="15">
-        <v>4860346483</v>
-      </c>
+      <c r="C388" s="15"/>
+      <c r="D388" s="15"/>
+      <c r="E388" s="15"/>
       <c r="F388" s="15"/>
       <c r="G388" s="15"/>
       <c r="H388" s="15"/>
@@ -12979,15 +12348,9 @@
       <c r="B389" s="13">
         <v>3697504613</v>
       </c>
-      <c r="C389" s="15">
-        <v>5152566089</v>
-      </c>
-      <c r="D389" s="15">
-        <v>5152002854</v>
-      </c>
-      <c r="E389" s="15">
-        <v>4860347049</v>
-      </c>
+      <c r="C389" s="15"/>
+      <c r="D389" s="15"/>
+      <c r="E389" s="15"/>
       <c r="F389" s="15"/>
       <c r="G389" s="15"/>
       <c r="H389" s="15"/>
@@ -13012,12 +12375,8 @@
       <c r="B390" s="13">
         <v>3697504303</v>
       </c>
-      <c r="C390" s="16">
-        <v>5152666487</v>
-      </c>
-      <c r="D390" s="15">
-        <v>4860345464</v>
-      </c>
+      <c r="C390" s="16"/>
+      <c r="D390" s="15"/>
       <c r="E390" s="15"/>
       <c r="F390" s="15"/>
       <c r="G390" s="15"/>
@@ -13043,15 +12402,8 @@
       <c r="B391" s="13">
         <v>3697504999</v>
       </c>
-      <c r="C391" s="15">
-        <v>5152568944</v>
-      </c>
-      <c r="D391" s="15">
-        <v>5535005093</v>
-      </c>
-      <c r="E391" s="15">
-        <v>4860349579</v>
-      </c>
+      <c r="C391" s="15"/>
+      <c r="D391" s="15"/>
       <c r="F391" s="15"/>
       <c r="G391" s="15"/>
       <c r="H391" s="15"/>
@@ -13103,21 +12455,11 @@
       <c r="B393" s="13">
         <v>3697504347</v>
       </c>
-      <c r="C393" s="15">
-        <v>5152650957</v>
-      </c>
-      <c r="D393" s="15">
-        <v>4860346280</v>
-      </c>
-      <c r="E393" s="15">
-        <v>5960096034</v>
-      </c>
-      <c r="F393" s="15">
-        <v>5551083402</v>
-      </c>
-      <c r="G393" s="15">
-        <v>5563669110</v>
-      </c>
+      <c r="C393" s="15"/>
+      <c r="D393" s="15"/>
+      <c r="E393" s="15"/>
+      <c r="F393" s="15"/>
+      <c r="G393" s="15"/>
       <c r="H393" s="15"/>
       <c r="I393" s="15"/>
       <c r="J393" s="15"/>
@@ -13140,27 +12482,13 @@
       <c r="B394" s="13">
         <v>3697504996</v>
       </c>
-      <c r="C394" s="15">
-        <v>5152547543</v>
-      </c>
-      <c r="D394" s="15">
-        <v>5534875016</v>
-      </c>
-      <c r="E394" s="15">
-        <v>5152635814</v>
-      </c>
-      <c r="F394" s="15">
-        <v>4860351913</v>
-      </c>
-      <c r="G394" s="15">
-        <v>4964035409</v>
-      </c>
-      <c r="H394" s="15">
-        <v>5960096320</v>
-      </c>
-      <c r="I394" s="15">
-        <v>5563682254</v>
-      </c>
+      <c r="C394" s="15"/>
+      <c r="D394" s="15"/>
+      <c r="E394" s="15"/>
+      <c r="F394" s="15"/>
+      <c r="G394" s="15"/>
+      <c r="H394" s="15"/>
+      <c r="I394" s="15"/>
       <c r="J394" s="15"/>
       <c r="K394" s="15"/>
       <c r="L394" s="15"/>
@@ -13181,21 +12509,11 @@
       <c r="B395" s="13">
         <v>3697504363</v>
       </c>
-      <c r="C395" s="16">
-        <v>5152666473</v>
-      </c>
-      <c r="D395" s="15">
-        <v>5526215018</v>
-      </c>
-      <c r="E395" s="15">
-        <v>4860355922</v>
-      </c>
-      <c r="F395" s="15">
-        <v>5960099989</v>
-      </c>
-      <c r="G395" s="15">
-        <v>5563670332</v>
-      </c>
+      <c r="C395" s="16"/>
+      <c r="D395" s="15"/>
+      <c r="E395" s="15"/>
+      <c r="F395" s="15"/>
+      <c r="G395" s="15"/>
       <c r="H395" s="15"/>
       <c r="I395" s="15"/>
       <c r="J395" s="15"/>
@@ -13218,12 +12536,8 @@
       <c r="B396" s="13">
         <v>3697505978</v>
       </c>
-      <c r="C396" s="15">
-        <v>5152544007</v>
-      </c>
-      <c r="D396" s="15">
-        <v>5960098646</v>
-      </c>
+      <c r="C396" s="15"/>
+      <c r="D396" s="15"/>
       <c r="E396" s="15"/>
       <c r="F396" s="15"/>
       <c r="G396" s="15"/>
@@ -13249,15 +12563,9 @@
       <c r="B397" s="13">
         <v>3697504998</v>
       </c>
-      <c r="C397" s="15">
-        <v>5152544942</v>
-      </c>
-      <c r="D397" s="15">
-        <v>5960097951</v>
-      </c>
-      <c r="E397" s="15">
-        <v>5563678263</v>
-      </c>
+      <c r="C397" s="15"/>
+      <c r="D397" s="15"/>
+      <c r="E397" s="15"/>
       <c r="F397" s="15"/>
       <c r="G397" s="15"/>
       <c r="H397" s="15"/>
@@ -13282,15 +12590,9 @@
       <c r="B398" s="13">
         <v>3697504814</v>
       </c>
-      <c r="C398" s="15">
-        <v>5526507678</v>
-      </c>
-      <c r="D398" s="15">
-        <v>5960097051</v>
-      </c>
-      <c r="E398" s="15">
-        <v>5563676577</v>
-      </c>
+      <c r="C398" s="15"/>
+      <c r="D398" s="15"/>
+      <c r="E398" s="15"/>
       <c r="F398" s="15"/>
       <c r="G398" s="15"/>
       <c r="H398" s="15"/>
@@ -13315,18 +12617,10 @@
       <c r="B399" s="13">
         <v>3697505764</v>
       </c>
-      <c r="C399" s="15">
-        <v>5534886498</v>
-      </c>
-      <c r="D399" s="15">
-        <v>4860341632</v>
-      </c>
-      <c r="E399" s="15">
-        <v>5960099631</v>
-      </c>
-      <c r="F399" s="15">
-        <v>5563677097</v>
-      </c>
+      <c r="C399" s="15"/>
+      <c r="D399" s="15"/>
+      <c r="E399" s="15"/>
+      <c r="F399" s="15"/>
       <c r="G399" s="15"/>
       <c r="H399" s="15"/>
       <c r="I399" s="15"/>
@@ -13350,12 +12644,8 @@
       <c r="B400" s="13">
         <v>3697506004</v>
       </c>
-      <c r="C400" s="15">
-        <v>5551065875</v>
-      </c>
-      <c r="D400" s="15">
-        <v>5960098689</v>
-      </c>
+      <c r="C400" s="15"/>
+      <c r="D400" s="15"/>
       <c r="E400" s="15"/>
       <c r="F400" s="15"/>
       <c r="G400" s="15"/>
@@ -13381,9 +12671,7 @@
       <c r="B401" s="13">
         <v>3697505436</v>
       </c>
-      <c r="C401" s="15">
-        <v>5960094846</v>
-      </c>
+      <c r="C401" s="15"/>
       <c r="D401" s="15"/>
       <c r="E401" s="15"/>
       <c r="F401" s="15"/>
@@ -13437,15 +12725,9 @@
       <c r="B403" s="13">
         <v>3697505575</v>
       </c>
-      <c r="C403" s="15">
-        <v>5535033445</v>
-      </c>
-      <c r="D403" s="15">
-        <v>5960102387</v>
-      </c>
-      <c r="E403" s="15">
-        <v>5563676115</v>
-      </c>
+      <c r="C403" s="15"/>
+      <c r="D403" s="15"/>
+      <c r="E403" s="15"/>
       <c r="F403" s="15"/>
       <c r="G403" s="15"/>
       <c r="H403" s="15"/>
@@ -13470,12 +12752,8 @@
       <c r="B404" s="13">
         <v>3701081855</v>
       </c>
-      <c r="C404" s="15">
-        <v>5960100802</v>
-      </c>
-      <c r="D404" s="15">
-        <v>5563677766</v>
-      </c>
+      <c r="C404" s="15"/>
+      <c r="D404" s="15"/>
       <c r="E404" s="15"/>
       <c r="F404" s="15"/>
       <c r="G404" s="15"/>
